--- a/public/assets/Importacion de usuarios.xlsx
+++ b/public/assets/Importacion de usuarios.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
   <si>
     <t>NOMBRES</t>
   </si>
@@ -75,6 +75,21 @@
   </si>
   <si>
     <t>EMPRESA</t>
+  </si>
+  <si>
+    <t>944556677</t>
+  </si>
+  <si>
+    <t>EGRESADO</t>
+  </si>
+  <si>
+    <t>Ana Torres Quispe</t>
+  </si>
+  <si>
+    <t>45678912</t>
+  </si>
+  <si>
+    <t>ana.torres@ejemplo.com</t>
   </si>
 </sst>
 </file>
@@ -562,9 +577,24 @@
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="B6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="F6" s="2"/>
+      <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
       <c r="B7" s="2"/>
@@ -5542,7 +5572,7 @@
       <formula1>"DNI,RUC,CE"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="Error de rol" error="Por favor seleccione un rol válido: ADMINISTRADOR, DOCENTE, ESTUDIANTE o EMPRESA" promptTitle="Rol" prompt="Seleccione el rol del usuario" sqref="F2:F1000">
-      <formula1>"ADMINISTRADOR,DOCENTE,ESTUDIANTE,EMPRESA"</formula1>
+      <formula1>"ADMINISTRADOR,DOCENTE,ESTUDIANTE,EMPRESA,EGRESADO"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="false" gridLinesSet="true"/>

--- a/public/assets/Importacion de usuarios.xlsx
+++ b/public/assets/Importacion de usuarios.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="28">
   <si>
     <t>NOMBRES</t>
   </si>
@@ -77,19 +77,28 @@
     <t>EMPRESA</t>
   </si>
   <si>
-    <t>944556677</t>
-  </si>
-  <si>
-    <t>EGRESADO</t>
-  </si>
-  <si>
     <t>Ana Torres Quispe</t>
   </si>
   <si>
     <t>45678912</t>
   </si>
   <si>
+    <t>944556677</t>
+  </si>
+  <si>
     <t>ana.torres@ejemplo.com</t>
+  </si>
+  <si>
+    <t>EGRESADO</t>
+  </si>
+  <si>
+    <t>PROGRAMA DE ESTUDIO</t>
+  </si>
+  <si>
+    <t>Administración</t>
+  </si>
+  <si>
+    <t>Ingeniería de Sistemas</t>
   </si>
 </sst>
 </file>
@@ -158,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
     <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
@@ -166,6 +175,10 @@
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="0" numFmtId="49" fillId="0" borderId="0" applyFont="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,7 +478,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:F1000"/>
+  <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="true" style="0"/>
@@ -474,9 +487,10 @@
     <col min="4" max="4" width="15" customWidth="true" style="0"/>
     <col min="5" max="5" width="30" customWidth="true" style="0"/>
     <col min="6" max="6" width="18" customWidth="true" style="0"/>
+    <col min="7" max="7" width="30" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -495,8 +509,11 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -515,8 +532,11 @@
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -535,8 +555,9 @@
       <c r="F3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -555,8 +576,9 @@
       <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -575,4996 +597,5994 @@
       <c r="F5" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
       <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
+      <c r="G6" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:7">
       <c r="B7" s="2"/>
       <c r="D7" s="2"/>
       <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" s="2"/>
       <c r="D8" s="2"/>
       <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9" s="2"/>
       <c r="D9" s="2"/>
       <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10" s="2"/>
       <c r="D10" s="2"/>
       <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6">
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7">
       <c r="B11" s="2"/>
       <c r="D11" s="2"/>
       <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:6">
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12" spans="1:7">
       <c r="B12" s="2"/>
       <c r="D12" s="2"/>
       <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6">
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" spans="1:7">
       <c r="B13" s="2"/>
       <c r="D13" s="2"/>
       <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:6">
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14" spans="1:7">
       <c r="B14" s="2"/>
       <c r="D14" s="2"/>
       <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" spans="1:7">
       <c r="B15" s="2"/>
       <c r="D15" s="2"/>
       <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:6">
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16" spans="1:7">
       <c r="B16" s="2"/>
       <c r="D16" s="2"/>
       <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6">
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7">
       <c r="B17" s="2"/>
       <c r="D17" s="2"/>
       <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="1:6">
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18" spans="1:7">
       <c r="B18" s="2"/>
       <c r="D18" s="2"/>
       <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6">
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" spans="1:7">
       <c r="B19" s="2"/>
       <c r="D19" s="2"/>
       <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="1:6">
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" spans="1:7">
       <c r="B20" s="2"/>
       <c r="D20" s="2"/>
       <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6">
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" spans="1:7">
       <c r="B21" s="2"/>
       <c r="D21" s="2"/>
       <c r="F21" s="2"/>
-    </row>
-    <row r="22" spans="1:6">
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7">
       <c r="B22" s="2"/>
       <c r="D22" s="2"/>
       <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6">
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7">
       <c r="B23" s="2"/>
       <c r="D23" s="2"/>
       <c r="F23" s="2"/>
-    </row>
-    <row r="24" spans="1:6">
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" spans="1:7">
       <c r="B24" s="2"/>
       <c r="D24" s="2"/>
       <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6">
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7">
       <c r="B25" s="2"/>
       <c r="D25" s="2"/>
       <c r="F25" s="2"/>
-    </row>
-    <row r="26" spans="1:6">
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" spans="1:7">
       <c r="B26" s="2"/>
       <c r="D26" s="2"/>
       <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6">
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:7">
       <c r="B27" s="2"/>
       <c r="D27" s="2"/>
       <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="1:6">
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" spans="1:7">
       <c r="B28" s="2"/>
       <c r="D28" s="2"/>
       <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="1:6">
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7">
       <c r="B29" s="2"/>
       <c r="D29" s="2"/>
       <c r="F29" s="2"/>
-    </row>
-    <row r="30" spans="1:6">
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" spans="1:7">
       <c r="B30" s="2"/>
       <c r="D30" s="2"/>
       <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6">
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="1:7">
       <c r="B31" s="2"/>
       <c r="D31" s="2"/>
       <c r="F31" s="2"/>
-    </row>
-    <row r="32" spans="1:6">
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32" spans="1:7">
       <c r="B32" s="2"/>
       <c r="D32" s="2"/>
       <c r="F32" s="2"/>
-    </row>
-    <row r="33" spans="1:6">
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33" spans="1:7">
       <c r="B33" s="2"/>
       <c r="D33" s="2"/>
       <c r="F33" s="2"/>
-    </row>
-    <row r="34" spans="1:6">
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34" spans="1:7">
       <c r="B34" s="2"/>
       <c r="D34" s="2"/>
       <c r="F34" s="2"/>
-    </row>
-    <row r="35" spans="1:6">
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:7">
       <c r="B35" s="2"/>
       <c r="D35" s="2"/>
       <c r="F35" s="2"/>
-    </row>
-    <row r="36" spans="1:6">
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="1:7">
       <c r="B36" s="2"/>
       <c r="D36" s="2"/>
       <c r="F36" s="2"/>
-    </row>
-    <row r="37" spans="1:6">
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7">
       <c r="B37" s="2"/>
       <c r="D37" s="2"/>
       <c r="F37" s="2"/>
-    </row>
-    <row r="38" spans="1:6">
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38" spans="1:7">
       <c r="B38" s="2"/>
       <c r="D38" s="2"/>
       <c r="F38" s="2"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" spans="1:7">
       <c r="B39" s="2"/>
       <c r="D39" s="2"/>
       <c r="F39" s="2"/>
-    </row>
-    <row r="40" spans="1:6">
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40" spans="1:7">
       <c r="B40" s="2"/>
       <c r="D40" s="2"/>
       <c r="F40" s="2"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41" spans="1:7">
       <c r="B41" s="2"/>
       <c r="D41" s="2"/>
       <c r="F41" s="2"/>
-    </row>
-    <row r="42" spans="1:6">
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="1:7">
       <c r="B42" s="2"/>
       <c r="D42" s="2"/>
       <c r="F42" s="2"/>
-    </row>
-    <row r="43" spans="1:6">
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="1:7">
       <c r="B43" s="2"/>
       <c r="D43" s="2"/>
       <c r="F43" s="2"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" spans="1:7">
       <c r="B44" s="2"/>
       <c r="D44" s="2"/>
       <c r="F44" s="2"/>
-    </row>
-    <row r="45" spans="1:6">
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="1:7">
       <c r="B45" s="2"/>
       <c r="D45" s="2"/>
       <c r="F45" s="2"/>
-    </row>
-    <row r="46" spans="1:6">
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" spans="1:7">
       <c r="B46" s="2"/>
       <c r="D46" s="2"/>
       <c r="F46" s="2"/>
-    </row>
-    <row r="47" spans="1:6">
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47" spans="1:7">
       <c r="B47" s="2"/>
       <c r="D47" s="2"/>
       <c r="F47" s="2"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48" spans="1:7">
       <c r="B48" s="2"/>
       <c r="D48" s="2"/>
       <c r="F48" s="2"/>
-    </row>
-    <row r="49" spans="1:6">
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49" spans="1:7">
       <c r="B49" s="2"/>
       <c r="D49" s="2"/>
       <c r="F49" s="2"/>
-    </row>
-    <row r="50" spans="1:6">
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50" spans="1:7">
       <c r="B50" s="2"/>
       <c r="D50" s="2"/>
       <c r="F50" s="2"/>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51" spans="1:7">
       <c r="B51" s="2"/>
       <c r="D51" s="2"/>
       <c r="F51" s="2"/>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52" spans="1:7">
       <c r="B52" s="2"/>
       <c r="D52" s="2"/>
       <c r="F52" s="2"/>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53" spans="1:7">
       <c r="B53" s="2"/>
       <c r="D53" s="2"/>
       <c r="F53" s="2"/>
-    </row>
-    <row r="54" spans="1:6">
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54" spans="1:7">
       <c r="B54" s="2"/>
       <c r="D54" s="2"/>
       <c r="F54" s="2"/>
-    </row>
-    <row r="55" spans="1:6">
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55" spans="1:7">
       <c r="B55" s="2"/>
       <c r="D55" s="2"/>
       <c r="F55" s="2"/>
-    </row>
-    <row r="56" spans="1:6">
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56" spans="1:7">
       <c r="B56" s="2"/>
       <c r="D56" s="2"/>
       <c r="F56" s="2"/>
-    </row>
-    <row r="57" spans="1:6">
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57" spans="1:7">
       <c r="B57" s="2"/>
       <c r="D57" s="2"/>
       <c r="F57" s="2"/>
-    </row>
-    <row r="58" spans="1:6">
+      <c r="G57" s="4"/>
+    </row>
+    <row r="58" spans="1:7">
       <c r="B58" s="2"/>
       <c r="D58" s="2"/>
       <c r="F58" s="2"/>
-    </row>
-    <row r="59" spans="1:6">
+      <c r="G58" s="4"/>
+    </row>
+    <row r="59" spans="1:7">
       <c r="B59" s="2"/>
       <c r="D59" s="2"/>
       <c r="F59" s="2"/>
-    </row>
-    <row r="60" spans="1:6">
+      <c r="G59" s="4"/>
+    </row>
+    <row r="60" spans="1:7">
       <c r="B60" s="2"/>
       <c r="D60" s="2"/>
       <c r="F60" s="2"/>
-    </row>
-    <row r="61" spans="1:6">
+      <c r="G60" s="4"/>
+    </row>
+    <row r="61" spans="1:7">
       <c r="B61" s="2"/>
       <c r="D61" s="2"/>
       <c r="F61" s="2"/>
-    </row>
-    <row r="62" spans="1:6">
+      <c r="G61" s="4"/>
+    </row>
+    <row r="62" spans="1:7">
       <c r="B62" s="2"/>
       <c r="D62" s="2"/>
       <c r="F62" s="2"/>
-    </row>
-    <row r="63" spans="1:6">
+      <c r="G62" s="4"/>
+    </row>
+    <row r="63" spans="1:7">
       <c r="B63" s="2"/>
       <c r="D63" s="2"/>
       <c r="F63" s="2"/>
-    </row>
-    <row r="64" spans="1:6">
+      <c r="G63" s="4"/>
+    </row>
+    <row r="64" spans="1:7">
       <c r="B64" s="2"/>
       <c r="D64" s="2"/>
       <c r="F64" s="2"/>
-    </row>
-    <row r="65" spans="1:6">
+      <c r="G64" s="4"/>
+    </row>
+    <row r="65" spans="1:7">
       <c r="B65" s="2"/>
       <c r="D65" s="2"/>
       <c r="F65" s="2"/>
-    </row>
-    <row r="66" spans="1:6">
+      <c r="G65" s="4"/>
+    </row>
+    <row r="66" spans="1:7">
       <c r="B66" s="2"/>
       <c r="D66" s="2"/>
       <c r="F66" s="2"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="G66" s="4"/>
+    </row>
+    <row r="67" spans="1:7">
       <c r="B67" s="2"/>
       <c r="D67" s="2"/>
       <c r="F67" s="2"/>
-    </row>
-    <row r="68" spans="1:6">
+      <c r="G67" s="4"/>
+    </row>
+    <row r="68" spans="1:7">
       <c r="B68" s="2"/>
       <c r="D68" s="2"/>
       <c r="F68" s="2"/>
-    </row>
-    <row r="69" spans="1:6">
+      <c r="G68" s="4"/>
+    </row>
+    <row r="69" spans="1:7">
       <c r="B69" s="2"/>
       <c r="D69" s="2"/>
       <c r="F69" s="2"/>
-    </row>
-    <row r="70" spans="1:6">
+      <c r="G69" s="4"/>
+    </row>
+    <row r="70" spans="1:7">
       <c r="B70" s="2"/>
       <c r="D70" s="2"/>
       <c r="F70" s="2"/>
-    </row>
-    <row r="71" spans="1:6">
+      <c r="G70" s="4"/>
+    </row>
+    <row r="71" spans="1:7">
       <c r="B71" s="2"/>
       <c r="D71" s="2"/>
       <c r="F71" s="2"/>
-    </row>
-    <row r="72" spans="1:6">
+      <c r="G71" s="4"/>
+    </row>
+    <row r="72" spans="1:7">
       <c r="B72" s="2"/>
       <c r="D72" s="2"/>
       <c r="F72" s="2"/>
-    </row>
-    <row r="73" spans="1:6">
+      <c r="G72" s="4"/>
+    </row>
+    <row r="73" spans="1:7">
       <c r="B73" s="2"/>
       <c r="D73" s="2"/>
       <c r="F73" s="2"/>
-    </row>
-    <row r="74" spans="1:6">
+      <c r="G73" s="4"/>
+    </row>
+    <row r="74" spans="1:7">
       <c r="B74" s="2"/>
       <c r="D74" s="2"/>
       <c r="F74" s="2"/>
-    </row>
-    <row r="75" spans="1:6">
+      <c r="G74" s="4"/>
+    </row>
+    <row r="75" spans="1:7">
       <c r="B75" s="2"/>
       <c r="D75" s="2"/>
       <c r="F75" s="2"/>
-    </row>
-    <row r="76" spans="1:6">
+      <c r="G75" s="4"/>
+    </row>
+    <row r="76" spans="1:7">
       <c r="B76" s="2"/>
       <c r="D76" s="2"/>
       <c r="F76" s="2"/>
-    </row>
-    <row r="77" spans="1:6">
+      <c r="G76" s="4"/>
+    </row>
+    <row r="77" spans="1:7">
       <c r="B77" s="2"/>
       <c r="D77" s="2"/>
       <c r="F77" s="2"/>
-    </row>
-    <row r="78" spans="1:6">
+      <c r="G77" s="4"/>
+    </row>
+    <row r="78" spans="1:7">
       <c r="B78" s="2"/>
       <c r="D78" s="2"/>
       <c r="F78" s="2"/>
-    </row>
-    <row r="79" spans="1:6">
+      <c r="G78" s="4"/>
+    </row>
+    <row r="79" spans="1:7">
       <c r="B79" s="2"/>
       <c r="D79" s="2"/>
       <c r="F79" s="2"/>
-    </row>
-    <row r="80" spans="1:6">
+      <c r="G79" s="4"/>
+    </row>
+    <row r="80" spans="1:7">
       <c r="B80" s="2"/>
       <c r="D80" s="2"/>
       <c r="F80" s="2"/>
-    </row>
-    <row r="81" spans="1:6">
+      <c r="G80" s="4"/>
+    </row>
+    <row r="81" spans="1:7">
       <c r="B81" s="2"/>
       <c r="D81" s="2"/>
       <c r="F81" s="2"/>
-    </row>
-    <row r="82" spans="1:6">
+      <c r="G81" s="4"/>
+    </row>
+    <row r="82" spans="1:7">
       <c r="B82" s="2"/>
       <c r="D82" s="2"/>
       <c r="F82" s="2"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="G82" s="4"/>
+    </row>
+    <row r="83" spans="1:7">
       <c r="B83" s="2"/>
       <c r="D83" s="2"/>
       <c r="F83" s="2"/>
-    </row>
-    <row r="84" spans="1:6">
+      <c r="G83" s="4"/>
+    </row>
+    <row r="84" spans="1:7">
       <c r="B84" s="2"/>
       <c r="D84" s="2"/>
       <c r="F84" s="2"/>
-    </row>
-    <row r="85" spans="1:6">
+      <c r="G84" s="4"/>
+    </row>
+    <row r="85" spans="1:7">
       <c r="B85" s="2"/>
       <c r="D85" s="2"/>
       <c r="F85" s="2"/>
-    </row>
-    <row r="86" spans="1:6">
+      <c r="G85" s="4"/>
+    </row>
+    <row r="86" spans="1:7">
       <c r="B86" s="2"/>
       <c r="D86" s="2"/>
       <c r="F86" s="2"/>
-    </row>
-    <row r="87" spans="1:6">
+      <c r="G86" s="4"/>
+    </row>
+    <row r="87" spans="1:7">
       <c r="B87" s="2"/>
       <c r="D87" s="2"/>
       <c r="F87" s="2"/>
-    </row>
-    <row r="88" spans="1:6">
+      <c r="G87" s="4"/>
+    </row>
+    <row r="88" spans="1:7">
       <c r="B88" s="2"/>
       <c r="D88" s="2"/>
       <c r="F88" s="2"/>
-    </row>
-    <row r="89" spans="1:6">
+      <c r="G88" s="4"/>
+    </row>
+    <row r="89" spans="1:7">
       <c r="B89" s="2"/>
       <c r="D89" s="2"/>
       <c r="F89" s="2"/>
-    </row>
-    <row r="90" spans="1:6">
+      <c r="G89" s="4"/>
+    </row>
+    <row r="90" spans="1:7">
       <c r="B90" s="2"/>
       <c r="D90" s="2"/>
       <c r="F90" s="2"/>
-    </row>
-    <row r="91" spans="1:6">
+      <c r="G90" s="4"/>
+    </row>
+    <row r="91" spans="1:7">
       <c r="B91" s="2"/>
       <c r="D91" s="2"/>
       <c r="F91" s="2"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="G91" s="4"/>
+    </row>
+    <row r="92" spans="1:7">
       <c r="B92" s="2"/>
       <c r="D92" s="2"/>
       <c r="F92" s="2"/>
-    </row>
-    <row r="93" spans="1:6">
+      <c r="G92" s="4"/>
+    </row>
+    <row r="93" spans="1:7">
       <c r="B93" s="2"/>
       <c r="D93" s="2"/>
       <c r="F93" s="2"/>
-    </row>
-    <row r="94" spans="1:6">
+      <c r="G93" s="4"/>
+    </row>
+    <row r="94" spans="1:7">
       <c r="B94" s="2"/>
       <c r="D94" s="2"/>
       <c r="F94" s="2"/>
-    </row>
-    <row r="95" spans="1:6">
+      <c r="G94" s="4"/>
+    </row>
+    <row r="95" spans="1:7">
       <c r="B95" s="2"/>
       <c r="D95" s="2"/>
       <c r="F95" s="2"/>
-    </row>
-    <row r="96" spans="1:6">
+      <c r="G95" s="4"/>
+    </row>
+    <row r="96" spans="1:7">
       <c r="B96" s="2"/>
       <c r="D96" s="2"/>
       <c r="F96" s="2"/>
-    </row>
-    <row r="97" spans="1:6">
+      <c r="G96" s="4"/>
+    </row>
+    <row r="97" spans="1:7">
       <c r="B97" s="2"/>
       <c r="D97" s="2"/>
       <c r="F97" s="2"/>
-    </row>
-    <row r="98" spans="1:6">
+      <c r="G97" s="4"/>
+    </row>
+    <row r="98" spans="1:7">
       <c r="B98" s="2"/>
       <c r="D98" s="2"/>
       <c r="F98" s="2"/>
-    </row>
-    <row r="99" spans="1:6">
+      <c r="G98" s="4"/>
+    </row>
+    <row r="99" spans="1:7">
       <c r="B99" s="2"/>
       <c r="D99" s="2"/>
       <c r="F99" s="2"/>
-    </row>
-    <row r="100" spans="1:6">
+      <c r="G99" s="4"/>
+    </row>
+    <row r="100" spans="1:7">
       <c r="B100" s="2"/>
       <c r="D100" s="2"/>
       <c r="F100" s="2"/>
-    </row>
-    <row r="101" spans="1:6">
+      <c r="G100" s="4"/>
+    </row>
+    <row r="101" spans="1:7">
       <c r="B101" s="2"/>
       <c r="D101" s="2"/>
       <c r="F101" s="2"/>
-    </row>
-    <row r="102" spans="1:6">
+      <c r="G101" s="4"/>
+    </row>
+    <row r="102" spans="1:7">
       <c r="B102" s="2"/>
       <c r="D102" s="2"/>
       <c r="F102" s="2"/>
-    </row>
-    <row r="103" spans="1:6">
+      <c r="G102" s="4"/>
+    </row>
+    <row r="103" spans="1:7">
       <c r="B103" s="2"/>
       <c r="D103" s="2"/>
       <c r="F103" s="2"/>
-    </row>
-    <row r="104" spans="1:6">
+      <c r="G103" s="4"/>
+    </row>
+    <row r="104" spans="1:7">
       <c r="B104" s="2"/>
       <c r="D104" s="2"/>
       <c r="F104" s="2"/>
-    </row>
-    <row r="105" spans="1:6">
+      <c r="G104" s="4"/>
+    </row>
+    <row r="105" spans="1:7">
       <c r="B105" s="2"/>
       <c r="D105" s="2"/>
       <c r="F105" s="2"/>
-    </row>
-    <row r="106" spans="1:6">
+      <c r="G105" s="4"/>
+    </row>
+    <row r="106" spans="1:7">
       <c r="B106" s="2"/>
       <c r="D106" s="2"/>
       <c r="F106" s="2"/>
-    </row>
-    <row r="107" spans="1:6">
+      <c r="G106" s="4"/>
+    </row>
+    <row r="107" spans="1:7">
       <c r="B107" s="2"/>
       <c r="D107" s="2"/>
       <c r="F107" s="2"/>
-    </row>
-    <row r="108" spans="1:6">
+      <c r="G107" s="4"/>
+    </row>
+    <row r="108" spans="1:7">
       <c r="B108" s="2"/>
       <c r="D108" s="2"/>
       <c r="F108" s="2"/>
-    </row>
-    <row r="109" spans="1:6">
+      <c r="G108" s="4"/>
+    </row>
+    <row r="109" spans="1:7">
       <c r="B109" s="2"/>
       <c r="D109" s="2"/>
       <c r="F109" s="2"/>
-    </row>
-    <row r="110" spans="1:6">
+      <c r="G109" s="4"/>
+    </row>
+    <row r="110" spans="1:7">
       <c r="B110" s="2"/>
       <c r="D110" s="2"/>
       <c r="F110" s="2"/>
-    </row>
-    <row r="111" spans="1:6">
+      <c r="G110" s="4"/>
+    </row>
+    <row r="111" spans="1:7">
       <c r="B111" s="2"/>
       <c r="D111" s="2"/>
       <c r="F111" s="2"/>
-    </row>
-    <row r="112" spans="1:6">
+      <c r="G111" s="4"/>
+    </row>
+    <row r="112" spans="1:7">
       <c r="B112" s="2"/>
       <c r="D112" s="2"/>
       <c r="F112" s="2"/>
-    </row>
-    <row r="113" spans="1:6">
+      <c r="G112" s="4"/>
+    </row>
+    <row r="113" spans="1:7">
       <c r="B113" s="2"/>
       <c r="D113" s="2"/>
       <c r="F113" s="2"/>
-    </row>
-    <row r="114" spans="1:6">
+      <c r="G113" s="4"/>
+    </row>
+    <row r="114" spans="1:7">
       <c r="B114" s="2"/>
       <c r="D114" s="2"/>
       <c r="F114" s="2"/>
-    </row>
-    <row r="115" spans="1:6">
+      <c r="G114" s="4"/>
+    </row>
+    <row r="115" spans="1:7">
       <c r="B115" s="2"/>
       <c r="D115" s="2"/>
       <c r="F115" s="2"/>
-    </row>
-    <row r="116" spans="1:6">
+      <c r="G115" s="4"/>
+    </row>
+    <row r="116" spans="1:7">
       <c r="B116" s="2"/>
       <c r="D116" s="2"/>
       <c r="F116" s="2"/>
-    </row>
-    <row r="117" spans="1:6">
+      <c r="G116" s="4"/>
+    </row>
+    <row r="117" spans="1:7">
       <c r="B117" s="2"/>
       <c r="D117" s="2"/>
       <c r="F117" s="2"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="G117" s="4"/>
+    </row>
+    <row r="118" spans="1:7">
       <c r="B118" s="2"/>
       <c r="D118" s="2"/>
       <c r="F118" s="2"/>
-    </row>
-    <row r="119" spans="1:6">
+      <c r="G118" s="4"/>
+    </row>
+    <row r="119" spans="1:7">
       <c r="B119" s="2"/>
       <c r="D119" s="2"/>
       <c r="F119" s="2"/>
-    </row>
-    <row r="120" spans="1:6">
+      <c r="G119" s="4"/>
+    </row>
+    <row r="120" spans="1:7">
       <c r="B120" s="2"/>
       <c r="D120" s="2"/>
       <c r="F120" s="2"/>
-    </row>
-    <row r="121" spans="1:6">
+      <c r="G120" s="4"/>
+    </row>
+    <row r="121" spans="1:7">
       <c r="B121" s="2"/>
       <c r="D121" s="2"/>
       <c r="F121" s="2"/>
-    </row>
-    <row r="122" spans="1:6">
+      <c r="G121" s="4"/>
+    </row>
+    <row r="122" spans="1:7">
       <c r="B122" s="2"/>
       <c r="D122" s="2"/>
       <c r="F122" s="2"/>
-    </row>
-    <row r="123" spans="1:6">
+      <c r="G122" s="4"/>
+    </row>
+    <row r="123" spans="1:7">
       <c r="B123" s="2"/>
       <c r="D123" s="2"/>
       <c r="F123" s="2"/>
-    </row>
-    <row r="124" spans="1:6">
+      <c r="G123" s="4"/>
+    </row>
+    <row r="124" spans="1:7">
       <c r="B124" s="2"/>
       <c r="D124" s="2"/>
       <c r="F124" s="2"/>
-    </row>
-    <row r="125" spans="1:6">
+      <c r="G124" s="4"/>
+    </row>
+    <row r="125" spans="1:7">
       <c r="B125" s="2"/>
       <c r="D125" s="2"/>
       <c r="F125" s="2"/>
-    </row>
-    <row r="126" spans="1:6">
+      <c r="G125" s="4"/>
+    </row>
+    <row r="126" spans="1:7">
       <c r="B126" s="2"/>
       <c r="D126" s="2"/>
       <c r="F126" s="2"/>
-    </row>
-    <row r="127" spans="1:6">
+      <c r="G126" s="4"/>
+    </row>
+    <row r="127" spans="1:7">
       <c r="B127" s="2"/>
       <c r="D127" s="2"/>
       <c r="F127" s="2"/>
-    </row>
-    <row r="128" spans="1:6">
+      <c r="G127" s="4"/>
+    </row>
+    <row r="128" spans="1:7">
       <c r="B128" s="2"/>
       <c r="D128" s="2"/>
       <c r="F128" s="2"/>
-    </row>
-    <row r="129" spans="1:6">
+      <c r="G128" s="4"/>
+    </row>
+    <row r="129" spans="1:7">
       <c r="B129" s="2"/>
       <c r="D129" s="2"/>
       <c r="F129" s="2"/>
-    </row>
-    <row r="130" spans="1:6">
+      <c r="G129" s="4"/>
+    </row>
+    <row r="130" spans="1:7">
       <c r="B130" s="2"/>
       <c r="D130" s="2"/>
       <c r="F130" s="2"/>
-    </row>
-    <row r="131" spans="1:6">
+      <c r="G130" s="4"/>
+    </row>
+    <row r="131" spans="1:7">
       <c r="B131" s="2"/>
       <c r="D131" s="2"/>
       <c r="F131" s="2"/>
-    </row>
-    <row r="132" spans="1:6">
+      <c r="G131" s="4"/>
+    </row>
+    <row r="132" spans="1:7">
       <c r="B132" s="2"/>
       <c r="D132" s="2"/>
       <c r="F132" s="2"/>
-    </row>
-    <row r="133" spans="1:6">
+      <c r="G132" s="4"/>
+    </row>
+    <row r="133" spans="1:7">
       <c r="B133" s="2"/>
       <c r="D133" s="2"/>
       <c r="F133" s="2"/>
-    </row>
-    <row r="134" spans="1:6">
+      <c r="G133" s="4"/>
+    </row>
+    <row r="134" spans="1:7">
       <c r="B134" s="2"/>
       <c r="D134" s="2"/>
       <c r="F134" s="2"/>
-    </row>
-    <row r="135" spans="1:6">
+      <c r="G134" s="4"/>
+    </row>
+    <row r="135" spans="1:7">
       <c r="B135" s="2"/>
       <c r="D135" s="2"/>
       <c r="F135" s="2"/>
-    </row>
-    <row r="136" spans="1:6">
+      <c r="G135" s="4"/>
+    </row>
+    <row r="136" spans="1:7">
       <c r="B136" s="2"/>
       <c r="D136" s="2"/>
       <c r="F136" s="2"/>
-    </row>
-    <row r="137" spans="1:6">
+      <c r="G136" s="4"/>
+    </row>
+    <row r="137" spans="1:7">
       <c r="B137" s="2"/>
       <c r="D137" s="2"/>
       <c r="F137" s="2"/>
-    </row>
-    <row r="138" spans="1:6">
+      <c r="G137" s="4"/>
+    </row>
+    <row r="138" spans="1:7">
       <c r="B138" s="2"/>
       <c r="D138" s="2"/>
       <c r="F138" s="2"/>
-    </row>
-    <row r="139" spans="1:6">
+      <c r="G138" s="4"/>
+    </row>
+    <row r="139" spans="1:7">
       <c r="B139" s="2"/>
       <c r="D139" s="2"/>
       <c r="F139" s="2"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="G139" s="4"/>
+    </row>
+    <row r="140" spans="1:7">
       <c r="B140" s="2"/>
       <c r="D140" s="2"/>
       <c r="F140" s="2"/>
-    </row>
-    <row r="141" spans="1:6">
+      <c r="G140" s="4"/>
+    </row>
+    <row r="141" spans="1:7">
       <c r="B141" s="2"/>
       <c r="D141" s="2"/>
       <c r="F141" s="2"/>
-    </row>
-    <row r="142" spans="1:6">
+      <c r="G141" s="4"/>
+    </row>
+    <row r="142" spans="1:7">
       <c r="B142" s="2"/>
       <c r="D142" s="2"/>
       <c r="F142" s="2"/>
-    </row>
-    <row r="143" spans="1:6">
+      <c r="G142" s="4"/>
+    </row>
+    <row r="143" spans="1:7">
       <c r="B143" s="2"/>
       <c r="D143" s="2"/>
       <c r="F143" s="2"/>
-    </row>
-    <row r="144" spans="1:6">
+      <c r="G143" s="4"/>
+    </row>
+    <row r="144" spans="1:7">
       <c r="B144" s="2"/>
       <c r="D144" s="2"/>
       <c r="F144" s="2"/>
-    </row>
-    <row r="145" spans="1:6">
+      <c r="G144" s="4"/>
+    </row>
+    <row r="145" spans="1:7">
       <c r="B145" s="2"/>
       <c r="D145" s="2"/>
       <c r="F145" s="2"/>
-    </row>
-    <row r="146" spans="1:6">
+      <c r="G145" s="4"/>
+    </row>
+    <row r="146" spans="1:7">
       <c r="B146" s="2"/>
       <c r="D146" s="2"/>
       <c r="F146" s="2"/>
-    </row>
-    <row r="147" spans="1:6">
+      <c r="G146" s="4"/>
+    </row>
+    <row r="147" spans="1:7">
       <c r="B147" s="2"/>
       <c r="D147" s="2"/>
       <c r="F147" s="2"/>
-    </row>
-    <row r="148" spans="1:6">
+      <c r="G147" s="4"/>
+    </row>
+    <row r="148" spans="1:7">
       <c r="B148" s="2"/>
       <c r="D148" s="2"/>
       <c r="F148" s="2"/>
-    </row>
-    <row r="149" spans="1:6">
+      <c r="G148" s="4"/>
+    </row>
+    <row r="149" spans="1:7">
       <c r="B149" s="2"/>
       <c r="D149" s="2"/>
       <c r="F149" s="2"/>
-    </row>
-    <row r="150" spans="1:6">
+      <c r="G149" s="4"/>
+    </row>
+    <row r="150" spans="1:7">
       <c r="B150" s="2"/>
       <c r="D150" s="2"/>
       <c r="F150" s="2"/>
-    </row>
-    <row r="151" spans="1:6">
+      <c r="G150" s="4"/>
+    </row>
+    <row r="151" spans="1:7">
       <c r="B151" s="2"/>
       <c r="D151" s="2"/>
       <c r="F151" s="2"/>
-    </row>
-    <row r="152" spans="1:6">
+      <c r="G151" s="4"/>
+    </row>
+    <row r="152" spans="1:7">
       <c r="B152" s="2"/>
       <c r="D152" s="2"/>
       <c r="F152" s="2"/>
-    </row>
-    <row r="153" spans="1:6">
+      <c r="G152" s="4"/>
+    </row>
+    <row r="153" spans="1:7">
       <c r="B153" s="2"/>
       <c r="D153" s="2"/>
       <c r="F153" s="2"/>
-    </row>
-    <row r="154" spans="1:6">
+      <c r="G153" s="4"/>
+    </row>
+    <row r="154" spans="1:7">
       <c r="B154" s="2"/>
       <c r="D154" s="2"/>
       <c r="F154" s="2"/>
-    </row>
-    <row r="155" spans="1:6">
+      <c r="G154" s="4"/>
+    </row>
+    <row r="155" spans="1:7">
       <c r="B155" s="2"/>
       <c r="D155" s="2"/>
       <c r="F155" s="2"/>
-    </row>
-    <row r="156" spans="1:6">
+      <c r="G155" s="4"/>
+    </row>
+    <row r="156" spans="1:7">
       <c r="B156" s="2"/>
       <c r="D156" s="2"/>
       <c r="F156" s="2"/>
-    </row>
-    <row r="157" spans="1:6">
+      <c r="G156" s="4"/>
+    </row>
+    <row r="157" spans="1:7">
       <c r="B157" s="2"/>
       <c r="D157" s="2"/>
       <c r="F157" s="2"/>
-    </row>
-    <row r="158" spans="1:6">
+      <c r="G157" s="4"/>
+    </row>
+    <row r="158" spans="1:7">
       <c r="B158" s="2"/>
       <c r="D158" s="2"/>
       <c r="F158" s="2"/>
-    </row>
-    <row r="159" spans="1:6">
+      <c r="G158" s="4"/>
+    </row>
+    <row r="159" spans="1:7">
       <c r="B159" s="2"/>
       <c r="D159" s="2"/>
       <c r="F159" s="2"/>
-    </row>
-    <row r="160" spans="1:6">
+      <c r="G159" s="4"/>
+    </row>
+    <row r="160" spans="1:7">
       <c r="B160" s="2"/>
       <c r="D160" s="2"/>
       <c r="F160" s="2"/>
-    </row>
-    <row r="161" spans="1:6">
+      <c r="G160" s="4"/>
+    </row>
+    <row r="161" spans="1:7">
       <c r="B161" s="2"/>
       <c r="D161" s="2"/>
       <c r="F161" s="2"/>
-    </row>
-    <row r="162" spans="1:6">
+      <c r="G161" s="4"/>
+    </row>
+    <row r="162" spans="1:7">
       <c r="B162" s="2"/>
       <c r="D162" s="2"/>
       <c r="F162" s="2"/>
-    </row>
-    <row r="163" spans="1:6">
+      <c r="G162" s="4"/>
+    </row>
+    <row r="163" spans="1:7">
       <c r="B163" s="2"/>
       <c r="D163" s="2"/>
       <c r="F163" s="2"/>
-    </row>
-    <row r="164" spans="1:6">
+      <c r="G163" s="4"/>
+    </row>
+    <row r="164" spans="1:7">
       <c r="B164" s="2"/>
       <c r="D164" s="2"/>
       <c r="F164" s="2"/>
-    </row>
-    <row r="165" spans="1:6">
+      <c r="G164" s="4"/>
+    </row>
+    <row r="165" spans="1:7">
       <c r="B165" s="2"/>
       <c r="D165" s="2"/>
       <c r="F165" s="2"/>
-    </row>
-    <row r="166" spans="1:6">
+      <c r="G165" s="4"/>
+    </row>
+    <row r="166" spans="1:7">
       <c r="B166" s="2"/>
       <c r="D166" s="2"/>
       <c r="F166" s="2"/>
-    </row>
-    <row r="167" spans="1:6">
+      <c r="G166" s="4"/>
+    </row>
+    <row r="167" spans="1:7">
       <c r="B167" s="2"/>
       <c r="D167" s="2"/>
       <c r="F167" s="2"/>
-    </row>
-    <row r="168" spans="1:6">
+      <c r="G167" s="4"/>
+    </row>
+    <row r="168" spans="1:7">
       <c r="B168" s="2"/>
       <c r="D168" s="2"/>
       <c r="F168" s="2"/>
-    </row>
-    <row r="169" spans="1:6">
+      <c r="G168" s="4"/>
+    </row>
+    <row r="169" spans="1:7">
       <c r="B169" s="2"/>
       <c r="D169" s="2"/>
       <c r="F169" s="2"/>
-    </row>
-    <row r="170" spans="1:6">
+      <c r="G169" s="4"/>
+    </row>
+    <row r="170" spans="1:7">
       <c r="B170" s="2"/>
       <c r="D170" s="2"/>
       <c r="F170" s="2"/>
-    </row>
-    <row r="171" spans="1:6">
+      <c r="G170" s="4"/>
+    </row>
+    <row r="171" spans="1:7">
       <c r="B171" s="2"/>
       <c r="D171" s="2"/>
       <c r="F171" s="2"/>
-    </row>
-    <row r="172" spans="1:6">
+      <c r="G171" s="4"/>
+    </row>
+    <row r="172" spans="1:7">
       <c r="B172" s="2"/>
       <c r="D172" s="2"/>
       <c r="F172" s="2"/>
-    </row>
-    <row r="173" spans="1:6">
+      <c r="G172" s="4"/>
+    </row>
+    <row r="173" spans="1:7">
       <c r="B173" s="2"/>
       <c r="D173" s="2"/>
       <c r="F173" s="2"/>
-    </row>
-    <row r="174" spans="1:6">
+      <c r="G173" s="4"/>
+    </row>
+    <row r="174" spans="1:7">
       <c r="B174" s="2"/>
       <c r="D174" s="2"/>
       <c r="F174" s="2"/>
-    </row>
-    <row r="175" spans="1:6">
+      <c r="G174" s="4"/>
+    </row>
+    <row r="175" spans="1:7">
       <c r="B175" s="2"/>
       <c r="D175" s="2"/>
       <c r="F175" s="2"/>
-    </row>
-    <row r="176" spans="1:6">
+      <c r="G175" s="4"/>
+    </row>
+    <row r="176" spans="1:7">
       <c r="B176" s="2"/>
       <c r="D176" s="2"/>
       <c r="F176" s="2"/>
-    </row>
-    <row r="177" spans="1:6">
+      <c r="G176" s="4"/>
+    </row>
+    <row r="177" spans="1:7">
       <c r="B177" s="2"/>
       <c r="D177" s="2"/>
       <c r="F177" s="2"/>
-    </row>
-    <row r="178" spans="1:6">
+      <c r="G177" s="4"/>
+    </row>
+    <row r="178" spans="1:7">
       <c r="B178" s="2"/>
       <c r="D178" s="2"/>
       <c r="F178" s="2"/>
-    </row>
-    <row r="179" spans="1:6">
+      <c r="G178" s="4"/>
+    </row>
+    <row r="179" spans="1:7">
       <c r="B179" s="2"/>
       <c r="D179" s="2"/>
       <c r="F179" s="2"/>
-    </row>
-    <row r="180" spans="1:6">
+      <c r="G179" s="4"/>
+    </row>
+    <row r="180" spans="1:7">
       <c r="B180" s="2"/>
       <c r="D180" s="2"/>
       <c r="F180" s="2"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="G180" s="4"/>
+    </row>
+    <row r="181" spans="1:7">
       <c r="B181" s="2"/>
       <c r="D181" s="2"/>
       <c r="F181" s="2"/>
-    </row>
-    <row r="182" spans="1:6">
+      <c r="G181" s="4"/>
+    </row>
+    <row r="182" spans="1:7">
       <c r="B182" s="2"/>
       <c r="D182" s="2"/>
       <c r="F182" s="2"/>
-    </row>
-    <row r="183" spans="1:6">
+      <c r="G182" s="4"/>
+    </row>
+    <row r="183" spans="1:7">
       <c r="B183" s="2"/>
       <c r="D183" s="2"/>
       <c r="F183" s="2"/>
-    </row>
-    <row r="184" spans="1:6">
+      <c r="G183" s="4"/>
+    </row>
+    <row r="184" spans="1:7">
       <c r="B184" s="2"/>
       <c r="D184" s="2"/>
       <c r="F184" s="2"/>
-    </row>
-    <row r="185" spans="1:6">
+      <c r="G184" s="4"/>
+    </row>
+    <row r="185" spans="1:7">
       <c r="B185" s="2"/>
       <c r="D185" s="2"/>
       <c r="F185" s="2"/>
-    </row>
-    <row r="186" spans="1:6">
+      <c r="G185" s="4"/>
+    </row>
+    <row r="186" spans="1:7">
       <c r="B186" s="2"/>
       <c r="D186" s="2"/>
       <c r="F186" s="2"/>
-    </row>
-    <row r="187" spans="1:6">
+      <c r="G186" s="4"/>
+    </row>
+    <row r="187" spans="1:7">
       <c r="B187" s="2"/>
       <c r="D187" s="2"/>
       <c r="F187" s="2"/>
-    </row>
-    <row r="188" spans="1:6">
+      <c r="G187" s="4"/>
+    </row>
+    <row r="188" spans="1:7">
       <c r="B188" s="2"/>
       <c r="D188" s="2"/>
       <c r="F188" s="2"/>
-    </row>
-    <row r="189" spans="1:6">
+      <c r="G188" s="4"/>
+    </row>
+    <row r="189" spans="1:7">
       <c r="B189" s="2"/>
       <c r="D189" s="2"/>
       <c r="F189" s="2"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="G189" s="4"/>
+    </row>
+    <row r="190" spans="1:7">
       <c r="B190" s="2"/>
       <c r="D190" s="2"/>
       <c r="F190" s="2"/>
-    </row>
-    <row r="191" spans="1:6">
+      <c r="G190" s="4"/>
+    </row>
+    <row r="191" spans="1:7">
       <c r="B191" s="2"/>
       <c r="D191" s="2"/>
       <c r="F191" s="2"/>
-    </row>
-    <row r="192" spans="1:6">
+      <c r="G191" s="4"/>
+    </row>
+    <row r="192" spans="1:7">
       <c r="B192" s="2"/>
       <c r="D192" s="2"/>
       <c r="F192" s="2"/>
-    </row>
-    <row r="193" spans="1:6">
+      <c r="G192" s="4"/>
+    </row>
+    <row r="193" spans="1:7">
       <c r="B193" s="2"/>
       <c r="D193" s="2"/>
       <c r="F193" s="2"/>
-    </row>
-    <row r="194" spans="1:6">
+      <c r="G193" s="4"/>
+    </row>
+    <row r="194" spans="1:7">
       <c r="B194" s="2"/>
       <c r="D194" s="2"/>
       <c r="F194" s="2"/>
-    </row>
-    <row r="195" spans="1:6">
+      <c r="G194" s="4"/>
+    </row>
+    <row r="195" spans="1:7">
       <c r="B195" s="2"/>
       <c r="D195" s="2"/>
       <c r="F195" s="2"/>
-    </row>
-    <row r="196" spans="1:6">
+      <c r="G195" s="4"/>
+    </row>
+    <row r="196" spans="1:7">
       <c r="B196" s="2"/>
       <c r="D196" s="2"/>
       <c r="F196" s="2"/>
-    </row>
-    <row r="197" spans="1:6">
+      <c r="G196" s="4"/>
+    </row>
+    <row r="197" spans="1:7">
       <c r="B197" s="2"/>
       <c r="D197" s="2"/>
       <c r="F197" s="2"/>
-    </row>
-    <row r="198" spans="1:6">
+      <c r="G197" s="4"/>
+    </row>
+    <row r="198" spans="1:7">
       <c r="B198" s="2"/>
       <c r="D198" s="2"/>
       <c r="F198" s="2"/>
-    </row>
-    <row r="199" spans="1:6">
+      <c r="G198" s="4"/>
+    </row>
+    <row r="199" spans="1:7">
       <c r="B199" s="2"/>
       <c r="D199" s="2"/>
       <c r="F199" s="2"/>
-    </row>
-    <row r="200" spans="1:6">
+      <c r="G199" s="4"/>
+    </row>
+    <row r="200" spans="1:7">
       <c r="B200" s="2"/>
       <c r="D200" s="2"/>
       <c r="F200" s="2"/>
-    </row>
-    <row r="201" spans="1:6">
+      <c r="G200" s="4"/>
+    </row>
+    <row r="201" spans="1:7">
       <c r="B201" s="2"/>
       <c r="D201" s="2"/>
       <c r="F201" s="2"/>
-    </row>
-    <row r="202" spans="1:6">
+      <c r="G201" s="4"/>
+    </row>
+    <row r="202" spans="1:7">
       <c r="B202" s="2"/>
       <c r="D202" s="2"/>
       <c r="F202" s="2"/>
-    </row>
-    <row r="203" spans="1:6">
+      <c r="G202" s="4"/>
+    </row>
+    <row r="203" spans="1:7">
       <c r="B203" s="2"/>
       <c r="D203" s="2"/>
       <c r="F203" s="2"/>
-    </row>
-    <row r="204" spans="1:6">
+      <c r="G203" s="4"/>
+    </row>
+    <row r="204" spans="1:7">
       <c r="B204" s="2"/>
       <c r="D204" s="2"/>
       <c r="F204" s="2"/>
-    </row>
-    <row r="205" spans="1:6">
+      <c r="G204" s="4"/>
+    </row>
+    <row r="205" spans="1:7">
       <c r="B205" s="2"/>
       <c r="D205" s="2"/>
       <c r="F205" s="2"/>
-    </row>
-    <row r="206" spans="1:6">
+      <c r="G205" s="4"/>
+    </row>
+    <row r="206" spans="1:7">
       <c r="B206" s="2"/>
       <c r="D206" s="2"/>
       <c r="F206" s="2"/>
-    </row>
-    <row r="207" spans="1:6">
+      <c r="G206" s="4"/>
+    </row>
+    <row r="207" spans="1:7">
       <c r="B207" s="2"/>
       <c r="D207" s="2"/>
       <c r="F207" s="2"/>
-    </row>
-    <row r="208" spans="1:6">
+      <c r="G207" s="4"/>
+    </row>
+    <row r="208" spans="1:7">
       <c r="B208" s="2"/>
       <c r="D208" s="2"/>
       <c r="F208" s="2"/>
-    </row>
-    <row r="209" spans="1:6">
+      <c r="G208" s="4"/>
+    </row>
+    <row r="209" spans="1:7">
       <c r="B209" s="2"/>
       <c r="D209" s="2"/>
       <c r="F209" s="2"/>
-    </row>
-    <row r="210" spans="1:6">
+      <c r="G209" s="4"/>
+    </row>
+    <row r="210" spans="1:7">
       <c r="B210" s="2"/>
       <c r="D210" s="2"/>
       <c r="F210" s="2"/>
-    </row>
-    <row r="211" spans="1:6">
+      <c r="G210" s="4"/>
+    </row>
+    <row r="211" spans="1:7">
       <c r="B211" s="2"/>
       <c r="D211" s="2"/>
       <c r="F211" s="2"/>
-    </row>
-    <row r="212" spans="1:6">
+      <c r="G211" s="4"/>
+    </row>
+    <row r="212" spans="1:7">
       <c r="B212" s="2"/>
       <c r="D212" s="2"/>
       <c r="F212" s="2"/>
-    </row>
-    <row r="213" spans="1:6">
+      <c r="G212" s="4"/>
+    </row>
+    <row r="213" spans="1:7">
       <c r="B213" s="2"/>
       <c r="D213" s="2"/>
       <c r="F213" s="2"/>
-    </row>
-    <row r="214" spans="1:6">
+      <c r="G213" s="4"/>
+    </row>
+    <row r="214" spans="1:7">
       <c r="B214" s="2"/>
       <c r="D214" s="2"/>
       <c r="F214" s="2"/>
-    </row>
-    <row r="215" spans="1:6">
+      <c r="G214" s="4"/>
+    </row>
+    <row r="215" spans="1:7">
       <c r="B215" s="2"/>
       <c r="D215" s="2"/>
       <c r="F215" s="2"/>
-    </row>
-    <row r="216" spans="1:6">
+      <c r="G215" s="4"/>
+    </row>
+    <row r="216" spans="1:7">
       <c r="B216" s="2"/>
       <c r="D216" s="2"/>
       <c r="F216" s="2"/>
-    </row>
-    <row r="217" spans="1:6">
+      <c r="G216" s="4"/>
+    </row>
+    <row r="217" spans="1:7">
       <c r="B217" s="2"/>
       <c r="D217" s="2"/>
       <c r="F217" s="2"/>
-    </row>
-    <row r="218" spans="1:6">
+      <c r="G217" s="4"/>
+    </row>
+    <row r="218" spans="1:7">
       <c r="B218" s="2"/>
       <c r="D218" s="2"/>
       <c r="F218" s="2"/>
-    </row>
-    <row r="219" spans="1:6">
+      <c r="G218" s="4"/>
+    </row>
+    <row r="219" spans="1:7">
       <c r="B219" s="2"/>
       <c r="D219" s="2"/>
       <c r="F219" s="2"/>
-    </row>
-    <row r="220" spans="1:6">
+      <c r="G219" s="4"/>
+    </row>
+    <row r="220" spans="1:7">
       <c r="B220" s="2"/>
       <c r="D220" s="2"/>
       <c r="F220" s="2"/>
-    </row>
-    <row r="221" spans="1:6">
+      <c r="G220" s="4"/>
+    </row>
+    <row r="221" spans="1:7">
       <c r="B221" s="2"/>
       <c r="D221" s="2"/>
       <c r="F221" s="2"/>
-    </row>
-    <row r="222" spans="1:6">
+      <c r="G221" s="4"/>
+    </row>
+    <row r="222" spans="1:7">
       <c r="B222" s="2"/>
       <c r="D222" s="2"/>
       <c r="F222" s="2"/>
-    </row>
-    <row r="223" spans="1:6">
+      <c r="G222" s="4"/>
+    </row>
+    <row r="223" spans="1:7">
       <c r="B223" s="2"/>
       <c r="D223" s="2"/>
       <c r="F223" s="2"/>
-    </row>
-    <row r="224" spans="1:6">
+      <c r="G223" s="4"/>
+    </row>
+    <row r="224" spans="1:7">
       <c r="B224" s="2"/>
       <c r="D224" s="2"/>
       <c r="F224" s="2"/>
-    </row>
-    <row r="225" spans="1:6">
+      <c r="G224" s="4"/>
+    </row>
+    <row r="225" spans="1:7">
       <c r="B225" s="2"/>
       <c r="D225" s="2"/>
       <c r="F225" s="2"/>
-    </row>
-    <row r="226" spans="1:6">
+      <c r="G225" s="4"/>
+    </row>
+    <row r="226" spans="1:7">
       <c r="B226" s="2"/>
       <c r="D226" s="2"/>
       <c r="F226" s="2"/>
-    </row>
-    <row r="227" spans="1:6">
+      <c r="G226" s="4"/>
+    </row>
+    <row r="227" spans="1:7">
       <c r="B227" s="2"/>
       <c r="D227" s="2"/>
       <c r="F227" s="2"/>
-    </row>
-    <row r="228" spans="1:6">
+      <c r="G227" s="4"/>
+    </row>
+    <row r="228" spans="1:7">
       <c r="B228" s="2"/>
       <c r="D228" s="2"/>
       <c r="F228" s="2"/>
-    </row>
-    <row r="229" spans="1:6">
+      <c r="G228" s="4"/>
+    </row>
+    <row r="229" spans="1:7">
       <c r="B229" s="2"/>
       <c r="D229" s="2"/>
       <c r="F229" s="2"/>
-    </row>
-    <row r="230" spans="1:6">
+      <c r="G229" s="4"/>
+    </row>
+    <row r="230" spans="1:7">
       <c r="B230" s="2"/>
       <c r="D230" s="2"/>
       <c r="F230" s="2"/>
-    </row>
-    <row r="231" spans="1:6">
+      <c r="G230" s="4"/>
+    </row>
+    <row r="231" spans="1:7">
       <c r="B231" s="2"/>
       <c r="D231" s="2"/>
       <c r="F231" s="2"/>
-    </row>
-    <row r="232" spans="1:6">
+      <c r="G231" s="4"/>
+    </row>
+    <row r="232" spans="1:7">
       <c r="B232" s="2"/>
       <c r="D232" s="2"/>
       <c r="F232" s="2"/>
-    </row>
-    <row r="233" spans="1:6">
+      <c r="G232" s="4"/>
+    </row>
+    <row r="233" spans="1:7">
       <c r="B233" s="2"/>
       <c r="D233" s="2"/>
       <c r="F233" s="2"/>
-    </row>
-    <row r="234" spans="1:6">
+      <c r="G233" s="4"/>
+    </row>
+    <row r="234" spans="1:7">
       <c r="B234" s="2"/>
       <c r="D234" s="2"/>
       <c r="F234" s="2"/>
-    </row>
-    <row r="235" spans="1:6">
+      <c r="G234" s="4"/>
+    </row>
+    <row r="235" spans="1:7">
       <c r="B235" s="2"/>
       <c r="D235" s="2"/>
       <c r="F235" s="2"/>
-    </row>
-    <row r="236" spans="1:6">
+      <c r="G235" s="4"/>
+    </row>
+    <row r="236" spans="1:7">
       <c r="B236" s="2"/>
       <c r="D236" s="2"/>
       <c r="F236" s="2"/>
-    </row>
-    <row r="237" spans="1:6">
+      <c r="G236" s="4"/>
+    </row>
+    <row r="237" spans="1:7">
       <c r="B237" s="2"/>
       <c r="D237" s="2"/>
       <c r="F237" s="2"/>
-    </row>
-    <row r="238" spans="1:6">
+      <c r="G237" s="4"/>
+    </row>
+    <row r="238" spans="1:7">
       <c r="B238" s="2"/>
       <c r="D238" s="2"/>
       <c r="F238" s="2"/>
-    </row>
-    <row r="239" spans="1:6">
+      <c r="G238" s="4"/>
+    </row>
+    <row r="239" spans="1:7">
       <c r="B239" s="2"/>
       <c r="D239" s="2"/>
       <c r="F239" s="2"/>
-    </row>
-    <row r="240" spans="1:6">
+      <c r="G239" s="4"/>
+    </row>
+    <row r="240" spans="1:7">
       <c r="B240" s="2"/>
       <c r="D240" s="2"/>
       <c r="F240" s="2"/>
-    </row>
-    <row r="241" spans="1:6">
+      <c r="G240" s="4"/>
+    </row>
+    <row r="241" spans="1:7">
       <c r="B241" s="2"/>
       <c r="D241" s="2"/>
       <c r="F241" s="2"/>
-    </row>
-    <row r="242" spans="1:6">
+      <c r="G241" s="4"/>
+    </row>
+    <row r="242" spans="1:7">
       <c r="B242" s="2"/>
       <c r="D242" s="2"/>
       <c r="F242" s="2"/>
-    </row>
-    <row r="243" spans="1:6">
+      <c r="G242" s="4"/>
+    </row>
+    <row r="243" spans="1:7">
       <c r="B243" s="2"/>
       <c r="D243" s="2"/>
       <c r="F243" s="2"/>
-    </row>
-    <row r="244" spans="1:6">
+      <c r="G243" s="4"/>
+    </row>
+    <row r="244" spans="1:7">
       <c r="B244" s="2"/>
       <c r="D244" s="2"/>
       <c r="F244" s="2"/>
-    </row>
-    <row r="245" spans="1:6">
+      <c r="G244" s="4"/>
+    </row>
+    <row r="245" spans="1:7">
       <c r="B245" s="2"/>
       <c r="D245" s="2"/>
       <c r="F245" s="2"/>
-    </row>
-    <row r="246" spans="1:6">
+      <c r="G245" s="4"/>
+    </row>
+    <row r="246" spans="1:7">
       <c r="B246" s="2"/>
       <c r="D246" s="2"/>
       <c r="F246" s="2"/>
-    </row>
-    <row r="247" spans="1:6">
+      <c r="G246" s="4"/>
+    </row>
+    <row r="247" spans="1:7">
       <c r="B247" s="2"/>
       <c r="D247" s="2"/>
       <c r="F247" s="2"/>
-    </row>
-    <row r="248" spans="1:6">
+      <c r="G247" s="4"/>
+    </row>
+    <row r="248" spans="1:7">
       <c r="B248" s="2"/>
       <c r="D248" s="2"/>
       <c r="F248" s="2"/>
-    </row>
-    <row r="249" spans="1:6">
+      <c r="G248" s="4"/>
+    </row>
+    <row r="249" spans="1:7">
       <c r="B249" s="2"/>
       <c r="D249" s="2"/>
       <c r="F249" s="2"/>
-    </row>
-    <row r="250" spans="1:6">
+      <c r="G249" s="4"/>
+    </row>
+    <row r="250" spans="1:7">
       <c r="B250" s="2"/>
       <c r="D250" s="2"/>
       <c r="F250" s="2"/>
-    </row>
-    <row r="251" spans="1:6">
+      <c r="G250" s="4"/>
+    </row>
+    <row r="251" spans="1:7">
       <c r="B251" s="2"/>
       <c r="D251" s="2"/>
       <c r="F251" s="2"/>
-    </row>
-    <row r="252" spans="1:6">
+      <c r="G251" s="4"/>
+    </row>
+    <row r="252" spans="1:7">
       <c r="B252" s="2"/>
       <c r="D252" s="2"/>
       <c r="F252" s="2"/>
-    </row>
-    <row r="253" spans="1:6">
+      <c r="G252" s="4"/>
+    </row>
+    <row r="253" spans="1:7">
       <c r="B253" s="2"/>
       <c r="D253" s="2"/>
       <c r="F253" s="2"/>
-    </row>
-    <row r="254" spans="1:6">
+      <c r="G253" s="4"/>
+    </row>
+    <row r="254" spans="1:7">
       <c r="B254" s="2"/>
       <c r="D254" s="2"/>
       <c r="F254" s="2"/>
-    </row>
-    <row r="255" spans="1:6">
+      <c r="G254" s="4"/>
+    </row>
+    <row r="255" spans="1:7">
       <c r="B255" s="2"/>
       <c r="D255" s="2"/>
       <c r="F255" s="2"/>
-    </row>
-    <row r="256" spans="1:6">
+      <c r="G255" s="4"/>
+    </row>
+    <row r="256" spans="1:7">
       <c r="B256" s="2"/>
       <c r="D256" s="2"/>
       <c r="F256" s="2"/>
-    </row>
-    <row r="257" spans="1:6">
+      <c r="G256" s="4"/>
+    </row>
+    <row r="257" spans="1:7">
       <c r="B257" s="2"/>
       <c r="D257" s="2"/>
       <c r="F257" s="2"/>
-    </row>
-    <row r="258" spans="1:6">
+      <c r="G257" s="4"/>
+    </row>
+    <row r="258" spans="1:7">
       <c r="B258" s="2"/>
       <c r="D258" s="2"/>
       <c r="F258" s="2"/>
-    </row>
-    <row r="259" spans="1:6">
+      <c r="G258" s="4"/>
+    </row>
+    <row r="259" spans="1:7">
       <c r="B259" s="2"/>
       <c r="D259" s="2"/>
       <c r="F259" s="2"/>
-    </row>
-    <row r="260" spans="1:6">
+      <c r="G259" s="4"/>
+    </row>
+    <row r="260" spans="1:7">
       <c r="B260" s="2"/>
       <c r="D260" s="2"/>
       <c r="F260" s="2"/>
-    </row>
-    <row r="261" spans="1:6">
+      <c r="G260" s="4"/>
+    </row>
+    <row r="261" spans="1:7">
       <c r="B261" s="2"/>
       <c r="D261" s="2"/>
       <c r="F261" s="2"/>
-    </row>
-    <row r="262" spans="1:6">
+      <c r="G261" s="4"/>
+    </row>
+    <row r="262" spans="1:7">
       <c r="B262" s="2"/>
       <c r="D262" s="2"/>
       <c r="F262" s="2"/>
-    </row>
-    <row r="263" spans="1:6">
+      <c r="G262" s="4"/>
+    </row>
+    <row r="263" spans="1:7">
       <c r="B263" s="2"/>
       <c r="D263" s="2"/>
       <c r="F263" s="2"/>
-    </row>
-    <row r="264" spans="1:6">
+      <c r="G263" s="4"/>
+    </row>
+    <row r="264" spans="1:7">
       <c r="B264" s="2"/>
       <c r="D264" s="2"/>
       <c r="F264" s="2"/>
-    </row>
-    <row r="265" spans="1:6">
+      <c r="G264" s="4"/>
+    </row>
+    <row r="265" spans="1:7">
       <c r="B265" s="2"/>
       <c r="D265" s="2"/>
       <c r="F265" s="2"/>
-    </row>
-    <row r="266" spans="1:6">
+      <c r="G265" s="4"/>
+    </row>
+    <row r="266" spans="1:7">
       <c r="B266" s="2"/>
       <c r="D266" s="2"/>
       <c r="F266" s="2"/>
-    </row>
-    <row r="267" spans="1:6">
+      <c r="G266" s="4"/>
+    </row>
+    <row r="267" spans="1:7">
       <c r="B267" s="2"/>
       <c r="D267" s="2"/>
       <c r="F267" s="2"/>
-    </row>
-    <row r="268" spans="1:6">
+      <c r="G267" s="4"/>
+    </row>
+    <row r="268" spans="1:7">
       <c r="B268" s="2"/>
       <c r="D268" s="2"/>
       <c r="F268" s="2"/>
-    </row>
-    <row r="269" spans="1:6">
+      <c r="G268" s="4"/>
+    </row>
+    <row r="269" spans="1:7">
       <c r="B269" s="2"/>
       <c r="D269" s="2"/>
       <c r="F269" s="2"/>
-    </row>
-    <row r="270" spans="1:6">
+      <c r="G269" s="4"/>
+    </row>
+    <row r="270" spans="1:7">
       <c r="B270" s="2"/>
       <c r="D270" s="2"/>
       <c r="F270" s="2"/>
-    </row>
-    <row r="271" spans="1:6">
+      <c r="G270" s="4"/>
+    </row>
+    <row r="271" spans="1:7">
       <c r="B271" s="2"/>
       <c r="D271" s="2"/>
       <c r="F271" s="2"/>
-    </row>
-    <row r="272" spans="1:6">
+      <c r="G271" s="4"/>
+    </row>
+    <row r="272" spans="1:7">
       <c r="B272" s="2"/>
       <c r="D272" s="2"/>
       <c r="F272" s="2"/>
-    </row>
-    <row r="273" spans="1:6">
+      <c r="G272" s="4"/>
+    </row>
+    <row r="273" spans="1:7">
       <c r="B273" s="2"/>
       <c r="D273" s="2"/>
       <c r="F273" s="2"/>
-    </row>
-    <row r="274" spans="1:6">
+      <c r="G273" s="4"/>
+    </row>
+    <row r="274" spans="1:7">
       <c r="B274" s="2"/>
       <c r="D274" s="2"/>
       <c r="F274" s="2"/>
-    </row>
-    <row r="275" spans="1:6">
+      <c r="G274" s="4"/>
+    </row>
+    <row r="275" spans="1:7">
       <c r="B275" s="2"/>
       <c r="D275" s="2"/>
       <c r="F275" s="2"/>
-    </row>
-    <row r="276" spans="1:6">
+      <c r="G275" s="4"/>
+    </row>
+    <row r="276" spans="1:7">
       <c r="B276" s="2"/>
       <c r="D276" s="2"/>
       <c r="F276" s="2"/>
-    </row>
-    <row r="277" spans="1:6">
+      <c r="G276" s="4"/>
+    </row>
+    <row r="277" spans="1:7">
       <c r="B277" s="2"/>
       <c r="D277" s="2"/>
       <c r="F277" s="2"/>
-    </row>
-    <row r="278" spans="1:6">
+      <c r="G277" s="4"/>
+    </row>
+    <row r="278" spans="1:7">
       <c r="B278" s="2"/>
       <c r="D278" s="2"/>
       <c r="F278" s="2"/>
-    </row>
-    <row r="279" spans="1:6">
+      <c r="G278" s="4"/>
+    </row>
+    <row r="279" spans="1:7">
       <c r="B279" s="2"/>
       <c r="D279" s="2"/>
       <c r="F279" s="2"/>
-    </row>
-    <row r="280" spans="1:6">
+      <c r="G279" s="4"/>
+    </row>
+    <row r="280" spans="1:7">
       <c r="B280" s="2"/>
       <c r="D280" s="2"/>
       <c r="F280" s="2"/>
-    </row>
-    <row r="281" spans="1:6">
+      <c r="G280" s="4"/>
+    </row>
+    <row r="281" spans="1:7">
       <c r="B281" s="2"/>
       <c r="D281" s="2"/>
       <c r="F281" s="2"/>
-    </row>
-    <row r="282" spans="1:6">
+      <c r="G281" s="4"/>
+    </row>
+    <row r="282" spans="1:7">
       <c r="B282" s="2"/>
       <c r="D282" s="2"/>
       <c r="F282" s="2"/>
-    </row>
-    <row r="283" spans="1:6">
+      <c r="G282" s="4"/>
+    </row>
+    <row r="283" spans="1:7">
       <c r="B283" s="2"/>
       <c r="D283" s="2"/>
       <c r="F283" s="2"/>
-    </row>
-    <row r="284" spans="1:6">
+      <c r="G283" s="4"/>
+    </row>
+    <row r="284" spans="1:7">
       <c r="B284" s="2"/>
       <c r="D284" s="2"/>
       <c r="F284" s="2"/>
-    </row>
-    <row r="285" spans="1:6">
+      <c r="G284" s="4"/>
+    </row>
+    <row r="285" spans="1:7">
       <c r="B285" s="2"/>
       <c r="D285" s="2"/>
       <c r="F285" s="2"/>
-    </row>
-    <row r="286" spans="1:6">
+      <c r="G285" s="4"/>
+    </row>
+    <row r="286" spans="1:7">
       <c r="B286" s="2"/>
       <c r="D286" s="2"/>
       <c r="F286" s="2"/>
-    </row>
-    <row r="287" spans="1:6">
+      <c r="G286" s="4"/>
+    </row>
+    <row r="287" spans="1:7">
       <c r="B287" s="2"/>
       <c r="D287" s="2"/>
       <c r="F287" s="2"/>
-    </row>
-    <row r="288" spans="1:6">
+      <c r="G287" s="4"/>
+    </row>
+    <row r="288" spans="1:7">
       <c r="B288" s="2"/>
       <c r="D288" s="2"/>
       <c r="F288" s="2"/>
-    </row>
-    <row r="289" spans="1:6">
+      <c r="G288" s="4"/>
+    </row>
+    <row r="289" spans="1:7">
       <c r="B289" s="2"/>
       <c r="D289" s="2"/>
       <c r="F289" s="2"/>
-    </row>
-    <row r="290" spans="1:6">
+      <c r="G289" s="4"/>
+    </row>
+    <row r="290" spans="1:7">
       <c r="B290" s="2"/>
       <c r="D290" s="2"/>
       <c r="F290" s="2"/>
-    </row>
-    <row r="291" spans="1:6">
+      <c r="G290" s="4"/>
+    </row>
+    <row r="291" spans="1:7">
       <c r="B291" s="2"/>
       <c r="D291" s="2"/>
       <c r="F291" s="2"/>
-    </row>
-    <row r="292" spans="1:6">
+      <c r="G291" s="4"/>
+    </row>
+    <row r="292" spans="1:7">
       <c r="B292" s="2"/>
       <c r="D292" s="2"/>
       <c r="F292" s="2"/>
-    </row>
-    <row r="293" spans="1:6">
+      <c r="G292" s="4"/>
+    </row>
+    <row r="293" spans="1:7">
       <c r="B293" s="2"/>
       <c r="D293" s="2"/>
       <c r="F293" s="2"/>
-    </row>
-    <row r="294" spans="1:6">
+      <c r="G293" s="4"/>
+    </row>
+    <row r="294" spans="1:7">
       <c r="B294" s="2"/>
       <c r="D294" s="2"/>
       <c r="F294" s="2"/>
-    </row>
-    <row r="295" spans="1:6">
+      <c r="G294" s="4"/>
+    </row>
+    <row r="295" spans="1:7">
       <c r="B295" s="2"/>
       <c r="D295" s="2"/>
       <c r="F295" s="2"/>
-    </row>
-    <row r="296" spans="1:6">
+      <c r="G295" s="4"/>
+    </row>
+    <row r="296" spans="1:7">
       <c r="B296" s="2"/>
       <c r="D296" s="2"/>
       <c r="F296" s="2"/>
-    </row>
-    <row r="297" spans="1:6">
+      <c r="G296" s="4"/>
+    </row>
+    <row r="297" spans="1:7">
       <c r="B297" s="2"/>
       <c r="D297" s="2"/>
       <c r="F297" s="2"/>
-    </row>
-    <row r="298" spans="1:6">
+      <c r="G297" s="4"/>
+    </row>
+    <row r="298" spans="1:7">
       <c r="B298" s="2"/>
       <c r="D298" s="2"/>
       <c r="F298" s="2"/>
-    </row>
-    <row r="299" spans="1:6">
+      <c r="G298" s="4"/>
+    </row>
+    <row r="299" spans="1:7">
       <c r="B299" s="2"/>
       <c r="D299" s="2"/>
       <c r="F299" s="2"/>
-    </row>
-    <row r="300" spans="1:6">
+      <c r="G299" s="4"/>
+    </row>
+    <row r="300" spans="1:7">
       <c r="B300" s="2"/>
       <c r="D300" s="2"/>
       <c r="F300" s="2"/>
-    </row>
-    <row r="301" spans="1:6">
+      <c r="G300" s="4"/>
+    </row>
+    <row r="301" spans="1:7">
       <c r="B301" s="2"/>
       <c r="D301" s="2"/>
       <c r="F301" s="2"/>
-    </row>
-    <row r="302" spans="1:6">
+      <c r="G301" s="4"/>
+    </row>
+    <row r="302" spans="1:7">
       <c r="B302" s="2"/>
       <c r="D302" s="2"/>
       <c r="F302" s="2"/>
-    </row>
-    <row r="303" spans="1:6">
+      <c r="G302" s="4"/>
+    </row>
+    <row r="303" spans="1:7">
       <c r="B303" s="2"/>
       <c r="D303" s="2"/>
       <c r="F303" s="2"/>
-    </row>
-    <row r="304" spans="1:6">
+      <c r="G303" s="4"/>
+    </row>
+    <row r="304" spans="1:7">
       <c r="B304" s="2"/>
       <c r="D304" s="2"/>
       <c r="F304" s="2"/>
-    </row>
-    <row r="305" spans="1:6">
+      <c r="G304" s="4"/>
+    </row>
+    <row r="305" spans="1:7">
       <c r="B305" s="2"/>
       <c r="D305" s="2"/>
       <c r="F305" s="2"/>
-    </row>
-    <row r="306" spans="1:6">
+      <c r="G305" s="4"/>
+    </row>
+    <row r="306" spans="1:7">
       <c r="B306" s="2"/>
       <c r="D306" s="2"/>
       <c r="F306" s="2"/>
-    </row>
-    <row r="307" spans="1:6">
+      <c r="G306" s="4"/>
+    </row>
+    <row r="307" spans="1:7">
       <c r="B307" s="2"/>
       <c r="D307" s="2"/>
       <c r="F307" s="2"/>
-    </row>
-    <row r="308" spans="1:6">
+      <c r="G307" s="4"/>
+    </row>
+    <row r="308" spans="1:7">
       <c r="B308" s="2"/>
       <c r="D308" s="2"/>
       <c r="F308" s="2"/>
-    </row>
-    <row r="309" spans="1:6">
+      <c r="G308" s="4"/>
+    </row>
+    <row r="309" spans="1:7">
       <c r="B309" s="2"/>
       <c r="D309" s="2"/>
       <c r="F309" s="2"/>
-    </row>
-    <row r="310" spans="1:6">
+      <c r="G309" s="4"/>
+    </row>
+    <row r="310" spans="1:7">
       <c r="B310" s="2"/>
       <c r="D310" s="2"/>
       <c r="F310" s="2"/>
-    </row>
-    <row r="311" spans="1:6">
+      <c r="G310" s="4"/>
+    </row>
+    <row r="311" spans="1:7">
       <c r="B311" s="2"/>
       <c r="D311" s="2"/>
       <c r="F311" s="2"/>
-    </row>
-    <row r="312" spans="1:6">
+      <c r="G311" s="4"/>
+    </row>
+    <row r="312" spans="1:7">
       <c r="B312" s="2"/>
       <c r="D312" s="2"/>
       <c r="F312" s="2"/>
-    </row>
-    <row r="313" spans="1:6">
+      <c r="G312" s="4"/>
+    </row>
+    <row r="313" spans="1:7">
       <c r="B313" s="2"/>
       <c r="D313" s="2"/>
       <c r="F313" s="2"/>
-    </row>
-    <row r="314" spans="1:6">
+      <c r="G313" s="4"/>
+    </row>
+    <row r="314" spans="1:7">
       <c r="B314" s="2"/>
       <c r="D314" s="2"/>
       <c r="F314" s="2"/>
-    </row>
-    <row r="315" spans="1:6">
+      <c r="G314" s="4"/>
+    </row>
+    <row r="315" spans="1:7">
       <c r="B315" s="2"/>
       <c r="D315" s="2"/>
       <c r="F315" s="2"/>
-    </row>
-    <row r="316" spans="1:6">
+      <c r="G315" s="4"/>
+    </row>
+    <row r="316" spans="1:7">
       <c r="B316" s="2"/>
       <c r="D316" s="2"/>
       <c r="F316" s="2"/>
-    </row>
-    <row r="317" spans="1:6">
+      <c r="G316" s="4"/>
+    </row>
+    <row r="317" spans="1:7">
       <c r="B317" s="2"/>
       <c r="D317" s="2"/>
       <c r="F317" s="2"/>
-    </row>
-    <row r="318" spans="1:6">
+      <c r="G317" s="4"/>
+    </row>
+    <row r="318" spans="1:7">
       <c r="B318" s="2"/>
       <c r="D318" s="2"/>
       <c r="F318" s="2"/>
-    </row>
-    <row r="319" spans="1:6">
+      <c r="G318" s="4"/>
+    </row>
+    <row r="319" spans="1:7">
       <c r="B319" s="2"/>
       <c r="D319" s="2"/>
       <c r="F319" s="2"/>
-    </row>
-    <row r="320" spans="1:6">
+      <c r="G319" s="4"/>
+    </row>
+    <row r="320" spans="1:7">
       <c r="B320" s="2"/>
       <c r="D320" s="2"/>
       <c r="F320" s="2"/>
-    </row>
-    <row r="321" spans="1:6">
+      <c r="G320" s="4"/>
+    </row>
+    <row r="321" spans="1:7">
       <c r="B321" s="2"/>
       <c r="D321" s="2"/>
       <c r="F321" s="2"/>
-    </row>
-    <row r="322" spans="1:6">
+      <c r="G321" s="4"/>
+    </row>
+    <row r="322" spans="1:7">
       <c r="B322" s="2"/>
       <c r="D322" s="2"/>
       <c r="F322" s="2"/>
-    </row>
-    <row r="323" spans="1:6">
+      <c r="G322" s="4"/>
+    </row>
+    <row r="323" spans="1:7">
       <c r="B323" s="2"/>
       <c r="D323" s="2"/>
       <c r="F323" s="2"/>
-    </row>
-    <row r="324" spans="1:6">
+      <c r="G323" s="4"/>
+    </row>
+    <row r="324" spans="1:7">
       <c r="B324" s="2"/>
       <c r="D324" s="2"/>
       <c r="F324" s="2"/>
-    </row>
-    <row r="325" spans="1:6">
+      <c r="G324" s="4"/>
+    </row>
+    <row r="325" spans="1:7">
       <c r="B325" s="2"/>
       <c r="D325" s="2"/>
       <c r="F325" s="2"/>
-    </row>
-    <row r="326" spans="1:6">
+      <c r="G325" s="4"/>
+    </row>
+    <row r="326" spans="1:7">
       <c r="B326" s="2"/>
       <c r="D326" s="2"/>
       <c r="F326" s="2"/>
-    </row>
-    <row r="327" spans="1:6">
+      <c r="G326" s="4"/>
+    </row>
+    <row r="327" spans="1:7">
       <c r="B327" s="2"/>
       <c r="D327" s="2"/>
       <c r="F327" s="2"/>
-    </row>
-    <row r="328" spans="1:6">
+      <c r="G327" s="4"/>
+    </row>
+    <row r="328" spans="1:7">
       <c r="B328" s="2"/>
       <c r="D328" s="2"/>
       <c r="F328" s="2"/>
-    </row>
-    <row r="329" spans="1:6">
+      <c r="G328" s="4"/>
+    </row>
+    <row r="329" spans="1:7">
       <c r="B329" s="2"/>
       <c r="D329" s="2"/>
       <c r="F329" s="2"/>
-    </row>
-    <row r="330" spans="1:6">
+      <c r="G329" s="4"/>
+    </row>
+    <row r="330" spans="1:7">
       <c r="B330" s="2"/>
       <c r="D330" s="2"/>
       <c r="F330" s="2"/>
-    </row>
-    <row r="331" spans="1:6">
+      <c r="G330" s="4"/>
+    </row>
+    <row r="331" spans="1:7">
       <c r="B331" s="2"/>
       <c r="D331" s="2"/>
       <c r="F331" s="2"/>
-    </row>
-    <row r="332" spans="1:6">
+      <c r="G331" s="4"/>
+    </row>
+    <row r="332" spans="1:7">
       <c r="B332" s="2"/>
       <c r="D332" s="2"/>
       <c r="F332" s="2"/>
-    </row>
-    <row r="333" spans="1:6">
+      <c r="G332" s="4"/>
+    </row>
+    <row r="333" spans="1:7">
       <c r="B333" s="2"/>
       <c r="D333" s="2"/>
       <c r="F333" s="2"/>
-    </row>
-    <row r="334" spans="1:6">
+      <c r="G333" s="4"/>
+    </row>
+    <row r="334" spans="1:7">
       <c r="B334" s="2"/>
       <c r="D334" s="2"/>
       <c r="F334" s="2"/>
-    </row>
-    <row r="335" spans="1:6">
+      <c r="G334" s="4"/>
+    </row>
+    <row r="335" spans="1:7">
       <c r="B335" s="2"/>
       <c r="D335" s="2"/>
       <c r="F335" s="2"/>
-    </row>
-    <row r="336" spans="1:6">
+      <c r="G335" s="4"/>
+    </row>
+    <row r="336" spans="1:7">
       <c r="B336" s="2"/>
       <c r="D336" s="2"/>
       <c r="F336" s="2"/>
-    </row>
-    <row r="337" spans="1:6">
+      <c r="G336" s="4"/>
+    </row>
+    <row r="337" spans="1:7">
       <c r="B337" s="2"/>
       <c r="D337" s="2"/>
       <c r="F337" s="2"/>
-    </row>
-    <row r="338" spans="1:6">
+      <c r="G337" s="4"/>
+    </row>
+    <row r="338" spans="1:7">
       <c r="B338" s="2"/>
       <c r="D338" s="2"/>
       <c r="F338" s="2"/>
-    </row>
-    <row r="339" spans="1:6">
+      <c r="G338" s="4"/>
+    </row>
+    <row r="339" spans="1:7">
       <c r="B339" s="2"/>
       <c r="D339" s="2"/>
       <c r="F339" s="2"/>
-    </row>
-    <row r="340" spans="1:6">
+      <c r="G339" s="4"/>
+    </row>
+    <row r="340" spans="1:7">
       <c r="B340" s="2"/>
       <c r="D340" s="2"/>
       <c r="F340" s="2"/>
-    </row>
-    <row r="341" spans="1:6">
+      <c r="G340" s="4"/>
+    </row>
+    <row r="341" spans="1:7">
       <c r="B341" s="2"/>
       <c r="D341" s="2"/>
       <c r="F341" s="2"/>
-    </row>
-    <row r="342" spans="1:6">
+      <c r="G341" s="4"/>
+    </row>
+    <row r="342" spans="1:7">
       <c r="B342" s="2"/>
       <c r="D342" s="2"/>
       <c r="F342" s="2"/>
-    </row>
-    <row r="343" spans="1:6">
+      <c r="G342" s="4"/>
+    </row>
+    <row r="343" spans="1:7">
       <c r="B343" s="2"/>
       <c r="D343" s="2"/>
       <c r="F343" s="2"/>
-    </row>
-    <row r="344" spans="1:6">
+      <c r="G343" s="4"/>
+    </row>
+    <row r="344" spans="1:7">
       <c r="B344" s="2"/>
       <c r="D344" s="2"/>
       <c r="F344" s="2"/>
-    </row>
-    <row r="345" spans="1:6">
+      <c r="G344" s="4"/>
+    </row>
+    <row r="345" spans="1:7">
       <c r="B345" s="2"/>
       <c r="D345" s="2"/>
       <c r="F345" s="2"/>
-    </row>
-    <row r="346" spans="1:6">
+      <c r="G345" s="4"/>
+    </row>
+    <row r="346" spans="1:7">
       <c r="B346" s="2"/>
       <c r="D346" s="2"/>
       <c r="F346" s="2"/>
-    </row>
-    <row r="347" spans="1:6">
+      <c r="G346" s="4"/>
+    </row>
+    <row r="347" spans="1:7">
       <c r="B347" s="2"/>
       <c r="D347" s="2"/>
       <c r="F347" s="2"/>
-    </row>
-    <row r="348" spans="1:6">
+      <c r="G347" s="4"/>
+    </row>
+    <row r="348" spans="1:7">
       <c r="B348" s="2"/>
       <c r="D348" s="2"/>
       <c r="F348" s="2"/>
-    </row>
-    <row r="349" spans="1:6">
+      <c r="G348" s="4"/>
+    </row>
+    <row r="349" spans="1:7">
       <c r="B349" s="2"/>
       <c r="D349" s="2"/>
       <c r="F349" s="2"/>
-    </row>
-    <row r="350" spans="1:6">
+      <c r="G349" s="4"/>
+    </row>
+    <row r="350" spans="1:7">
       <c r="B350" s="2"/>
       <c r="D350" s="2"/>
       <c r="F350" s="2"/>
-    </row>
-    <row r="351" spans="1:6">
+      <c r="G350" s="4"/>
+    </row>
+    <row r="351" spans="1:7">
       <c r="B351" s="2"/>
       <c r="D351" s="2"/>
       <c r="F351" s="2"/>
-    </row>
-    <row r="352" spans="1:6">
+      <c r="G351" s="4"/>
+    </row>
+    <row r="352" spans="1:7">
       <c r="B352" s="2"/>
       <c r="D352" s="2"/>
       <c r="F352" s="2"/>
-    </row>
-    <row r="353" spans="1:6">
+      <c r="G352" s="4"/>
+    </row>
+    <row r="353" spans="1:7">
       <c r="B353" s="2"/>
       <c r="D353" s="2"/>
       <c r="F353" s="2"/>
-    </row>
-    <row r="354" spans="1:6">
+      <c r="G353" s="4"/>
+    </row>
+    <row r="354" spans="1:7">
       <c r="B354" s="2"/>
       <c r="D354" s="2"/>
       <c r="F354" s="2"/>
-    </row>
-    <row r="355" spans="1:6">
+      <c r="G354" s="4"/>
+    </row>
+    <row r="355" spans="1:7">
       <c r="B355" s="2"/>
       <c r="D355" s="2"/>
       <c r="F355" s="2"/>
-    </row>
-    <row r="356" spans="1:6">
+      <c r="G355" s="4"/>
+    </row>
+    <row r="356" spans="1:7">
       <c r="B356" s="2"/>
       <c r="D356" s="2"/>
       <c r="F356" s="2"/>
-    </row>
-    <row r="357" spans="1:6">
+      <c r="G356" s="4"/>
+    </row>
+    <row r="357" spans="1:7">
       <c r="B357" s="2"/>
       <c r="D357" s="2"/>
       <c r="F357" s="2"/>
-    </row>
-    <row r="358" spans="1:6">
+      <c r="G357" s="4"/>
+    </row>
+    <row r="358" spans="1:7">
       <c r="B358" s="2"/>
       <c r="D358" s="2"/>
       <c r="F358" s="2"/>
-    </row>
-    <row r="359" spans="1:6">
+      <c r="G358" s="4"/>
+    </row>
+    <row r="359" spans="1:7">
       <c r="B359" s="2"/>
       <c r="D359" s="2"/>
       <c r="F359" s="2"/>
-    </row>
-    <row r="360" spans="1:6">
+      <c r="G359" s="4"/>
+    </row>
+    <row r="360" spans="1:7">
       <c r="B360" s="2"/>
       <c r="D360" s="2"/>
       <c r="F360" s="2"/>
-    </row>
-    <row r="361" spans="1:6">
+      <c r="G360" s="4"/>
+    </row>
+    <row r="361" spans="1:7">
       <c r="B361" s="2"/>
       <c r="D361" s="2"/>
       <c r="F361" s="2"/>
-    </row>
-    <row r="362" spans="1:6">
+      <c r="G361" s="4"/>
+    </row>
+    <row r="362" spans="1:7">
       <c r="B362" s="2"/>
       <c r="D362" s="2"/>
       <c r="F362" s="2"/>
-    </row>
-    <row r="363" spans="1:6">
+      <c r="G362" s="4"/>
+    </row>
+    <row r="363" spans="1:7">
       <c r="B363" s="2"/>
       <c r="D363" s="2"/>
       <c r="F363" s="2"/>
-    </row>
-    <row r="364" spans="1:6">
+      <c r="G363" s="4"/>
+    </row>
+    <row r="364" spans="1:7">
       <c r="B364" s="2"/>
       <c r="D364" s="2"/>
       <c r="F364" s="2"/>
-    </row>
-    <row r="365" spans="1:6">
+      <c r="G364" s="4"/>
+    </row>
+    <row r="365" spans="1:7">
       <c r="B365" s="2"/>
       <c r="D365" s="2"/>
       <c r="F365" s="2"/>
-    </row>
-    <row r="366" spans="1:6">
+      <c r="G365" s="4"/>
+    </row>
+    <row r="366" spans="1:7">
       <c r="B366" s="2"/>
       <c r="D366" s="2"/>
       <c r="F366" s="2"/>
-    </row>
-    <row r="367" spans="1:6">
+      <c r="G366" s="4"/>
+    </row>
+    <row r="367" spans="1:7">
       <c r="B367" s="2"/>
       <c r="D367" s="2"/>
       <c r="F367" s="2"/>
-    </row>
-    <row r="368" spans="1:6">
+      <c r="G367" s="4"/>
+    </row>
+    <row r="368" spans="1:7">
       <c r="B368" s="2"/>
       <c r="D368" s="2"/>
       <c r="F368" s="2"/>
-    </row>
-    <row r="369" spans="1:6">
+      <c r="G368" s="4"/>
+    </row>
+    <row r="369" spans="1:7">
       <c r="B369" s="2"/>
       <c r="D369" s="2"/>
       <c r="F369" s="2"/>
-    </row>
-    <row r="370" spans="1:6">
+      <c r="G369" s="4"/>
+    </row>
+    <row r="370" spans="1:7">
       <c r="B370" s="2"/>
       <c r="D370" s="2"/>
       <c r="F370" s="2"/>
-    </row>
-    <row r="371" spans="1:6">
+      <c r="G370" s="4"/>
+    </row>
+    <row r="371" spans="1:7">
       <c r="B371" s="2"/>
       <c r="D371" s="2"/>
       <c r="F371" s="2"/>
-    </row>
-    <row r="372" spans="1:6">
+      <c r="G371" s="4"/>
+    </row>
+    <row r="372" spans="1:7">
       <c r="B372" s="2"/>
       <c r="D372" s="2"/>
       <c r="F372" s="2"/>
-    </row>
-    <row r="373" spans="1:6">
+      <c r="G372" s="4"/>
+    </row>
+    <row r="373" spans="1:7">
       <c r="B373" s="2"/>
       <c r="D373" s="2"/>
       <c r="F373" s="2"/>
-    </row>
-    <row r="374" spans="1:6">
+      <c r="G373" s="4"/>
+    </row>
+    <row r="374" spans="1:7">
       <c r="B374" s="2"/>
       <c r="D374" s="2"/>
       <c r="F374" s="2"/>
-    </row>
-    <row r="375" spans="1:6">
+      <c r="G374" s="4"/>
+    </row>
+    <row r="375" spans="1:7">
       <c r="B375" s="2"/>
       <c r="D375" s="2"/>
       <c r="F375" s="2"/>
-    </row>
-    <row r="376" spans="1:6">
+      <c r="G375" s="4"/>
+    </row>
+    <row r="376" spans="1:7">
       <c r="B376" s="2"/>
       <c r="D376" s="2"/>
       <c r="F376" s="2"/>
-    </row>
-    <row r="377" spans="1:6">
+      <c r="G376" s="4"/>
+    </row>
+    <row r="377" spans="1:7">
       <c r="B377" s="2"/>
       <c r="D377" s="2"/>
       <c r="F377" s="2"/>
-    </row>
-    <row r="378" spans="1:6">
+      <c r="G377" s="4"/>
+    </row>
+    <row r="378" spans="1:7">
       <c r="B378" s="2"/>
       <c r="D378" s="2"/>
       <c r="F378" s="2"/>
-    </row>
-    <row r="379" spans="1:6">
+      <c r="G378" s="4"/>
+    </row>
+    <row r="379" spans="1:7">
       <c r="B379" s="2"/>
       <c r="D379" s="2"/>
       <c r="F379" s="2"/>
-    </row>
-    <row r="380" spans="1:6">
+      <c r="G379" s="4"/>
+    </row>
+    <row r="380" spans="1:7">
       <c r="B380" s="2"/>
       <c r="D380" s="2"/>
       <c r="F380" s="2"/>
-    </row>
-    <row r="381" spans="1:6">
+      <c r="G380" s="4"/>
+    </row>
+    <row r="381" spans="1:7">
       <c r="B381" s="2"/>
       <c r="D381" s="2"/>
       <c r="F381" s="2"/>
-    </row>
-    <row r="382" spans="1:6">
+      <c r="G381" s="4"/>
+    </row>
+    <row r="382" spans="1:7">
       <c r="B382" s="2"/>
       <c r="D382" s="2"/>
       <c r="F382" s="2"/>
-    </row>
-    <row r="383" spans="1:6">
+      <c r="G382" s="4"/>
+    </row>
+    <row r="383" spans="1:7">
       <c r="B383" s="2"/>
       <c r="D383" s="2"/>
       <c r="F383" s="2"/>
-    </row>
-    <row r="384" spans="1:6">
+      <c r="G383" s="4"/>
+    </row>
+    <row r="384" spans="1:7">
       <c r="B384" s="2"/>
       <c r="D384" s="2"/>
       <c r="F384" s="2"/>
-    </row>
-    <row r="385" spans="1:6">
+      <c r="G384" s="4"/>
+    </row>
+    <row r="385" spans="1:7">
       <c r="B385" s="2"/>
       <c r="D385" s="2"/>
       <c r="F385" s="2"/>
-    </row>
-    <row r="386" spans="1:6">
+      <c r="G385" s="4"/>
+    </row>
+    <row r="386" spans="1:7">
       <c r="B386" s="2"/>
       <c r="D386" s="2"/>
       <c r="F386" s="2"/>
-    </row>
-    <row r="387" spans="1:6">
+      <c r="G386" s="4"/>
+    </row>
+    <row r="387" spans="1:7">
       <c r="B387" s="2"/>
       <c r="D387" s="2"/>
       <c r="F387" s="2"/>
-    </row>
-    <row r="388" spans="1:6">
+      <c r="G387" s="4"/>
+    </row>
+    <row r="388" spans="1:7">
       <c r="B388" s="2"/>
       <c r="D388" s="2"/>
       <c r="F388" s="2"/>
-    </row>
-    <row r="389" spans="1:6">
+      <c r="G388" s="4"/>
+    </row>
+    <row r="389" spans="1:7">
       <c r="B389" s="2"/>
       <c r="D389" s="2"/>
       <c r="F389" s="2"/>
-    </row>
-    <row r="390" spans="1:6">
+      <c r="G389" s="4"/>
+    </row>
+    <row r="390" spans="1:7">
       <c r="B390" s="2"/>
       <c r="D390" s="2"/>
       <c r="F390" s="2"/>
-    </row>
-    <row r="391" spans="1:6">
+      <c r="G390" s="4"/>
+    </row>
+    <row r="391" spans="1:7">
       <c r="B391" s="2"/>
       <c r="D391" s="2"/>
       <c r="F391" s="2"/>
-    </row>
-    <row r="392" spans="1:6">
+      <c r="G391" s="4"/>
+    </row>
+    <row r="392" spans="1:7">
       <c r="B392" s="2"/>
       <c r="D392" s="2"/>
       <c r="F392" s="2"/>
-    </row>
-    <row r="393" spans="1:6">
+      <c r="G392" s="4"/>
+    </row>
+    <row r="393" spans="1:7">
       <c r="B393" s="2"/>
       <c r="D393" s="2"/>
       <c r="F393" s="2"/>
-    </row>
-    <row r="394" spans="1:6">
+      <c r="G393" s="4"/>
+    </row>
+    <row r="394" spans="1:7">
       <c r="B394" s="2"/>
       <c r="D394" s="2"/>
       <c r="F394" s="2"/>
-    </row>
-    <row r="395" spans="1:6">
+      <c r="G394" s="4"/>
+    </row>
+    <row r="395" spans="1:7">
       <c r="B395" s="2"/>
       <c r="D395" s="2"/>
       <c r="F395" s="2"/>
-    </row>
-    <row r="396" spans="1:6">
+      <c r="G395" s="4"/>
+    </row>
+    <row r="396" spans="1:7">
       <c r="B396" s="2"/>
       <c r="D396" s="2"/>
       <c r="F396" s="2"/>
-    </row>
-    <row r="397" spans="1:6">
+      <c r="G396" s="4"/>
+    </row>
+    <row r="397" spans="1:7">
       <c r="B397" s="2"/>
       <c r="D397" s="2"/>
       <c r="F397" s="2"/>
-    </row>
-    <row r="398" spans="1:6">
+      <c r="G397" s="4"/>
+    </row>
+    <row r="398" spans="1:7">
       <c r="B398" s="2"/>
       <c r="D398" s="2"/>
       <c r="F398" s="2"/>
-    </row>
-    <row r="399" spans="1:6">
+      <c r="G398" s="4"/>
+    </row>
+    <row r="399" spans="1:7">
       <c r="B399" s="2"/>
       <c r="D399" s="2"/>
       <c r="F399" s="2"/>
-    </row>
-    <row r="400" spans="1:6">
+      <c r="G399" s="4"/>
+    </row>
+    <row r="400" spans="1:7">
       <c r="B400" s="2"/>
       <c r="D400" s="2"/>
       <c r="F400" s="2"/>
-    </row>
-    <row r="401" spans="1:6">
+      <c r="G400" s="4"/>
+    </row>
+    <row r="401" spans="1:7">
       <c r="B401" s="2"/>
       <c r="D401" s="2"/>
       <c r="F401" s="2"/>
-    </row>
-    <row r="402" spans="1:6">
+      <c r="G401" s="4"/>
+    </row>
+    <row r="402" spans="1:7">
       <c r="B402" s="2"/>
       <c r="D402" s="2"/>
       <c r="F402" s="2"/>
-    </row>
-    <row r="403" spans="1:6">
+      <c r="G402" s="4"/>
+    </row>
+    <row r="403" spans="1:7">
       <c r="B403" s="2"/>
       <c r="D403" s="2"/>
       <c r="F403" s="2"/>
-    </row>
-    <row r="404" spans="1:6">
+      <c r="G403" s="4"/>
+    </row>
+    <row r="404" spans="1:7">
       <c r="B404" s="2"/>
       <c r="D404" s="2"/>
       <c r="F404" s="2"/>
-    </row>
-    <row r="405" spans="1:6">
+      <c r="G404" s="4"/>
+    </row>
+    <row r="405" spans="1:7">
       <c r="B405" s="2"/>
       <c r="D405" s="2"/>
       <c r="F405" s="2"/>
-    </row>
-    <row r="406" spans="1:6">
+      <c r="G405" s="4"/>
+    </row>
+    <row r="406" spans="1:7">
       <c r="B406" s="2"/>
       <c r="D406" s="2"/>
       <c r="F406" s="2"/>
-    </row>
-    <row r="407" spans="1:6">
+      <c r="G406" s="4"/>
+    </row>
+    <row r="407" spans="1:7">
       <c r="B407" s="2"/>
       <c r="D407" s="2"/>
       <c r="F407" s="2"/>
-    </row>
-    <row r="408" spans="1:6">
+      <c r="G407" s="4"/>
+    </row>
+    <row r="408" spans="1:7">
       <c r="B408" s="2"/>
       <c r="D408" s="2"/>
       <c r="F408" s="2"/>
-    </row>
-    <row r="409" spans="1:6">
+      <c r="G408" s="4"/>
+    </row>
+    <row r="409" spans="1:7">
       <c r="B409" s="2"/>
       <c r="D409" s="2"/>
       <c r="F409" s="2"/>
-    </row>
-    <row r="410" spans="1:6">
+      <c r="G409" s="4"/>
+    </row>
+    <row r="410" spans="1:7">
       <c r="B410" s="2"/>
       <c r="D410" s="2"/>
       <c r="F410" s="2"/>
-    </row>
-    <row r="411" spans="1:6">
+      <c r="G410" s="4"/>
+    </row>
+    <row r="411" spans="1:7">
       <c r="B411" s="2"/>
       <c r="D411" s="2"/>
       <c r="F411" s="2"/>
-    </row>
-    <row r="412" spans="1:6">
+      <c r="G411" s="4"/>
+    </row>
+    <row r="412" spans="1:7">
       <c r="B412" s="2"/>
       <c r="D412" s="2"/>
       <c r="F412" s="2"/>
-    </row>
-    <row r="413" spans="1:6">
+      <c r="G412" s="4"/>
+    </row>
+    <row r="413" spans="1:7">
       <c r="B413" s="2"/>
       <c r="D413" s="2"/>
       <c r="F413" s="2"/>
-    </row>
-    <row r="414" spans="1:6">
+      <c r="G413" s="4"/>
+    </row>
+    <row r="414" spans="1:7">
       <c r="B414" s="2"/>
       <c r="D414" s="2"/>
       <c r="F414" s="2"/>
-    </row>
-    <row r="415" spans="1:6">
+      <c r="G414" s="4"/>
+    </row>
+    <row r="415" spans="1:7">
       <c r="B415" s="2"/>
       <c r="D415" s="2"/>
       <c r="F415" s="2"/>
-    </row>
-    <row r="416" spans="1:6">
+      <c r="G415" s="4"/>
+    </row>
+    <row r="416" spans="1:7">
       <c r="B416" s="2"/>
       <c r="D416" s="2"/>
       <c r="F416" s="2"/>
-    </row>
-    <row r="417" spans="1:6">
+      <c r="G416" s="4"/>
+    </row>
+    <row r="417" spans="1:7">
       <c r="B417" s="2"/>
       <c r="D417" s="2"/>
       <c r="F417" s="2"/>
-    </row>
-    <row r="418" spans="1:6">
+      <c r="G417" s="4"/>
+    </row>
+    <row r="418" spans="1:7">
       <c r="B418" s="2"/>
       <c r="D418" s="2"/>
       <c r="F418" s="2"/>
-    </row>
-    <row r="419" spans="1:6">
+      <c r="G418" s="4"/>
+    </row>
+    <row r="419" spans="1:7">
       <c r="B419" s="2"/>
       <c r="D419" s="2"/>
       <c r="F419" s="2"/>
-    </row>
-    <row r="420" spans="1:6">
+      <c r="G419" s="4"/>
+    </row>
+    <row r="420" spans="1:7">
       <c r="B420" s="2"/>
       <c r="D420" s="2"/>
       <c r="F420" s="2"/>
-    </row>
-    <row r="421" spans="1:6">
+      <c r="G420" s="4"/>
+    </row>
+    <row r="421" spans="1:7">
       <c r="B421" s="2"/>
       <c r="D421" s="2"/>
       <c r="F421" s="2"/>
-    </row>
-    <row r="422" spans="1:6">
+      <c r="G421" s="4"/>
+    </row>
+    <row r="422" spans="1:7">
       <c r="B422" s="2"/>
       <c r="D422" s="2"/>
       <c r="F422" s="2"/>
-    </row>
-    <row r="423" spans="1:6">
+      <c r="G422" s="4"/>
+    </row>
+    <row r="423" spans="1:7">
       <c r="B423" s="2"/>
       <c r="D423" s="2"/>
       <c r="F423" s="2"/>
-    </row>
-    <row r="424" spans="1:6">
+      <c r="G423" s="4"/>
+    </row>
+    <row r="424" spans="1:7">
       <c r="B424" s="2"/>
       <c r="D424" s="2"/>
       <c r="F424" s="2"/>
-    </row>
-    <row r="425" spans="1:6">
+      <c r="G424" s="4"/>
+    </row>
+    <row r="425" spans="1:7">
       <c r="B425" s="2"/>
       <c r="D425" s="2"/>
       <c r="F425" s="2"/>
-    </row>
-    <row r="426" spans="1:6">
+      <c r="G425" s="4"/>
+    </row>
+    <row r="426" spans="1:7">
       <c r="B426" s="2"/>
       <c r="D426" s="2"/>
       <c r="F426" s="2"/>
-    </row>
-    <row r="427" spans="1:6">
+      <c r="G426" s="4"/>
+    </row>
+    <row r="427" spans="1:7">
       <c r="B427" s="2"/>
       <c r="D427" s="2"/>
       <c r="F427" s="2"/>
-    </row>
-    <row r="428" spans="1:6">
+      <c r="G427" s="4"/>
+    </row>
+    <row r="428" spans="1:7">
       <c r="B428" s="2"/>
       <c r="D428" s="2"/>
       <c r="F428" s="2"/>
-    </row>
-    <row r="429" spans="1:6">
+      <c r="G428" s="4"/>
+    </row>
+    <row r="429" spans="1:7">
       <c r="B429" s="2"/>
       <c r="D429" s="2"/>
       <c r="F429" s="2"/>
-    </row>
-    <row r="430" spans="1:6">
+      <c r="G429" s="4"/>
+    </row>
+    <row r="430" spans="1:7">
       <c r="B430" s="2"/>
       <c r="D430" s="2"/>
       <c r="F430" s="2"/>
-    </row>
-    <row r="431" spans="1:6">
+      <c r="G430" s="4"/>
+    </row>
+    <row r="431" spans="1:7">
       <c r="B431" s="2"/>
       <c r="D431" s="2"/>
       <c r="F431" s="2"/>
-    </row>
-    <row r="432" spans="1:6">
+      <c r="G431" s="4"/>
+    </row>
+    <row r="432" spans="1:7">
       <c r="B432" s="2"/>
       <c r="D432" s="2"/>
       <c r="F432" s="2"/>
-    </row>
-    <row r="433" spans="1:6">
+      <c r="G432" s="4"/>
+    </row>
+    <row r="433" spans="1:7">
       <c r="B433" s="2"/>
       <c r="D433" s="2"/>
       <c r="F433" s="2"/>
-    </row>
-    <row r="434" spans="1:6">
+      <c r="G433" s="4"/>
+    </row>
+    <row r="434" spans="1:7">
       <c r="B434" s="2"/>
       <c r="D434" s="2"/>
       <c r="F434" s="2"/>
-    </row>
-    <row r="435" spans="1:6">
+      <c r="G434" s="4"/>
+    </row>
+    <row r="435" spans="1:7">
       <c r="B435" s="2"/>
       <c r="D435" s="2"/>
       <c r="F435" s="2"/>
-    </row>
-    <row r="436" spans="1:6">
+      <c r="G435" s="4"/>
+    </row>
+    <row r="436" spans="1:7">
       <c r="B436" s="2"/>
       <c r="D436" s="2"/>
       <c r="F436" s="2"/>
-    </row>
-    <row r="437" spans="1:6">
+      <c r="G436" s="4"/>
+    </row>
+    <row r="437" spans="1:7">
       <c r="B437" s="2"/>
       <c r="D437" s="2"/>
       <c r="F437" s="2"/>
-    </row>
-    <row r="438" spans="1:6">
+      <c r="G437" s="4"/>
+    </row>
+    <row r="438" spans="1:7">
       <c r="B438" s="2"/>
       <c r="D438" s="2"/>
       <c r="F438" s="2"/>
-    </row>
-    <row r="439" spans="1:6">
+      <c r="G438" s="4"/>
+    </row>
+    <row r="439" spans="1:7">
       <c r="B439" s="2"/>
       <c r="D439" s="2"/>
       <c r="F439" s="2"/>
-    </row>
-    <row r="440" spans="1:6">
+      <c r="G439" s="4"/>
+    </row>
+    <row r="440" spans="1:7">
       <c r="B440" s="2"/>
       <c r="D440" s="2"/>
       <c r="F440" s="2"/>
-    </row>
-    <row r="441" spans="1:6">
+      <c r="G440" s="4"/>
+    </row>
+    <row r="441" spans="1:7">
       <c r="B441" s="2"/>
       <c r="D441" s="2"/>
       <c r="F441" s="2"/>
-    </row>
-    <row r="442" spans="1:6">
+      <c r="G441" s="4"/>
+    </row>
+    <row r="442" spans="1:7">
       <c r="B442" s="2"/>
       <c r="D442" s="2"/>
       <c r="F442" s="2"/>
-    </row>
-    <row r="443" spans="1:6">
+      <c r="G442" s="4"/>
+    </row>
+    <row r="443" spans="1:7">
       <c r="B443" s="2"/>
       <c r="D443" s="2"/>
       <c r="F443" s="2"/>
-    </row>
-    <row r="444" spans="1:6">
+      <c r="G443" s="4"/>
+    </row>
+    <row r="444" spans="1:7">
       <c r="B444" s="2"/>
       <c r="D444" s="2"/>
       <c r="F444" s="2"/>
-    </row>
-    <row r="445" spans="1:6">
+      <c r="G444" s="4"/>
+    </row>
+    <row r="445" spans="1:7">
       <c r="B445" s="2"/>
       <c r="D445" s="2"/>
       <c r="F445" s="2"/>
-    </row>
-    <row r="446" spans="1:6">
+      <c r="G445" s="4"/>
+    </row>
+    <row r="446" spans="1:7">
       <c r="B446" s="2"/>
       <c r="D446" s="2"/>
       <c r="F446" s="2"/>
-    </row>
-    <row r="447" spans="1:6">
+      <c r="G446" s="4"/>
+    </row>
+    <row r="447" spans="1:7">
       <c r="B447" s="2"/>
       <c r="D447" s="2"/>
       <c r="F447" s="2"/>
-    </row>
-    <row r="448" spans="1:6">
+      <c r="G447" s="4"/>
+    </row>
+    <row r="448" spans="1:7">
       <c r="B448" s="2"/>
       <c r="D448" s="2"/>
       <c r="F448" s="2"/>
-    </row>
-    <row r="449" spans="1:6">
+      <c r="G448" s="4"/>
+    </row>
+    <row r="449" spans="1:7">
       <c r="B449" s="2"/>
       <c r="D449" s="2"/>
       <c r="F449" s="2"/>
-    </row>
-    <row r="450" spans="1:6">
+      <c r="G449" s="4"/>
+    </row>
+    <row r="450" spans="1:7">
       <c r="B450" s="2"/>
       <c r="D450" s="2"/>
       <c r="F450" s="2"/>
-    </row>
-    <row r="451" spans="1:6">
+      <c r="G450" s="4"/>
+    </row>
+    <row r="451" spans="1:7">
       <c r="B451" s="2"/>
       <c r="D451" s="2"/>
       <c r="F451" s="2"/>
-    </row>
-    <row r="452" spans="1:6">
+      <c r="G451" s="4"/>
+    </row>
+    <row r="452" spans="1:7">
       <c r="B452" s="2"/>
       <c r="D452" s="2"/>
       <c r="F452" s="2"/>
-    </row>
-    <row r="453" spans="1:6">
+      <c r="G452" s="4"/>
+    </row>
+    <row r="453" spans="1:7">
       <c r="B453" s="2"/>
       <c r="D453" s="2"/>
       <c r="F453" s="2"/>
-    </row>
-    <row r="454" spans="1:6">
+      <c r="G453" s="4"/>
+    </row>
+    <row r="454" spans="1:7">
       <c r="B454" s="2"/>
       <c r="D454" s="2"/>
       <c r="F454" s="2"/>
-    </row>
-    <row r="455" spans="1:6">
+      <c r="G454" s="4"/>
+    </row>
+    <row r="455" spans="1:7">
       <c r="B455" s="2"/>
       <c r="D455" s="2"/>
       <c r="F455" s="2"/>
-    </row>
-    <row r="456" spans="1:6">
+      <c r="G455" s="4"/>
+    </row>
+    <row r="456" spans="1:7">
       <c r="B456" s="2"/>
       <c r="D456" s="2"/>
       <c r="F456" s="2"/>
-    </row>
-    <row r="457" spans="1:6">
+      <c r="G456" s="4"/>
+    </row>
+    <row r="457" spans="1:7">
       <c r="B457" s="2"/>
       <c r="D457" s="2"/>
       <c r="F457" s="2"/>
-    </row>
-    <row r="458" spans="1:6">
+      <c r="G457" s="4"/>
+    </row>
+    <row r="458" spans="1:7">
       <c r="B458" s="2"/>
       <c r="D458" s="2"/>
       <c r="F458" s="2"/>
-    </row>
-    <row r="459" spans="1:6">
+      <c r="G458" s="4"/>
+    </row>
+    <row r="459" spans="1:7">
       <c r="B459" s="2"/>
       <c r="D459" s="2"/>
       <c r="F459" s="2"/>
-    </row>
-    <row r="460" spans="1:6">
+      <c r="G459" s="4"/>
+    </row>
+    <row r="460" spans="1:7">
       <c r="B460" s="2"/>
       <c r="D460" s="2"/>
       <c r="F460" s="2"/>
-    </row>
-    <row r="461" spans="1:6">
+      <c r="G460" s="4"/>
+    </row>
+    <row r="461" spans="1:7">
       <c r="B461" s="2"/>
       <c r="D461" s="2"/>
       <c r="F461" s="2"/>
-    </row>
-    <row r="462" spans="1:6">
+      <c r="G461" s="4"/>
+    </row>
+    <row r="462" spans="1:7">
       <c r="B462" s="2"/>
       <c r="D462" s="2"/>
       <c r="F462" s="2"/>
-    </row>
-    <row r="463" spans="1:6">
+      <c r="G462" s="4"/>
+    </row>
+    <row r="463" spans="1:7">
       <c r="B463" s="2"/>
       <c r="D463" s="2"/>
       <c r="F463" s="2"/>
-    </row>
-    <row r="464" spans="1:6">
+      <c r="G463" s="4"/>
+    </row>
+    <row r="464" spans="1:7">
       <c r="B464" s="2"/>
       <c r="D464" s="2"/>
       <c r="F464" s="2"/>
-    </row>
-    <row r="465" spans="1:6">
+      <c r="G464" s="4"/>
+    </row>
+    <row r="465" spans="1:7">
       <c r="B465" s="2"/>
       <c r="D465" s="2"/>
       <c r="F465" s="2"/>
-    </row>
-    <row r="466" spans="1:6">
+      <c r="G465" s="4"/>
+    </row>
+    <row r="466" spans="1:7">
       <c r="B466" s="2"/>
       <c r="D466" s="2"/>
       <c r="F466" s="2"/>
-    </row>
-    <row r="467" spans="1:6">
+      <c r="G466" s="4"/>
+    </row>
+    <row r="467" spans="1:7">
       <c r="B467" s="2"/>
       <c r="D467" s="2"/>
       <c r="F467" s="2"/>
-    </row>
-    <row r="468" spans="1:6">
+      <c r="G467" s="4"/>
+    </row>
+    <row r="468" spans="1:7">
       <c r="B468" s="2"/>
       <c r="D468" s="2"/>
       <c r="F468" s="2"/>
-    </row>
-    <row r="469" spans="1:6">
+      <c r="G468" s="4"/>
+    </row>
+    <row r="469" spans="1:7">
       <c r="B469" s="2"/>
       <c r="D469" s="2"/>
       <c r="F469" s="2"/>
-    </row>
-    <row r="470" spans="1:6">
+      <c r="G469" s="4"/>
+    </row>
+    <row r="470" spans="1:7">
       <c r="B470" s="2"/>
       <c r="D470" s="2"/>
       <c r="F470" s="2"/>
-    </row>
-    <row r="471" spans="1:6">
+      <c r="G470" s="4"/>
+    </row>
+    <row r="471" spans="1:7">
       <c r="B471" s="2"/>
       <c r="D471" s="2"/>
       <c r="F471" s="2"/>
-    </row>
-    <row r="472" spans="1:6">
+      <c r="G471" s="4"/>
+    </row>
+    <row r="472" spans="1:7">
       <c r="B472" s="2"/>
       <c r="D472" s="2"/>
       <c r="F472" s="2"/>
-    </row>
-    <row r="473" spans="1:6">
+      <c r="G472" s="4"/>
+    </row>
+    <row r="473" spans="1:7">
       <c r="B473" s="2"/>
       <c r="D473" s="2"/>
       <c r="F473" s="2"/>
-    </row>
-    <row r="474" spans="1:6">
+      <c r="G473" s="4"/>
+    </row>
+    <row r="474" spans="1:7">
       <c r="B474" s="2"/>
       <c r="D474" s="2"/>
       <c r="F474" s="2"/>
-    </row>
-    <row r="475" spans="1:6">
+      <c r="G474" s="4"/>
+    </row>
+    <row r="475" spans="1:7">
       <c r="B475" s="2"/>
       <c r="D475" s="2"/>
       <c r="F475" s="2"/>
-    </row>
-    <row r="476" spans="1:6">
+      <c r="G475" s="4"/>
+    </row>
+    <row r="476" spans="1:7">
       <c r="B476" s="2"/>
       <c r="D476" s="2"/>
       <c r="F476" s="2"/>
-    </row>
-    <row r="477" spans="1:6">
+      <c r="G476" s="4"/>
+    </row>
+    <row r="477" spans="1:7">
       <c r="B477" s="2"/>
       <c r="D477" s="2"/>
       <c r="F477" s="2"/>
-    </row>
-    <row r="478" spans="1:6">
+      <c r="G477" s="4"/>
+    </row>
+    <row r="478" spans="1:7">
       <c r="B478" s="2"/>
       <c r="D478" s="2"/>
       <c r="F478" s="2"/>
-    </row>
-    <row r="479" spans="1:6">
+      <c r="G478" s="4"/>
+    </row>
+    <row r="479" spans="1:7">
       <c r="B479" s="2"/>
       <c r="D479" s="2"/>
       <c r="F479" s="2"/>
-    </row>
-    <row r="480" spans="1:6">
+      <c r="G479" s="4"/>
+    </row>
+    <row r="480" spans="1:7">
       <c r="B480" s="2"/>
       <c r="D480" s="2"/>
       <c r="F480" s="2"/>
-    </row>
-    <row r="481" spans="1:6">
+      <c r="G480" s="4"/>
+    </row>
+    <row r="481" spans="1:7">
       <c r="B481" s="2"/>
       <c r="D481" s="2"/>
       <c r="F481" s="2"/>
-    </row>
-    <row r="482" spans="1:6">
+      <c r="G481" s="4"/>
+    </row>
+    <row r="482" spans="1:7">
       <c r="B482" s="2"/>
       <c r="D482" s="2"/>
       <c r="F482" s="2"/>
-    </row>
-    <row r="483" spans="1:6">
+      <c r="G482" s="4"/>
+    </row>
+    <row r="483" spans="1:7">
       <c r="B483" s="2"/>
       <c r="D483" s="2"/>
       <c r="F483" s="2"/>
-    </row>
-    <row r="484" spans="1:6">
+      <c r="G483" s="4"/>
+    </row>
+    <row r="484" spans="1:7">
       <c r="B484" s="2"/>
       <c r="D484" s="2"/>
       <c r="F484" s="2"/>
-    </row>
-    <row r="485" spans="1:6">
+      <c r="G484" s="4"/>
+    </row>
+    <row r="485" spans="1:7">
       <c r="B485" s="2"/>
       <c r="D485" s="2"/>
       <c r="F485" s="2"/>
-    </row>
-    <row r="486" spans="1:6">
+      <c r="G485" s="4"/>
+    </row>
+    <row r="486" spans="1:7">
       <c r="B486" s="2"/>
       <c r="D486" s="2"/>
       <c r="F486" s="2"/>
-    </row>
-    <row r="487" spans="1:6">
+      <c r="G486" s="4"/>
+    </row>
+    <row r="487" spans="1:7">
       <c r="B487" s="2"/>
       <c r="D487" s="2"/>
       <c r="F487" s="2"/>
-    </row>
-    <row r="488" spans="1:6">
+      <c r="G487" s="4"/>
+    </row>
+    <row r="488" spans="1:7">
       <c r="B488" s="2"/>
       <c r="D488" s="2"/>
       <c r="F488" s="2"/>
-    </row>
-    <row r="489" spans="1:6">
+      <c r="G488" s="4"/>
+    </row>
+    <row r="489" spans="1:7">
       <c r="B489" s="2"/>
       <c r="D489" s="2"/>
       <c r="F489" s="2"/>
-    </row>
-    <row r="490" spans="1:6">
+      <c r="G489" s="4"/>
+    </row>
+    <row r="490" spans="1:7">
       <c r="B490" s="2"/>
       <c r="D490" s="2"/>
       <c r="F490" s="2"/>
-    </row>
-    <row r="491" spans="1:6">
+      <c r="G490" s="4"/>
+    </row>
+    <row r="491" spans="1:7">
       <c r="B491" s="2"/>
       <c r="D491" s="2"/>
       <c r="F491" s="2"/>
-    </row>
-    <row r="492" spans="1:6">
+      <c r="G491" s="4"/>
+    </row>
+    <row r="492" spans="1:7">
       <c r="B492" s="2"/>
       <c r="D492" s="2"/>
       <c r="F492" s="2"/>
-    </row>
-    <row r="493" spans="1:6">
+      <c r="G492" s="4"/>
+    </row>
+    <row r="493" spans="1:7">
       <c r="B493" s="2"/>
       <c r="D493" s="2"/>
       <c r="F493" s="2"/>
-    </row>
-    <row r="494" spans="1:6">
+      <c r="G493" s="4"/>
+    </row>
+    <row r="494" spans="1:7">
       <c r="B494" s="2"/>
       <c r="D494" s="2"/>
       <c r="F494" s="2"/>
-    </row>
-    <row r="495" spans="1:6">
+      <c r="G494" s="4"/>
+    </row>
+    <row r="495" spans="1:7">
       <c r="B495" s="2"/>
       <c r="D495" s="2"/>
       <c r="F495" s="2"/>
-    </row>
-    <row r="496" spans="1:6">
+      <c r="G495" s="4"/>
+    </row>
+    <row r="496" spans="1:7">
       <c r="B496" s="2"/>
       <c r="D496" s="2"/>
       <c r="F496" s="2"/>
-    </row>
-    <row r="497" spans="1:6">
+      <c r="G496" s="4"/>
+    </row>
+    <row r="497" spans="1:7">
       <c r="B497" s="2"/>
       <c r="D497" s="2"/>
       <c r="F497" s="2"/>
-    </row>
-    <row r="498" spans="1:6">
+      <c r="G497" s="4"/>
+    </row>
+    <row r="498" spans="1:7">
       <c r="B498" s="2"/>
       <c r="D498" s="2"/>
       <c r="F498" s="2"/>
-    </row>
-    <row r="499" spans="1:6">
+      <c r="G498" s="4"/>
+    </row>
+    <row r="499" spans="1:7">
       <c r="B499" s="2"/>
       <c r="D499" s="2"/>
       <c r="F499" s="2"/>
-    </row>
-    <row r="500" spans="1:6">
+      <c r="G499" s="4"/>
+    </row>
+    <row r="500" spans="1:7">
       <c r="B500" s="2"/>
       <c r="D500" s="2"/>
       <c r="F500" s="2"/>
-    </row>
-    <row r="501" spans="1:6">
+      <c r="G500" s="4"/>
+    </row>
+    <row r="501" spans="1:7">
       <c r="B501" s="2"/>
       <c r="D501" s="2"/>
       <c r="F501" s="2"/>
-    </row>
-    <row r="502" spans="1:6">
+      <c r="G501" s="4"/>
+    </row>
+    <row r="502" spans="1:7">
       <c r="B502" s="2"/>
       <c r="D502" s="2"/>
       <c r="F502" s="2"/>
-    </row>
-    <row r="503" spans="1:6">
+      <c r="G502" s="4"/>
+    </row>
+    <row r="503" spans="1:7">
       <c r="B503" s="2"/>
       <c r="D503" s="2"/>
       <c r="F503" s="2"/>
-    </row>
-    <row r="504" spans="1:6">
+      <c r="G503" s="4"/>
+    </row>
+    <row r="504" spans="1:7">
       <c r="B504" s="2"/>
       <c r="D504" s="2"/>
       <c r="F504" s="2"/>
-    </row>
-    <row r="505" spans="1:6">
+      <c r="G504" s="4"/>
+    </row>
+    <row r="505" spans="1:7">
       <c r="B505" s="2"/>
       <c r="D505" s="2"/>
       <c r="F505" s="2"/>
-    </row>
-    <row r="506" spans="1:6">
+      <c r="G505" s="4"/>
+    </row>
+    <row r="506" spans="1:7">
       <c r="B506" s="2"/>
       <c r="D506" s="2"/>
       <c r="F506" s="2"/>
-    </row>
-    <row r="507" spans="1:6">
+      <c r="G506" s="4"/>
+    </row>
+    <row r="507" spans="1:7">
       <c r="B507" s="2"/>
       <c r="D507" s="2"/>
       <c r="F507" s="2"/>
-    </row>
-    <row r="508" spans="1:6">
+      <c r="G507" s="4"/>
+    </row>
+    <row r="508" spans="1:7">
       <c r="B508" s="2"/>
       <c r="D508" s="2"/>
       <c r="F508" s="2"/>
-    </row>
-    <row r="509" spans="1:6">
+      <c r="G508" s="4"/>
+    </row>
+    <row r="509" spans="1:7">
       <c r="B509" s="2"/>
       <c r="D509" s="2"/>
       <c r="F509" s="2"/>
-    </row>
-    <row r="510" spans="1:6">
+      <c r="G509" s="4"/>
+    </row>
+    <row r="510" spans="1:7">
       <c r="B510" s="2"/>
       <c r="D510" s="2"/>
       <c r="F510" s="2"/>
-    </row>
-    <row r="511" spans="1:6">
+      <c r="G510" s="4"/>
+    </row>
+    <row r="511" spans="1:7">
       <c r="B511" s="2"/>
       <c r="D511" s="2"/>
       <c r="F511" s="2"/>
-    </row>
-    <row r="512" spans="1:6">
+      <c r="G511" s="4"/>
+    </row>
+    <row r="512" spans="1:7">
       <c r="B512" s="2"/>
       <c r="D512" s="2"/>
       <c r="F512" s="2"/>
-    </row>
-    <row r="513" spans="1:6">
+      <c r="G512" s="4"/>
+    </row>
+    <row r="513" spans="1:7">
       <c r="B513" s="2"/>
       <c r="D513" s="2"/>
       <c r="F513" s="2"/>
-    </row>
-    <row r="514" spans="1:6">
+      <c r="G513" s="4"/>
+    </row>
+    <row r="514" spans="1:7">
       <c r="B514" s="2"/>
       <c r="D514" s="2"/>
       <c r="F514" s="2"/>
-    </row>
-    <row r="515" spans="1:6">
+      <c r="G514" s="4"/>
+    </row>
+    <row r="515" spans="1:7">
       <c r="B515" s="2"/>
       <c r="D515" s="2"/>
       <c r="F515" s="2"/>
-    </row>
-    <row r="516" spans="1:6">
+      <c r="G515" s="4"/>
+    </row>
+    <row r="516" spans="1:7">
       <c r="B516" s="2"/>
       <c r="D516" s="2"/>
       <c r="F516" s="2"/>
-    </row>
-    <row r="517" spans="1:6">
+      <c r="G516" s="4"/>
+    </row>
+    <row r="517" spans="1:7">
       <c r="B517" s="2"/>
       <c r="D517" s="2"/>
       <c r="F517" s="2"/>
-    </row>
-    <row r="518" spans="1:6">
+      <c r="G517" s="4"/>
+    </row>
+    <row r="518" spans="1:7">
       <c r="B518" s="2"/>
       <c r="D518" s="2"/>
       <c r="F518" s="2"/>
-    </row>
-    <row r="519" spans="1:6">
+      <c r="G518" s="4"/>
+    </row>
+    <row r="519" spans="1:7">
       <c r="B519" s="2"/>
       <c r="D519" s="2"/>
       <c r="F519" s="2"/>
-    </row>
-    <row r="520" spans="1:6">
+      <c r="G519" s="4"/>
+    </row>
+    <row r="520" spans="1:7">
       <c r="B520" s="2"/>
       <c r="D520" s="2"/>
       <c r="F520" s="2"/>
-    </row>
-    <row r="521" spans="1:6">
+      <c r="G520" s="4"/>
+    </row>
+    <row r="521" spans="1:7">
       <c r="B521" s="2"/>
       <c r="D521" s="2"/>
       <c r="F521" s="2"/>
-    </row>
-    <row r="522" spans="1:6">
+      <c r="G521" s="4"/>
+    </row>
+    <row r="522" spans="1:7">
       <c r="B522" s="2"/>
       <c r="D522" s="2"/>
       <c r="F522" s="2"/>
-    </row>
-    <row r="523" spans="1:6">
+      <c r="G522" s="4"/>
+    </row>
+    <row r="523" spans="1:7">
       <c r="B523" s="2"/>
       <c r="D523" s="2"/>
       <c r="F523" s="2"/>
-    </row>
-    <row r="524" spans="1:6">
+      <c r="G523" s="4"/>
+    </row>
+    <row r="524" spans="1:7">
       <c r="B524" s="2"/>
       <c r="D524" s="2"/>
       <c r="F524" s="2"/>
-    </row>
-    <row r="525" spans="1:6">
+      <c r="G524" s="4"/>
+    </row>
+    <row r="525" spans="1:7">
       <c r="B525" s="2"/>
       <c r="D525" s="2"/>
       <c r="F525" s="2"/>
-    </row>
-    <row r="526" spans="1:6">
+      <c r="G525" s="4"/>
+    </row>
+    <row r="526" spans="1:7">
       <c r="B526" s="2"/>
       <c r="D526" s="2"/>
       <c r="F526" s="2"/>
-    </row>
-    <row r="527" spans="1:6">
+      <c r="G526" s="4"/>
+    </row>
+    <row r="527" spans="1:7">
       <c r="B527" s="2"/>
       <c r="D527" s="2"/>
       <c r="F527" s="2"/>
-    </row>
-    <row r="528" spans="1:6">
+      <c r="G527" s="4"/>
+    </row>
+    <row r="528" spans="1:7">
       <c r="B528" s="2"/>
       <c r="D528" s="2"/>
       <c r="F528" s="2"/>
-    </row>
-    <row r="529" spans="1:6">
+      <c r="G528" s="4"/>
+    </row>
+    <row r="529" spans="1:7">
       <c r="B529" s="2"/>
       <c r="D529" s="2"/>
       <c r="F529" s="2"/>
-    </row>
-    <row r="530" spans="1:6">
+      <c r="G529" s="4"/>
+    </row>
+    <row r="530" spans="1:7">
       <c r="B530" s="2"/>
       <c r="D530" s="2"/>
       <c r="F530" s="2"/>
-    </row>
-    <row r="531" spans="1:6">
+      <c r="G530" s="4"/>
+    </row>
+    <row r="531" spans="1:7">
       <c r="B531" s="2"/>
       <c r="D531" s="2"/>
       <c r="F531" s="2"/>
-    </row>
-    <row r="532" spans="1:6">
+      <c r="G531" s="4"/>
+    </row>
+    <row r="532" spans="1:7">
       <c r="B532" s="2"/>
       <c r="D532" s="2"/>
       <c r="F532" s="2"/>
-    </row>
-    <row r="533" spans="1:6">
+      <c r="G532" s="4"/>
+    </row>
+    <row r="533" spans="1:7">
       <c r="B533" s="2"/>
       <c r="D533" s="2"/>
       <c r="F533" s="2"/>
-    </row>
-    <row r="534" spans="1:6">
+      <c r="G533" s="4"/>
+    </row>
+    <row r="534" spans="1:7">
       <c r="B534" s="2"/>
       <c r="D534" s="2"/>
       <c r="F534" s="2"/>
-    </row>
-    <row r="535" spans="1:6">
+      <c r="G534" s="4"/>
+    </row>
+    <row r="535" spans="1:7">
       <c r="B535" s="2"/>
       <c r="D535" s="2"/>
       <c r="F535" s="2"/>
-    </row>
-    <row r="536" spans="1:6">
+      <c r="G535" s="4"/>
+    </row>
+    <row r="536" spans="1:7">
       <c r="B536" s="2"/>
       <c r="D536" s="2"/>
       <c r="F536" s="2"/>
-    </row>
-    <row r="537" spans="1:6">
+      <c r="G536" s="4"/>
+    </row>
+    <row r="537" spans="1:7">
       <c r="B537" s="2"/>
       <c r="D537" s="2"/>
       <c r="F537" s="2"/>
-    </row>
-    <row r="538" spans="1:6">
+      <c r="G537" s="4"/>
+    </row>
+    <row r="538" spans="1:7">
       <c r="B538" s="2"/>
       <c r="D538" s="2"/>
       <c r="F538" s="2"/>
-    </row>
-    <row r="539" spans="1:6">
+      <c r="G538" s="4"/>
+    </row>
+    <row r="539" spans="1:7">
       <c r="B539" s="2"/>
       <c r="D539" s="2"/>
       <c r="F539" s="2"/>
-    </row>
-    <row r="540" spans="1:6">
+      <c r="G539" s="4"/>
+    </row>
+    <row r="540" spans="1:7">
       <c r="B540" s="2"/>
       <c r="D540" s="2"/>
       <c r="F540" s="2"/>
-    </row>
-    <row r="541" spans="1:6">
+      <c r="G540" s="4"/>
+    </row>
+    <row r="541" spans="1:7">
       <c r="B541" s="2"/>
       <c r="D541" s="2"/>
       <c r="F541" s="2"/>
-    </row>
-    <row r="542" spans="1:6">
+      <c r="G541" s="4"/>
+    </row>
+    <row r="542" spans="1:7">
       <c r="B542" s="2"/>
       <c r="D542" s="2"/>
       <c r="F542" s="2"/>
-    </row>
-    <row r="543" spans="1:6">
+      <c r="G542" s="4"/>
+    </row>
+    <row r="543" spans="1:7">
       <c r="B543" s="2"/>
       <c r="D543" s="2"/>
       <c r="F543" s="2"/>
-    </row>
-    <row r="544" spans="1:6">
+      <c r="G543" s="4"/>
+    </row>
+    <row r="544" spans="1:7">
       <c r="B544" s="2"/>
       <c r="D544" s="2"/>
       <c r="F544" s="2"/>
-    </row>
-    <row r="545" spans="1:6">
+      <c r="G544" s="4"/>
+    </row>
+    <row r="545" spans="1:7">
       <c r="B545" s="2"/>
       <c r="D545" s="2"/>
       <c r="F545" s="2"/>
-    </row>
-    <row r="546" spans="1:6">
+      <c r="G545" s="4"/>
+    </row>
+    <row r="546" spans="1:7">
       <c r="B546" s="2"/>
       <c r="D546" s="2"/>
       <c r="F546" s="2"/>
-    </row>
-    <row r="547" spans="1:6">
+      <c r="G546" s="4"/>
+    </row>
+    <row r="547" spans="1:7">
       <c r="B547" s="2"/>
       <c r="D547" s="2"/>
       <c r="F547" s="2"/>
-    </row>
-    <row r="548" spans="1:6">
+      <c r="G547" s="4"/>
+    </row>
+    <row r="548" spans="1:7">
       <c r="B548" s="2"/>
       <c r="D548" s="2"/>
       <c r="F548" s="2"/>
-    </row>
-    <row r="549" spans="1:6">
+      <c r="G548" s="4"/>
+    </row>
+    <row r="549" spans="1:7">
       <c r="B549" s="2"/>
       <c r="D549" s="2"/>
       <c r="F549" s="2"/>
-    </row>
-    <row r="550" spans="1:6">
+      <c r="G549" s="4"/>
+    </row>
+    <row r="550" spans="1:7">
       <c r="B550" s="2"/>
       <c r="D550" s="2"/>
       <c r="F550" s="2"/>
-    </row>
-    <row r="551" spans="1:6">
+      <c r="G550" s="4"/>
+    </row>
+    <row r="551" spans="1:7">
       <c r="B551" s="2"/>
       <c r="D551" s="2"/>
       <c r="F551" s="2"/>
-    </row>
-    <row r="552" spans="1:6">
+      <c r="G551" s="4"/>
+    </row>
+    <row r="552" spans="1:7">
       <c r="B552" s="2"/>
       <c r="D552" s="2"/>
       <c r="F552" s="2"/>
-    </row>
-    <row r="553" spans="1:6">
+      <c r="G552" s="4"/>
+    </row>
+    <row r="553" spans="1:7">
       <c r="B553" s="2"/>
       <c r="D553" s="2"/>
       <c r="F553" s="2"/>
-    </row>
-    <row r="554" spans="1:6">
+      <c r="G553" s="4"/>
+    </row>
+    <row r="554" spans="1:7">
       <c r="B554" s="2"/>
       <c r="D554" s="2"/>
       <c r="F554" s="2"/>
-    </row>
-    <row r="555" spans="1:6">
+      <c r="G554" s="4"/>
+    </row>
+    <row r="555" spans="1:7">
       <c r="B555" s="2"/>
       <c r="D555" s="2"/>
       <c r="F555" s="2"/>
-    </row>
-    <row r="556" spans="1:6">
+      <c r="G555" s="4"/>
+    </row>
+    <row r="556" spans="1:7">
       <c r="B556" s="2"/>
       <c r="D556" s="2"/>
       <c r="F556" s="2"/>
-    </row>
-    <row r="557" spans="1:6">
+      <c r="G556" s="4"/>
+    </row>
+    <row r="557" spans="1:7">
       <c r="B557" s="2"/>
       <c r="D557" s="2"/>
       <c r="F557" s="2"/>
-    </row>
-    <row r="558" spans="1:6">
+      <c r="G557" s="4"/>
+    </row>
+    <row r="558" spans="1:7">
       <c r="B558" s="2"/>
       <c r="D558" s="2"/>
       <c r="F558" s="2"/>
-    </row>
-    <row r="559" spans="1:6">
+      <c r="G558" s="4"/>
+    </row>
+    <row r="559" spans="1:7">
       <c r="B559" s="2"/>
       <c r="D559" s="2"/>
       <c r="F559" s="2"/>
-    </row>
-    <row r="560" spans="1:6">
+      <c r="G559" s="4"/>
+    </row>
+    <row r="560" spans="1:7">
       <c r="B560" s="2"/>
       <c r="D560" s="2"/>
       <c r="F560" s="2"/>
-    </row>
-    <row r="561" spans="1:6">
+      <c r="G560" s="4"/>
+    </row>
+    <row r="561" spans="1:7">
       <c r="B561" s="2"/>
       <c r="D561" s="2"/>
       <c r="F561" s="2"/>
-    </row>
-    <row r="562" spans="1:6">
+      <c r="G561" s="4"/>
+    </row>
+    <row r="562" spans="1:7">
       <c r="B562" s="2"/>
       <c r="D562" s="2"/>
       <c r="F562" s="2"/>
-    </row>
-    <row r="563" spans="1:6">
+      <c r="G562" s="4"/>
+    </row>
+    <row r="563" spans="1:7">
       <c r="B563" s="2"/>
       <c r="D563" s="2"/>
       <c r="F563" s="2"/>
-    </row>
-    <row r="564" spans="1:6">
+      <c r="G563" s="4"/>
+    </row>
+    <row r="564" spans="1:7">
       <c r="B564" s="2"/>
       <c r="D564" s="2"/>
       <c r="F564" s="2"/>
-    </row>
-    <row r="565" spans="1:6">
+      <c r="G564" s="4"/>
+    </row>
+    <row r="565" spans="1:7">
       <c r="B565" s="2"/>
       <c r="D565" s="2"/>
       <c r="F565" s="2"/>
-    </row>
-    <row r="566" spans="1:6">
+      <c r="G565" s="4"/>
+    </row>
+    <row r="566" spans="1:7">
       <c r="B566" s="2"/>
       <c r="D566" s="2"/>
       <c r="F566" s="2"/>
-    </row>
-    <row r="567" spans="1:6">
+      <c r="G566" s="4"/>
+    </row>
+    <row r="567" spans="1:7">
       <c r="B567" s="2"/>
       <c r="D567" s="2"/>
       <c r="F567" s="2"/>
-    </row>
-    <row r="568" spans="1:6">
+      <c r="G567" s="4"/>
+    </row>
+    <row r="568" spans="1:7">
       <c r="B568" s="2"/>
       <c r="D568" s="2"/>
       <c r="F568" s="2"/>
-    </row>
-    <row r="569" spans="1:6">
+      <c r="G568" s="4"/>
+    </row>
+    <row r="569" spans="1:7">
       <c r="B569" s="2"/>
       <c r="D569" s="2"/>
       <c r="F569" s="2"/>
-    </row>
-    <row r="570" spans="1:6">
+      <c r="G569" s="4"/>
+    </row>
+    <row r="570" spans="1:7">
       <c r="B570" s="2"/>
       <c r="D570" s="2"/>
       <c r="F570" s="2"/>
-    </row>
-    <row r="571" spans="1:6">
+      <c r="G570" s="4"/>
+    </row>
+    <row r="571" spans="1:7">
       <c r="B571" s="2"/>
       <c r="D571" s="2"/>
       <c r="F571" s="2"/>
-    </row>
-    <row r="572" spans="1:6">
+      <c r="G571" s="4"/>
+    </row>
+    <row r="572" spans="1:7">
       <c r="B572" s="2"/>
       <c r="D572" s="2"/>
       <c r="F572" s="2"/>
-    </row>
-    <row r="573" spans="1:6">
+      <c r="G572" s="4"/>
+    </row>
+    <row r="573" spans="1:7">
       <c r="B573" s="2"/>
       <c r="D573" s="2"/>
       <c r="F573" s="2"/>
-    </row>
-    <row r="574" spans="1:6">
+      <c r="G573" s="4"/>
+    </row>
+    <row r="574" spans="1:7">
       <c r="B574" s="2"/>
       <c r="D574" s="2"/>
       <c r="F574" s="2"/>
-    </row>
-    <row r="575" spans="1:6">
+      <c r="G574" s="4"/>
+    </row>
+    <row r="575" spans="1:7">
       <c r="B575" s="2"/>
       <c r="D575" s="2"/>
       <c r="F575" s="2"/>
-    </row>
-    <row r="576" spans="1:6">
+      <c r="G575" s="4"/>
+    </row>
+    <row r="576" spans="1:7">
       <c r="B576" s="2"/>
       <c r="D576" s="2"/>
       <c r="F576" s="2"/>
-    </row>
-    <row r="577" spans="1:6">
+      <c r="G576" s="4"/>
+    </row>
+    <row r="577" spans="1:7">
       <c r="B577" s="2"/>
       <c r="D577" s="2"/>
       <c r="F577" s="2"/>
-    </row>
-    <row r="578" spans="1:6">
+      <c r="G577" s="4"/>
+    </row>
+    <row r="578" spans="1:7">
       <c r="B578" s="2"/>
       <c r="D578" s="2"/>
       <c r="F578" s="2"/>
-    </row>
-    <row r="579" spans="1:6">
+      <c r="G578" s="4"/>
+    </row>
+    <row r="579" spans="1:7">
       <c r="B579" s="2"/>
       <c r="D579" s="2"/>
       <c r="F579" s="2"/>
-    </row>
-    <row r="580" spans="1:6">
+      <c r="G579" s="4"/>
+    </row>
+    <row r="580" spans="1:7">
       <c r="B580" s="2"/>
       <c r="D580" s="2"/>
       <c r="F580" s="2"/>
-    </row>
-    <row r="581" spans="1:6">
+      <c r="G580" s="4"/>
+    </row>
+    <row r="581" spans="1:7">
       <c r="B581" s="2"/>
       <c r="D581" s="2"/>
       <c r="F581" s="2"/>
-    </row>
-    <row r="582" spans="1:6">
+      <c r="G581" s="4"/>
+    </row>
+    <row r="582" spans="1:7">
       <c r="B582" s="2"/>
       <c r="D582" s="2"/>
       <c r="F582" s="2"/>
-    </row>
-    <row r="583" spans="1:6">
+      <c r="G582" s="4"/>
+    </row>
+    <row r="583" spans="1:7">
       <c r="B583" s="2"/>
       <c r="D583" s="2"/>
       <c r="F583" s="2"/>
-    </row>
-    <row r="584" spans="1:6">
+      <c r="G583" s="4"/>
+    </row>
+    <row r="584" spans="1:7">
       <c r="B584" s="2"/>
       <c r="D584" s="2"/>
       <c r="F584" s="2"/>
-    </row>
-    <row r="585" spans="1:6">
+      <c r="G584" s="4"/>
+    </row>
+    <row r="585" spans="1:7">
       <c r="B585" s="2"/>
       <c r="D585" s="2"/>
       <c r="F585" s="2"/>
-    </row>
-    <row r="586" spans="1:6">
+      <c r="G585" s="4"/>
+    </row>
+    <row r="586" spans="1:7">
       <c r="B586" s="2"/>
       <c r="D586" s="2"/>
       <c r="F586" s="2"/>
-    </row>
-    <row r="587" spans="1:6">
+      <c r="G586" s="4"/>
+    </row>
+    <row r="587" spans="1:7">
       <c r="B587" s="2"/>
       <c r="D587" s="2"/>
       <c r="F587" s="2"/>
-    </row>
-    <row r="588" spans="1:6">
+      <c r="G587" s="4"/>
+    </row>
+    <row r="588" spans="1:7">
       <c r="B588" s="2"/>
       <c r="D588" s="2"/>
       <c r="F588" s="2"/>
-    </row>
-    <row r="589" spans="1:6">
+      <c r="G588" s="4"/>
+    </row>
+    <row r="589" spans="1:7">
       <c r="B589" s="2"/>
       <c r="D589" s="2"/>
       <c r="F589" s="2"/>
-    </row>
-    <row r="590" spans="1:6">
+      <c r="G589" s="4"/>
+    </row>
+    <row r="590" spans="1:7">
       <c r="B590" s="2"/>
       <c r="D590" s="2"/>
       <c r="F590" s="2"/>
-    </row>
-    <row r="591" spans="1:6">
+      <c r="G590" s="4"/>
+    </row>
+    <row r="591" spans="1:7">
       <c r="B591" s="2"/>
       <c r="D591" s="2"/>
       <c r="F591" s="2"/>
-    </row>
-    <row r="592" spans="1:6">
+      <c r="G591" s="4"/>
+    </row>
+    <row r="592" spans="1:7">
       <c r="B592" s="2"/>
       <c r="D592" s="2"/>
       <c r="F592" s="2"/>
-    </row>
-    <row r="593" spans="1:6">
+      <c r="G592" s="4"/>
+    </row>
+    <row r="593" spans="1:7">
       <c r="B593" s="2"/>
       <c r="D593" s="2"/>
       <c r="F593" s="2"/>
-    </row>
-    <row r="594" spans="1:6">
+      <c r="G593" s="4"/>
+    </row>
+    <row r="594" spans="1:7">
       <c r="B594" s="2"/>
       <c r="D594" s="2"/>
       <c r="F594" s="2"/>
-    </row>
-    <row r="595" spans="1:6">
+      <c r="G594" s="4"/>
+    </row>
+    <row r="595" spans="1:7">
       <c r="B595" s="2"/>
       <c r="D595" s="2"/>
       <c r="F595" s="2"/>
-    </row>
-    <row r="596" spans="1:6">
+      <c r="G595" s="4"/>
+    </row>
+    <row r="596" spans="1:7">
       <c r="B596" s="2"/>
       <c r="D596" s="2"/>
       <c r="F596" s="2"/>
-    </row>
-    <row r="597" spans="1:6">
+      <c r="G596" s="4"/>
+    </row>
+    <row r="597" spans="1:7">
       <c r="B597" s="2"/>
       <c r="D597" s="2"/>
       <c r="F597" s="2"/>
-    </row>
-    <row r="598" spans="1:6">
+      <c r="G597" s="4"/>
+    </row>
+    <row r="598" spans="1:7">
       <c r="B598" s="2"/>
       <c r="D598" s="2"/>
       <c r="F598" s="2"/>
-    </row>
-    <row r="599" spans="1:6">
+      <c r="G598" s="4"/>
+    </row>
+    <row r="599" spans="1:7">
       <c r="B599" s="2"/>
       <c r="D599" s="2"/>
       <c r="F599" s="2"/>
-    </row>
-    <row r="600" spans="1:6">
+      <c r="G599" s="4"/>
+    </row>
+    <row r="600" spans="1:7">
       <c r="B600" s="2"/>
       <c r="D600" s="2"/>
       <c r="F600" s="2"/>
-    </row>
-    <row r="601" spans="1:6">
+      <c r="G600" s="4"/>
+    </row>
+    <row r="601" spans="1:7">
       <c r="B601" s="2"/>
       <c r="D601" s="2"/>
       <c r="F601" s="2"/>
-    </row>
-    <row r="602" spans="1:6">
+      <c r="G601" s="4"/>
+    </row>
+    <row r="602" spans="1:7">
       <c r="B602" s="2"/>
       <c r="D602" s="2"/>
       <c r="F602" s="2"/>
-    </row>
-    <row r="603" spans="1:6">
+      <c r="G602" s="4"/>
+    </row>
+    <row r="603" spans="1:7">
       <c r="B603" s="2"/>
       <c r="D603" s="2"/>
       <c r="F603" s="2"/>
-    </row>
-    <row r="604" spans="1:6">
+      <c r="G603" s="4"/>
+    </row>
+    <row r="604" spans="1:7">
       <c r="B604" s="2"/>
       <c r="D604" s="2"/>
       <c r="F604" s="2"/>
-    </row>
-    <row r="605" spans="1:6">
+      <c r="G604" s="4"/>
+    </row>
+    <row r="605" spans="1:7">
       <c r="B605" s="2"/>
       <c r="D605" s="2"/>
       <c r="F605" s="2"/>
-    </row>
-    <row r="606" spans="1:6">
+      <c r="G605" s="4"/>
+    </row>
+    <row r="606" spans="1:7">
       <c r="B606" s="2"/>
       <c r="D606" s="2"/>
       <c r="F606" s="2"/>
-    </row>
-    <row r="607" spans="1:6">
+      <c r="G606" s="4"/>
+    </row>
+    <row r="607" spans="1:7">
       <c r="B607" s="2"/>
       <c r="D607" s="2"/>
       <c r="F607" s="2"/>
-    </row>
-    <row r="608" spans="1:6">
+      <c r="G607" s="4"/>
+    </row>
+    <row r="608" spans="1:7">
       <c r="B608" s="2"/>
       <c r="D608" s="2"/>
       <c r="F608" s="2"/>
-    </row>
-    <row r="609" spans="1:6">
+      <c r="G608" s="4"/>
+    </row>
+    <row r="609" spans="1:7">
       <c r="B609" s="2"/>
       <c r="D609" s="2"/>
       <c r="F609" s="2"/>
-    </row>
-    <row r="610" spans="1:6">
+      <c r="G609" s="4"/>
+    </row>
+    <row r="610" spans="1:7">
       <c r="B610" s="2"/>
       <c r="D610" s="2"/>
       <c r="F610" s="2"/>
-    </row>
-    <row r="611" spans="1:6">
+      <c r="G610" s="4"/>
+    </row>
+    <row r="611" spans="1:7">
       <c r="B611" s="2"/>
       <c r="D611" s="2"/>
       <c r="F611" s="2"/>
-    </row>
-    <row r="612" spans="1:6">
+      <c r="G611" s="4"/>
+    </row>
+    <row r="612" spans="1:7">
       <c r="B612" s="2"/>
       <c r="D612" s="2"/>
       <c r="F612" s="2"/>
-    </row>
-    <row r="613" spans="1:6">
+      <c r="G612" s="4"/>
+    </row>
+    <row r="613" spans="1:7">
       <c r="B613" s="2"/>
       <c r="D613" s="2"/>
       <c r="F613" s="2"/>
-    </row>
-    <row r="614" spans="1:6">
+      <c r="G613" s="4"/>
+    </row>
+    <row r="614" spans="1:7">
       <c r="B614" s="2"/>
       <c r="D614" s="2"/>
       <c r="F614" s="2"/>
-    </row>
-    <row r="615" spans="1:6">
+      <c r="G614" s="4"/>
+    </row>
+    <row r="615" spans="1:7">
       <c r="B615" s="2"/>
       <c r="D615" s="2"/>
       <c r="F615" s="2"/>
-    </row>
-    <row r="616" spans="1:6">
+      <c r="G615" s="4"/>
+    </row>
+    <row r="616" spans="1:7">
       <c r="B616" s="2"/>
       <c r="D616" s="2"/>
       <c r="F616" s="2"/>
-    </row>
-    <row r="617" spans="1:6">
+      <c r="G616" s="4"/>
+    </row>
+    <row r="617" spans="1:7">
       <c r="B617" s="2"/>
       <c r="D617" s="2"/>
       <c r="F617" s="2"/>
-    </row>
-    <row r="618" spans="1:6">
+      <c r="G617" s="4"/>
+    </row>
+    <row r="618" spans="1:7">
       <c r="B618" s="2"/>
       <c r="D618" s="2"/>
       <c r="F618" s="2"/>
-    </row>
-    <row r="619" spans="1:6">
+      <c r="G618" s="4"/>
+    </row>
+    <row r="619" spans="1:7">
       <c r="B619" s="2"/>
       <c r="D619" s="2"/>
       <c r="F619" s="2"/>
-    </row>
-    <row r="620" spans="1:6">
+      <c r="G619" s="4"/>
+    </row>
+    <row r="620" spans="1:7">
       <c r="B620" s="2"/>
       <c r="D620" s="2"/>
       <c r="F620" s="2"/>
-    </row>
-    <row r="621" spans="1:6">
+      <c r="G620" s="4"/>
+    </row>
+    <row r="621" spans="1:7">
       <c r="B621" s="2"/>
       <c r="D621" s="2"/>
       <c r="F621" s="2"/>
-    </row>
-    <row r="622" spans="1:6">
+      <c r="G621" s="4"/>
+    </row>
+    <row r="622" spans="1:7">
       <c r="B622" s="2"/>
       <c r="D622" s="2"/>
       <c r="F622" s="2"/>
-    </row>
-    <row r="623" spans="1:6">
+      <c r="G622" s="4"/>
+    </row>
+    <row r="623" spans="1:7">
       <c r="B623" s="2"/>
       <c r="D623" s="2"/>
       <c r="F623" s="2"/>
-    </row>
-    <row r="624" spans="1:6">
+      <c r="G623" s="4"/>
+    </row>
+    <row r="624" spans="1:7">
       <c r="B624" s="2"/>
       <c r="D624" s="2"/>
       <c r="F624" s="2"/>
-    </row>
-    <row r="625" spans="1:6">
+      <c r="G624" s="4"/>
+    </row>
+    <row r="625" spans="1:7">
       <c r="B625" s="2"/>
       <c r="D625" s="2"/>
       <c r="F625" s="2"/>
-    </row>
-    <row r="626" spans="1:6">
+      <c r="G625" s="4"/>
+    </row>
+    <row r="626" spans="1:7">
       <c r="B626" s="2"/>
       <c r="D626" s="2"/>
       <c r="F626" s="2"/>
-    </row>
-    <row r="627" spans="1:6">
+      <c r="G626" s="4"/>
+    </row>
+    <row r="627" spans="1:7">
       <c r="B627" s="2"/>
       <c r="D627" s="2"/>
       <c r="F627" s="2"/>
-    </row>
-    <row r="628" spans="1:6">
+      <c r="G627" s="4"/>
+    </row>
+    <row r="628" spans="1:7">
       <c r="B628" s="2"/>
       <c r="D628" s="2"/>
       <c r="F628" s="2"/>
-    </row>
-    <row r="629" spans="1:6">
+      <c r="G628" s="4"/>
+    </row>
+    <row r="629" spans="1:7">
       <c r="B629" s="2"/>
       <c r="D629" s="2"/>
       <c r="F629" s="2"/>
-    </row>
-    <row r="630" spans="1:6">
+      <c r="G629" s="4"/>
+    </row>
+    <row r="630" spans="1:7">
       <c r="B630" s="2"/>
       <c r="D630" s="2"/>
       <c r="F630" s="2"/>
-    </row>
-    <row r="631" spans="1:6">
+      <c r="G630" s="4"/>
+    </row>
+    <row r="631" spans="1:7">
       <c r="B631" s="2"/>
       <c r="D631" s="2"/>
       <c r="F631" s="2"/>
-    </row>
-    <row r="632" spans="1:6">
+      <c r="G631" s="4"/>
+    </row>
+    <row r="632" spans="1:7">
       <c r="B632" s="2"/>
       <c r="D632" s="2"/>
       <c r="F632" s="2"/>
-    </row>
-    <row r="633" spans="1:6">
+      <c r="G632" s="4"/>
+    </row>
+    <row r="633" spans="1:7">
       <c r="B633" s="2"/>
       <c r="D633" s="2"/>
       <c r="F633" s="2"/>
-    </row>
-    <row r="634" spans="1:6">
+      <c r="G633" s="4"/>
+    </row>
+    <row r="634" spans="1:7">
       <c r="B634" s="2"/>
       <c r="D634" s="2"/>
       <c r="F634" s="2"/>
-    </row>
-    <row r="635" spans="1:6">
+      <c r="G634" s="4"/>
+    </row>
+    <row r="635" spans="1:7">
       <c r="B635" s="2"/>
       <c r="D635" s="2"/>
       <c r="F635" s="2"/>
-    </row>
-    <row r="636" spans="1:6">
+      <c r="G635" s="4"/>
+    </row>
+    <row r="636" spans="1:7">
       <c r="B636" s="2"/>
       <c r="D636" s="2"/>
       <c r="F636" s="2"/>
-    </row>
-    <row r="637" spans="1:6">
+      <c r="G636" s="4"/>
+    </row>
+    <row r="637" spans="1:7">
       <c r="B637" s="2"/>
       <c r="D637" s="2"/>
       <c r="F637" s="2"/>
-    </row>
-    <row r="638" spans="1:6">
+      <c r="G637" s="4"/>
+    </row>
+    <row r="638" spans="1:7">
       <c r="B638" s="2"/>
       <c r="D638" s="2"/>
       <c r="F638" s="2"/>
-    </row>
-    <row r="639" spans="1:6">
+      <c r="G638" s="4"/>
+    </row>
+    <row r="639" spans="1:7">
       <c r="B639" s="2"/>
       <c r="D639" s="2"/>
       <c r="F639" s="2"/>
-    </row>
-    <row r="640" spans="1:6">
+      <c r="G639" s="4"/>
+    </row>
+    <row r="640" spans="1:7">
       <c r="B640" s="2"/>
       <c r="D640" s="2"/>
       <c r="F640" s="2"/>
-    </row>
-    <row r="641" spans="1:6">
+      <c r="G640" s="4"/>
+    </row>
+    <row r="641" spans="1:7">
       <c r="B641" s="2"/>
       <c r="D641" s="2"/>
       <c r="F641" s="2"/>
-    </row>
-    <row r="642" spans="1:6">
+      <c r="G641" s="4"/>
+    </row>
+    <row r="642" spans="1:7">
       <c r="B642" s="2"/>
       <c r="D642" s="2"/>
       <c r="F642" s="2"/>
-    </row>
-    <row r="643" spans="1:6">
+      <c r="G642" s="4"/>
+    </row>
+    <row r="643" spans="1:7">
       <c r="B643" s="2"/>
       <c r="D643" s="2"/>
       <c r="F643" s="2"/>
-    </row>
-    <row r="644" spans="1:6">
+      <c r="G643" s="4"/>
+    </row>
+    <row r="644" spans="1:7">
       <c r="B644" s="2"/>
       <c r="D644" s="2"/>
       <c r="F644" s="2"/>
-    </row>
-    <row r="645" spans="1:6">
+      <c r="G644" s="4"/>
+    </row>
+    <row r="645" spans="1:7">
       <c r="B645" s="2"/>
       <c r="D645" s="2"/>
       <c r="F645" s="2"/>
-    </row>
-    <row r="646" spans="1:6">
+      <c r="G645" s="4"/>
+    </row>
+    <row r="646" spans="1:7">
       <c r="B646" s="2"/>
       <c r="D646" s="2"/>
       <c r="F646" s="2"/>
-    </row>
-    <row r="647" spans="1:6">
+      <c r="G646" s="4"/>
+    </row>
+    <row r="647" spans="1:7">
       <c r="B647" s="2"/>
       <c r="D647" s="2"/>
       <c r="F647" s="2"/>
-    </row>
-    <row r="648" spans="1:6">
+      <c r="G647" s="4"/>
+    </row>
+    <row r="648" spans="1:7">
       <c r="B648" s="2"/>
       <c r="D648" s="2"/>
       <c r="F648" s="2"/>
-    </row>
-    <row r="649" spans="1:6">
+      <c r="G648" s="4"/>
+    </row>
+    <row r="649" spans="1:7">
       <c r="B649" s="2"/>
       <c r="D649" s="2"/>
       <c r="F649" s="2"/>
-    </row>
-    <row r="650" spans="1:6">
+      <c r="G649" s="4"/>
+    </row>
+    <row r="650" spans="1:7">
       <c r="B650" s="2"/>
       <c r="D650" s="2"/>
       <c r="F650" s="2"/>
-    </row>
-    <row r="651" spans="1:6">
+      <c r="G650" s="4"/>
+    </row>
+    <row r="651" spans="1:7">
       <c r="B651" s="2"/>
       <c r="D651" s="2"/>
       <c r="F651" s="2"/>
-    </row>
-    <row r="652" spans="1:6">
+      <c r="G651" s="4"/>
+    </row>
+    <row r="652" spans="1:7">
       <c r="B652" s="2"/>
       <c r="D652" s="2"/>
       <c r="F652" s="2"/>
-    </row>
-    <row r="653" spans="1:6">
+      <c r="G652" s="4"/>
+    </row>
+    <row r="653" spans="1:7">
       <c r="B653" s="2"/>
       <c r="D653" s="2"/>
       <c r="F653" s="2"/>
-    </row>
-    <row r="654" spans="1:6">
+      <c r="G653" s="4"/>
+    </row>
+    <row r="654" spans="1:7">
       <c r="B654" s="2"/>
       <c r="D654" s="2"/>
       <c r="F654" s="2"/>
-    </row>
-    <row r="655" spans="1:6">
+      <c r="G654" s="4"/>
+    </row>
+    <row r="655" spans="1:7">
       <c r="B655" s="2"/>
       <c r="D655" s="2"/>
       <c r="F655" s="2"/>
-    </row>
-    <row r="656" spans="1:6">
+      <c r="G655" s="4"/>
+    </row>
+    <row r="656" spans="1:7">
       <c r="B656" s="2"/>
       <c r="D656" s="2"/>
       <c r="F656" s="2"/>
-    </row>
-    <row r="657" spans="1:6">
+      <c r="G656" s="4"/>
+    </row>
+    <row r="657" spans="1:7">
       <c r="B657" s="2"/>
       <c r="D657" s="2"/>
       <c r="F657" s="2"/>
-    </row>
-    <row r="658" spans="1:6">
+      <c r="G657" s="4"/>
+    </row>
+    <row r="658" spans="1:7">
       <c r="B658" s="2"/>
       <c r="D658" s="2"/>
       <c r="F658" s="2"/>
-    </row>
-    <row r="659" spans="1:6">
+      <c r="G658" s="4"/>
+    </row>
+    <row r="659" spans="1:7">
       <c r="B659" s="2"/>
       <c r="D659" s="2"/>
       <c r="F659" s="2"/>
-    </row>
-    <row r="660" spans="1:6">
+      <c r="G659" s="4"/>
+    </row>
+    <row r="660" spans="1:7">
       <c r="B660" s="2"/>
       <c r="D660" s="2"/>
       <c r="F660" s="2"/>
-    </row>
-    <row r="661" spans="1:6">
+      <c r="G660" s="4"/>
+    </row>
+    <row r="661" spans="1:7">
       <c r="B661" s="2"/>
       <c r="D661" s="2"/>
       <c r="F661" s="2"/>
-    </row>
-    <row r="662" spans="1:6">
+      <c r="G661" s="4"/>
+    </row>
+    <row r="662" spans="1:7">
       <c r="B662" s="2"/>
       <c r="D662" s="2"/>
       <c r="F662" s="2"/>
-    </row>
-    <row r="663" spans="1:6">
+      <c r="G662" s="4"/>
+    </row>
+    <row r="663" spans="1:7">
       <c r="B663" s="2"/>
       <c r="D663" s="2"/>
       <c r="F663" s="2"/>
-    </row>
-    <row r="664" spans="1:6">
+      <c r="G663" s="4"/>
+    </row>
+    <row r="664" spans="1:7">
       <c r="B664" s="2"/>
       <c r="D664" s="2"/>
       <c r="F664" s="2"/>
-    </row>
-    <row r="665" spans="1:6">
+      <c r="G664" s="4"/>
+    </row>
+    <row r="665" spans="1:7">
       <c r="B665" s="2"/>
       <c r="D665" s="2"/>
       <c r="F665" s="2"/>
-    </row>
-    <row r="666" spans="1:6">
+      <c r="G665" s="4"/>
+    </row>
+    <row r="666" spans="1:7">
       <c r="B666" s="2"/>
       <c r="D666" s="2"/>
       <c r="F666" s="2"/>
-    </row>
-    <row r="667" spans="1:6">
+      <c r="G666" s="4"/>
+    </row>
+    <row r="667" spans="1:7">
       <c r="B667" s="2"/>
       <c r="D667" s="2"/>
       <c r="F667" s="2"/>
-    </row>
-    <row r="668" spans="1:6">
+      <c r="G667" s="4"/>
+    </row>
+    <row r="668" spans="1:7">
       <c r="B668" s="2"/>
       <c r="D668" s="2"/>
       <c r="F668" s="2"/>
-    </row>
-    <row r="669" spans="1:6">
+      <c r="G668" s="4"/>
+    </row>
+    <row r="669" spans="1:7">
       <c r="B669" s="2"/>
       <c r="D669" s="2"/>
       <c r="F669" s="2"/>
-    </row>
-    <row r="670" spans="1:6">
+      <c r="G669" s="4"/>
+    </row>
+    <row r="670" spans="1:7">
       <c r="B670" s="2"/>
       <c r="D670" s="2"/>
       <c r="F670" s="2"/>
-    </row>
-    <row r="671" spans="1:6">
+      <c r="G670" s="4"/>
+    </row>
+    <row r="671" spans="1:7">
       <c r="B671" s="2"/>
       <c r="D671" s="2"/>
       <c r="F671" s="2"/>
-    </row>
-    <row r="672" spans="1:6">
+      <c r="G671" s="4"/>
+    </row>
+    <row r="672" spans="1:7">
       <c r="B672" s="2"/>
       <c r="D672" s="2"/>
       <c r="F672" s="2"/>
-    </row>
-    <row r="673" spans="1:6">
+      <c r="G672" s="4"/>
+    </row>
+    <row r="673" spans="1:7">
       <c r="B673" s="2"/>
       <c r="D673" s="2"/>
       <c r="F673" s="2"/>
-    </row>
-    <row r="674" spans="1:6">
+      <c r="G673" s="4"/>
+    </row>
+    <row r="674" spans="1:7">
       <c r="B674" s="2"/>
       <c r="D674" s="2"/>
       <c r="F674" s="2"/>
-    </row>
-    <row r="675" spans="1:6">
+      <c r="G674" s="4"/>
+    </row>
+    <row r="675" spans="1:7">
       <c r="B675" s="2"/>
       <c r="D675" s="2"/>
       <c r="F675" s="2"/>
-    </row>
-    <row r="676" spans="1:6">
+      <c r="G675" s="4"/>
+    </row>
+    <row r="676" spans="1:7">
       <c r="B676" s="2"/>
       <c r="D676" s="2"/>
       <c r="F676" s="2"/>
-    </row>
-    <row r="677" spans="1:6">
+      <c r="G676" s="4"/>
+    </row>
+    <row r="677" spans="1:7">
       <c r="B677" s="2"/>
       <c r="D677" s="2"/>
       <c r="F677" s="2"/>
-    </row>
-    <row r="678" spans="1:6">
+      <c r="G677" s="4"/>
+    </row>
+    <row r="678" spans="1:7">
       <c r="B678" s="2"/>
       <c r="D678" s="2"/>
       <c r="F678" s="2"/>
-    </row>
-    <row r="679" spans="1:6">
+      <c r="G678" s="4"/>
+    </row>
+    <row r="679" spans="1:7">
       <c r="B679" s="2"/>
       <c r="D679" s="2"/>
       <c r="F679" s="2"/>
-    </row>
-    <row r="680" spans="1:6">
+      <c r="G679" s="4"/>
+    </row>
+    <row r="680" spans="1:7">
       <c r="B680" s="2"/>
       <c r="D680" s="2"/>
       <c r="F680" s="2"/>
-    </row>
-    <row r="681" spans="1:6">
+      <c r="G680" s="4"/>
+    </row>
+    <row r="681" spans="1:7">
       <c r="B681" s="2"/>
       <c r="D681" s="2"/>
       <c r="F681" s="2"/>
-    </row>
-    <row r="682" spans="1:6">
+      <c r="G681" s="4"/>
+    </row>
+    <row r="682" spans="1:7">
       <c r="B682" s="2"/>
       <c r="D682" s="2"/>
       <c r="F682" s="2"/>
-    </row>
-    <row r="683" spans="1:6">
+      <c r="G682" s="4"/>
+    </row>
+    <row r="683" spans="1:7">
       <c r="B683" s="2"/>
       <c r="D683" s="2"/>
       <c r="F683" s="2"/>
-    </row>
-    <row r="684" spans="1:6">
+      <c r="G683" s="4"/>
+    </row>
+    <row r="684" spans="1:7">
       <c r="B684" s="2"/>
       <c r="D684" s="2"/>
       <c r="F684" s="2"/>
-    </row>
-    <row r="685" spans="1:6">
+      <c r="G684" s="4"/>
+    </row>
+    <row r="685" spans="1:7">
       <c r="B685" s="2"/>
       <c r="D685" s="2"/>
       <c r="F685" s="2"/>
-    </row>
-    <row r="686" spans="1:6">
+      <c r="G685" s="4"/>
+    </row>
+    <row r="686" spans="1:7">
       <c r="B686" s="2"/>
       <c r="D686" s="2"/>
       <c r="F686" s="2"/>
-    </row>
-    <row r="687" spans="1:6">
+      <c r="G686" s="4"/>
+    </row>
+    <row r="687" spans="1:7">
       <c r="B687" s="2"/>
       <c r="D687" s="2"/>
       <c r="F687" s="2"/>
-    </row>
-    <row r="688" spans="1:6">
+      <c r="G687" s="4"/>
+    </row>
+    <row r="688" spans="1:7">
       <c r="B688" s="2"/>
       <c r="D688" s="2"/>
       <c r="F688" s="2"/>
-    </row>
-    <row r="689" spans="1:6">
+      <c r="G688" s="4"/>
+    </row>
+    <row r="689" spans="1:7">
       <c r="B689" s="2"/>
       <c r="D689" s="2"/>
       <c r="F689" s="2"/>
-    </row>
-    <row r="690" spans="1:6">
+      <c r="G689" s="4"/>
+    </row>
+    <row r="690" spans="1:7">
       <c r="B690" s="2"/>
       <c r="D690" s="2"/>
       <c r="F690" s="2"/>
-    </row>
-    <row r="691" spans="1:6">
+      <c r="G690" s="4"/>
+    </row>
+    <row r="691" spans="1:7">
       <c r="B691" s="2"/>
       <c r="D691" s="2"/>
       <c r="F691" s="2"/>
-    </row>
-    <row r="692" spans="1:6">
+      <c r="G691" s="4"/>
+    </row>
+    <row r="692" spans="1:7">
       <c r="B692" s="2"/>
       <c r="D692" s="2"/>
       <c r="F692" s="2"/>
-    </row>
-    <row r="693" spans="1:6">
+      <c r="G692" s="4"/>
+    </row>
+    <row r="693" spans="1:7">
       <c r="B693" s="2"/>
       <c r="D693" s="2"/>
       <c r="F693" s="2"/>
-    </row>
-    <row r="694" spans="1:6">
+      <c r="G693" s="4"/>
+    </row>
+    <row r="694" spans="1:7">
       <c r="B694" s="2"/>
       <c r="D694" s="2"/>
       <c r="F694" s="2"/>
-    </row>
-    <row r="695" spans="1:6">
+      <c r="G694" s="4"/>
+    </row>
+    <row r="695" spans="1:7">
       <c r="B695" s="2"/>
       <c r="D695" s="2"/>
       <c r="F695" s="2"/>
-    </row>
-    <row r="696" spans="1:6">
+      <c r="G695" s="4"/>
+    </row>
+    <row r="696" spans="1:7">
       <c r="B696" s="2"/>
       <c r="D696" s="2"/>
       <c r="F696" s="2"/>
-    </row>
-    <row r="697" spans="1:6">
+      <c r="G696" s="4"/>
+    </row>
+    <row r="697" spans="1:7">
       <c r="B697" s="2"/>
       <c r="D697" s="2"/>
       <c r="F697" s="2"/>
-    </row>
-    <row r="698" spans="1:6">
+      <c r="G697" s="4"/>
+    </row>
+    <row r="698" spans="1:7">
       <c r="B698" s="2"/>
       <c r="D698" s="2"/>
       <c r="F698" s="2"/>
-    </row>
-    <row r="699" spans="1:6">
+      <c r="G698" s="4"/>
+    </row>
+    <row r="699" spans="1:7">
       <c r="B699" s="2"/>
       <c r="D699" s="2"/>
       <c r="F699" s="2"/>
-    </row>
-    <row r="700" spans="1:6">
+      <c r="G699" s="4"/>
+    </row>
+    <row r="700" spans="1:7">
       <c r="B700" s="2"/>
       <c r="D700" s="2"/>
       <c r="F700" s="2"/>
-    </row>
-    <row r="701" spans="1:6">
+      <c r="G700" s="4"/>
+    </row>
+    <row r="701" spans="1:7">
       <c r="B701" s="2"/>
       <c r="D701" s="2"/>
       <c r="F701" s="2"/>
-    </row>
-    <row r="702" spans="1:6">
+      <c r="G701" s="4"/>
+    </row>
+    <row r="702" spans="1:7">
       <c r="B702" s="2"/>
       <c r="D702" s="2"/>
       <c r="F702" s="2"/>
-    </row>
-    <row r="703" spans="1:6">
+      <c r="G702" s="4"/>
+    </row>
+    <row r="703" spans="1:7">
       <c r="B703" s="2"/>
       <c r="D703" s="2"/>
       <c r="F703" s="2"/>
-    </row>
-    <row r="704" spans="1:6">
+      <c r="G703" s="4"/>
+    </row>
+    <row r="704" spans="1:7">
       <c r="B704" s="2"/>
       <c r="D704" s="2"/>
       <c r="F704" s="2"/>
-    </row>
-    <row r="705" spans="1:6">
+      <c r="G704" s="4"/>
+    </row>
+    <row r="705" spans="1:7">
       <c r="B705" s="2"/>
       <c r="D705" s="2"/>
       <c r="F705" s="2"/>
-    </row>
-    <row r="706" spans="1:6">
+      <c r="G705" s="4"/>
+    </row>
+    <row r="706" spans="1:7">
       <c r="B706" s="2"/>
       <c r="D706" s="2"/>
       <c r="F706" s="2"/>
-    </row>
-    <row r="707" spans="1:6">
+      <c r="G706" s="4"/>
+    </row>
+    <row r="707" spans="1:7">
       <c r="B707" s="2"/>
       <c r="D707" s="2"/>
       <c r="F707" s="2"/>
-    </row>
-    <row r="708" spans="1:6">
+      <c r="G707" s="4"/>
+    </row>
+    <row r="708" spans="1:7">
       <c r="B708" s="2"/>
       <c r="D708" s="2"/>
       <c r="F708" s="2"/>
-    </row>
-    <row r="709" spans="1:6">
+      <c r="G708" s="4"/>
+    </row>
+    <row r="709" spans="1:7">
       <c r="B709" s="2"/>
       <c r="D709" s="2"/>
       <c r="F709" s="2"/>
-    </row>
-    <row r="710" spans="1:6">
+      <c r="G709" s="4"/>
+    </row>
+    <row r="710" spans="1:7">
       <c r="B710" s="2"/>
       <c r="D710" s="2"/>
       <c r="F710" s="2"/>
-    </row>
-    <row r="711" spans="1:6">
+      <c r="G710" s="4"/>
+    </row>
+    <row r="711" spans="1:7">
       <c r="B711" s="2"/>
       <c r="D711" s="2"/>
       <c r="F711" s="2"/>
-    </row>
-    <row r="712" spans="1:6">
+      <c r="G711" s="4"/>
+    </row>
+    <row r="712" spans="1:7">
       <c r="B712" s="2"/>
       <c r="D712" s="2"/>
       <c r="F712" s="2"/>
-    </row>
-    <row r="713" spans="1:6">
+      <c r="G712" s="4"/>
+    </row>
+    <row r="713" spans="1:7">
       <c r="B713" s="2"/>
       <c r="D713" s="2"/>
       <c r="F713" s="2"/>
-    </row>
-    <row r="714" spans="1:6">
+      <c r="G713" s="4"/>
+    </row>
+    <row r="714" spans="1:7">
       <c r="B714" s="2"/>
       <c r="D714" s="2"/>
       <c r="F714" s="2"/>
-    </row>
-    <row r="715" spans="1:6">
+      <c r="G714" s="4"/>
+    </row>
+    <row r="715" spans="1:7">
       <c r="B715" s="2"/>
       <c r="D715" s="2"/>
       <c r="F715" s="2"/>
-    </row>
-    <row r="716" spans="1:6">
+      <c r="G715" s="4"/>
+    </row>
+    <row r="716" spans="1:7">
       <c r="B716" s="2"/>
       <c r="D716" s="2"/>
       <c r="F716" s="2"/>
-    </row>
-    <row r="717" spans="1:6">
+      <c r="G716" s="4"/>
+    </row>
+    <row r="717" spans="1:7">
       <c r="B717" s="2"/>
       <c r="D717" s="2"/>
       <c r="F717" s="2"/>
-    </row>
-    <row r="718" spans="1:6">
+      <c r="G717" s="4"/>
+    </row>
+    <row r="718" spans="1:7">
       <c r="B718" s="2"/>
       <c r="D718" s="2"/>
       <c r="F718" s="2"/>
-    </row>
-    <row r="719" spans="1:6">
+      <c r="G718" s="4"/>
+    </row>
+    <row r="719" spans="1:7">
       <c r="B719" s="2"/>
       <c r="D719" s="2"/>
       <c r="F719" s="2"/>
-    </row>
-    <row r="720" spans="1:6">
+      <c r="G719" s="4"/>
+    </row>
+    <row r="720" spans="1:7">
       <c r="B720" s="2"/>
       <c r="D720" s="2"/>
       <c r="F720" s="2"/>
-    </row>
-    <row r="721" spans="1:6">
+      <c r="G720" s="4"/>
+    </row>
+    <row r="721" spans="1:7">
       <c r="B721" s="2"/>
       <c r="D721" s="2"/>
       <c r="F721" s="2"/>
-    </row>
-    <row r="722" spans="1:6">
+      <c r="G721" s="4"/>
+    </row>
+    <row r="722" spans="1:7">
       <c r="B722" s="2"/>
       <c r="D722" s="2"/>
       <c r="F722" s="2"/>
-    </row>
-    <row r="723" spans="1:6">
+      <c r="G722" s="4"/>
+    </row>
+    <row r="723" spans="1:7">
       <c r="B723" s="2"/>
       <c r="D723" s="2"/>
       <c r="F723" s="2"/>
-    </row>
-    <row r="724" spans="1:6">
+      <c r="G723" s="4"/>
+    </row>
+    <row r="724" spans="1:7">
       <c r="B724" s="2"/>
       <c r="D724" s="2"/>
       <c r="F724" s="2"/>
-    </row>
-    <row r="725" spans="1:6">
+      <c r="G724" s="4"/>
+    </row>
+    <row r="725" spans="1:7">
       <c r="B725" s="2"/>
       <c r="D725" s="2"/>
       <c r="F725" s="2"/>
-    </row>
-    <row r="726" spans="1:6">
+      <c r="G725" s="4"/>
+    </row>
+    <row r="726" spans="1:7">
       <c r="B726" s="2"/>
       <c r="D726" s="2"/>
       <c r="F726" s="2"/>
-    </row>
-    <row r="727" spans="1:6">
+      <c r="G726" s="4"/>
+    </row>
+    <row r="727" spans="1:7">
       <c r="B727" s="2"/>
       <c r="D727" s="2"/>
       <c r="F727" s="2"/>
-    </row>
-    <row r="728" spans="1:6">
+      <c r="G727" s="4"/>
+    </row>
+    <row r="728" spans="1:7">
       <c r="B728" s="2"/>
       <c r="D728" s="2"/>
       <c r="F728" s="2"/>
-    </row>
-    <row r="729" spans="1:6">
+      <c r="G728" s="4"/>
+    </row>
+    <row r="729" spans="1:7">
       <c r="B729" s="2"/>
       <c r="D729" s="2"/>
       <c r="F729" s="2"/>
-    </row>
-    <row r="730" spans="1:6">
+      <c r="G729" s="4"/>
+    </row>
+    <row r="730" spans="1:7">
       <c r="B730" s="2"/>
       <c r="D730" s="2"/>
       <c r="F730" s="2"/>
-    </row>
-    <row r="731" spans="1:6">
+      <c r="G730" s="4"/>
+    </row>
+    <row r="731" spans="1:7">
       <c r="B731" s="2"/>
       <c r="D731" s="2"/>
       <c r="F731" s="2"/>
-    </row>
-    <row r="732" spans="1:6">
+      <c r="G731" s="4"/>
+    </row>
+    <row r="732" spans="1:7">
       <c r="B732" s="2"/>
       <c r="D732" s="2"/>
       <c r="F732" s="2"/>
-    </row>
-    <row r="733" spans="1:6">
+      <c r="G732" s="4"/>
+    </row>
+    <row r="733" spans="1:7">
       <c r="B733" s="2"/>
       <c r="D733" s="2"/>
       <c r="F733" s="2"/>
-    </row>
-    <row r="734" spans="1:6">
+      <c r="G733" s="4"/>
+    </row>
+    <row r="734" spans="1:7">
       <c r="B734" s="2"/>
       <c r="D734" s="2"/>
       <c r="F734" s="2"/>
-    </row>
-    <row r="735" spans="1:6">
+      <c r="G734" s="4"/>
+    </row>
+    <row r="735" spans="1:7">
       <c r="B735" s="2"/>
       <c r="D735" s="2"/>
       <c r="F735" s="2"/>
-    </row>
-    <row r="736" spans="1:6">
+      <c r="G735" s="4"/>
+    </row>
+    <row r="736" spans="1:7">
       <c r="B736" s="2"/>
       <c r="D736" s="2"/>
       <c r="F736" s="2"/>
-    </row>
-    <row r="737" spans="1:6">
+      <c r="G736" s="4"/>
+    </row>
+    <row r="737" spans="1:7">
       <c r="B737" s="2"/>
       <c r="D737" s="2"/>
       <c r="F737" s="2"/>
-    </row>
-    <row r="738" spans="1:6">
+      <c r="G737" s="4"/>
+    </row>
+    <row r="738" spans="1:7">
       <c r="B738" s="2"/>
       <c r="D738" s="2"/>
       <c r="F738" s="2"/>
-    </row>
-    <row r="739" spans="1:6">
+      <c r="G738" s="4"/>
+    </row>
+    <row r="739" spans="1:7">
       <c r="B739" s="2"/>
       <c r="D739" s="2"/>
       <c r="F739" s="2"/>
-    </row>
-    <row r="740" spans="1:6">
+      <c r="G739" s="4"/>
+    </row>
+    <row r="740" spans="1:7">
       <c r="B740" s="2"/>
       <c r="D740" s="2"/>
       <c r="F740" s="2"/>
-    </row>
-    <row r="741" spans="1:6">
+      <c r="G740" s="4"/>
+    </row>
+    <row r="741" spans="1:7">
       <c r="B741" s="2"/>
       <c r="D741" s="2"/>
       <c r="F741" s="2"/>
-    </row>
-    <row r="742" spans="1:6">
+      <c r="G741" s="4"/>
+    </row>
+    <row r="742" spans="1:7">
       <c r="B742" s="2"/>
       <c r="D742" s="2"/>
       <c r="F742" s="2"/>
-    </row>
-    <row r="743" spans="1:6">
+      <c r="G742" s="4"/>
+    </row>
+    <row r="743" spans="1:7">
       <c r="B743" s="2"/>
       <c r="D743" s="2"/>
       <c r="F743" s="2"/>
-    </row>
-    <row r="744" spans="1:6">
+      <c r="G743" s="4"/>
+    </row>
+    <row r="744" spans="1:7">
       <c r="B744" s="2"/>
       <c r="D744" s="2"/>
       <c r="F744" s="2"/>
-    </row>
-    <row r="745" spans="1:6">
+      <c r="G744" s="4"/>
+    </row>
+    <row r="745" spans="1:7">
       <c r="B745" s="2"/>
       <c r="D745" s="2"/>
       <c r="F745" s="2"/>
-    </row>
-    <row r="746" spans="1:6">
+      <c r="G745" s="4"/>
+    </row>
+    <row r="746" spans="1:7">
       <c r="B746" s="2"/>
       <c r="D746" s="2"/>
       <c r="F746" s="2"/>
-    </row>
-    <row r="747" spans="1:6">
+      <c r="G746" s="4"/>
+    </row>
+    <row r="747" spans="1:7">
       <c r="B747" s="2"/>
       <c r="D747" s="2"/>
       <c r="F747" s="2"/>
-    </row>
-    <row r="748" spans="1:6">
+      <c r="G747" s="4"/>
+    </row>
+    <row r="748" spans="1:7">
       <c r="B748" s="2"/>
       <c r="D748" s="2"/>
       <c r="F748" s="2"/>
-    </row>
-    <row r="749" spans="1:6">
+      <c r="G748" s="4"/>
+    </row>
+    <row r="749" spans="1:7">
       <c r="B749" s="2"/>
       <c r="D749" s="2"/>
       <c r="F749" s="2"/>
-    </row>
-    <row r="750" spans="1:6">
+      <c r="G749" s="4"/>
+    </row>
+    <row r="750" spans="1:7">
       <c r="B750" s="2"/>
       <c r="D750" s="2"/>
       <c r="F750" s="2"/>
-    </row>
-    <row r="751" spans="1:6">
+      <c r="G750" s="4"/>
+    </row>
+    <row r="751" spans="1:7">
       <c r="B751" s="2"/>
       <c r="D751" s="2"/>
       <c r="F751" s="2"/>
-    </row>
-    <row r="752" spans="1:6">
+      <c r="G751" s="4"/>
+    </row>
+    <row r="752" spans="1:7">
       <c r="B752" s="2"/>
       <c r="D752" s="2"/>
       <c r="F752" s="2"/>
-    </row>
-    <row r="753" spans="1:6">
+      <c r="G752" s="4"/>
+    </row>
+    <row r="753" spans="1:7">
       <c r="B753" s="2"/>
       <c r="D753" s="2"/>
       <c r="F753" s="2"/>
-    </row>
-    <row r="754" spans="1:6">
+      <c r="G753" s="4"/>
+    </row>
+    <row r="754" spans="1:7">
       <c r="B754" s="2"/>
       <c r="D754" s="2"/>
       <c r="F754" s="2"/>
-    </row>
-    <row r="755" spans="1:6">
+      <c r="G754" s="4"/>
+    </row>
+    <row r="755" spans="1:7">
       <c r="B755" s="2"/>
       <c r="D755" s="2"/>
       <c r="F755" s="2"/>
-    </row>
-    <row r="756" spans="1:6">
+      <c r="G755" s="4"/>
+    </row>
+    <row r="756" spans="1:7">
       <c r="B756" s="2"/>
       <c r="D756" s="2"/>
       <c r="F756" s="2"/>
-    </row>
-    <row r="757" spans="1:6">
+      <c r="G756" s="4"/>
+    </row>
+    <row r="757" spans="1:7">
       <c r="B757" s="2"/>
       <c r="D757" s="2"/>
       <c r="F757" s="2"/>
-    </row>
-    <row r="758" spans="1:6">
+      <c r="G757" s="4"/>
+    </row>
+    <row r="758" spans="1:7">
       <c r="B758" s="2"/>
       <c r="D758" s="2"/>
       <c r="F758" s="2"/>
-    </row>
-    <row r="759" spans="1:6">
+      <c r="G758" s="4"/>
+    </row>
+    <row r="759" spans="1:7">
       <c r="B759" s="2"/>
       <c r="D759" s="2"/>
       <c r="F759" s="2"/>
-    </row>
-    <row r="760" spans="1:6">
+      <c r="G759" s="4"/>
+    </row>
+    <row r="760" spans="1:7">
       <c r="B760" s="2"/>
       <c r="D760" s="2"/>
       <c r="F760" s="2"/>
-    </row>
-    <row r="761" spans="1:6">
+      <c r="G760" s="4"/>
+    </row>
+    <row r="761" spans="1:7">
       <c r="B761" s="2"/>
       <c r="D761" s="2"/>
       <c r="F761" s="2"/>
-    </row>
-    <row r="762" spans="1:6">
+      <c r="G761" s="4"/>
+    </row>
+    <row r="762" spans="1:7">
       <c r="B762" s="2"/>
       <c r="D762" s="2"/>
       <c r="F762" s="2"/>
-    </row>
-    <row r="763" spans="1:6">
+      <c r="G762" s="4"/>
+    </row>
+    <row r="763" spans="1:7">
       <c r="B763" s="2"/>
       <c r="D763" s="2"/>
       <c r="F763" s="2"/>
-    </row>
-    <row r="764" spans="1:6">
+      <c r="G763" s="4"/>
+    </row>
+    <row r="764" spans="1:7">
       <c r="B764" s="2"/>
       <c r="D764" s="2"/>
       <c r="F764" s="2"/>
-    </row>
-    <row r="765" spans="1:6">
+      <c r="G764" s="4"/>
+    </row>
+    <row r="765" spans="1:7">
       <c r="B765" s="2"/>
       <c r="D765" s="2"/>
       <c r="F765" s="2"/>
-    </row>
-    <row r="766" spans="1:6">
+      <c r="G765" s="4"/>
+    </row>
+    <row r="766" spans="1:7">
       <c r="B766" s="2"/>
       <c r="D766" s="2"/>
       <c r="F766" s="2"/>
-    </row>
-    <row r="767" spans="1:6">
+      <c r="G766" s="4"/>
+    </row>
+    <row r="767" spans="1:7">
       <c r="B767" s="2"/>
       <c r="D767" s="2"/>
       <c r="F767" s="2"/>
-    </row>
-    <row r="768" spans="1:6">
+      <c r="G767" s="4"/>
+    </row>
+    <row r="768" spans="1:7">
       <c r="B768" s="2"/>
       <c r="D768" s="2"/>
       <c r="F768" s="2"/>
-    </row>
-    <row r="769" spans="1:6">
+      <c r="G768" s="4"/>
+    </row>
+    <row r="769" spans="1:7">
       <c r="B769" s="2"/>
       <c r="D769" s="2"/>
       <c r="F769" s="2"/>
-    </row>
-    <row r="770" spans="1:6">
+      <c r="G769" s="4"/>
+    </row>
+    <row r="770" spans="1:7">
       <c r="B770" s="2"/>
       <c r="D770" s="2"/>
       <c r="F770" s="2"/>
-    </row>
-    <row r="771" spans="1:6">
+      <c r="G770" s="4"/>
+    </row>
+    <row r="771" spans="1:7">
       <c r="B771" s="2"/>
       <c r="D771" s="2"/>
       <c r="F771" s="2"/>
-    </row>
-    <row r="772" spans="1:6">
+      <c r="G771" s="4"/>
+    </row>
+    <row r="772" spans="1:7">
       <c r="B772" s="2"/>
       <c r="D772" s="2"/>
       <c r="F772" s="2"/>
-    </row>
-    <row r="773" spans="1:6">
+      <c r="G772" s="4"/>
+    </row>
+    <row r="773" spans="1:7">
       <c r="B773" s="2"/>
       <c r="D773" s="2"/>
       <c r="F773" s="2"/>
-    </row>
-    <row r="774" spans="1:6">
+      <c r="G773" s="4"/>
+    </row>
+    <row r="774" spans="1:7">
       <c r="B774" s="2"/>
       <c r="D774" s="2"/>
       <c r="F774" s="2"/>
-    </row>
-    <row r="775" spans="1:6">
+      <c r="G774" s="4"/>
+    </row>
+    <row r="775" spans="1:7">
       <c r="B775" s="2"/>
       <c r="D775" s="2"/>
       <c r="F775" s="2"/>
-    </row>
-    <row r="776" spans="1:6">
+      <c r="G775" s="4"/>
+    </row>
+    <row r="776" spans="1:7">
       <c r="B776" s="2"/>
       <c r="D776" s="2"/>
       <c r="F776" s="2"/>
-    </row>
-    <row r="777" spans="1:6">
+      <c r="G776" s="4"/>
+    </row>
+    <row r="777" spans="1:7">
       <c r="B777" s="2"/>
       <c r="D777" s="2"/>
       <c r="F777" s="2"/>
-    </row>
-    <row r="778" spans="1:6">
+      <c r="G777" s="4"/>
+    </row>
+    <row r="778" spans="1:7">
       <c r="B778" s="2"/>
       <c r="D778" s="2"/>
       <c r="F778" s="2"/>
-    </row>
-    <row r="779" spans="1:6">
+      <c r="G778" s="4"/>
+    </row>
+    <row r="779" spans="1:7">
       <c r="B779" s="2"/>
       <c r="D779" s="2"/>
       <c r="F779" s="2"/>
-    </row>
-    <row r="780" spans="1:6">
+      <c r="G779" s="4"/>
+    </row>
+    <row r="780" spans="1:7">
       <c r="B780" s="2"/>
       <c r="D780" s="2"/>
       <c r="F780" s="2"/>
-    </row>
-    <row r="781" spans="1:6">
+      <c r="G780" s="4"/>
+    </row>
+    <row r="781" spans="1:7">
       <c r="B781" s="2"/>
       <c r="D781" s="2"/>
       <c r="F781" s="2"/>
-    </row>
-    <row r="782" spans="1:6">
+      <c r="G781" s="4"/>
+    </row>
+    <row r="782" spans="1:7">
       <c r="B782" s="2"/>
       <c r="D782" s="2"/>
       <c r="F782" s="2"/>
-    </row>
-    <row r="783" spans="1:6">
+      <c r="G782" s="4"/>
+    </row>
+    <row r="783" spans="1:7">
       <c r="B783" s="2"/>
       <c r="D783" s="2"/>
       <c r="F783" s="2"/>
-    </row>
-    <row r="784" spans="1:6">
+      <c r="G783" s="4"/>
+    </row>
+    <row r="784" spans="1:7">
       <c r="B784" s="2"/>
       <c r="D784" s="2"/>
       <c r="F784" s="2"/>
-    </row>
-    <row r="785" spans="1:6">
+      <c r="G784" s="4"/>
+    </row>
+    <row r="785" spans="1:7">
       <c r="B785" s="2"/>
       <c r="D785" s="2"/>
       <c r="F785" s="2"/>
-    </row>
-    <row r="786" spans="1:6">
+      <c r="G785" s="4"/>
+    </row>
+    <row r="786" spans="1:7">
       <c r="B786" s="2"/>
       <c r="D786" s="2"/>
       <c r="F786" s="2"/>
-    </row>
-    <row r="787" spans="1:6">
+      <c r="G786" s="4"/>
+    </row>
+    <row r="787" spans="1:7">
       <c r="B787" s="2"/>
       <c r="D787" s="2"/>
       <c r="F787" s="2"/>
-    </row>
-    <row r="788" spans="1:6">
+      <c r="G787" s="4"/>
+    </row>
+    <row r="788" spans="1:7">
       <c r="B788" s="2"/>
       <c r="D788" s="2"/>
       <c r="F788" s="2"/>
-    </row>
-    <row r="789" spans="1:6">
+      <c r="G788" s="4"/>
+    </row>
+    <row r="789" spans="1:7">
       <c r="B789" s="2"/>
       <c r="D789" s="2"/>
       <c r="F789" s="2"/>
-    </row>
-    <row r="790" spans="1:6">
+      <c r="G789" s="4"/>
+    </row>
+    <row r="790" spans="1:7">
       <c r="B790" s="2"/>
       <c r="D790" s="2"/>
       <c r="F790" s="2"/>
-    </row>
-    <row r="791" spans="1:6">
+      <c r="G790" s="4"/>
+    </row>
+    <row r="791" spans="1:7">
       <c r="B791" s="2"/>
       <c r="D791" s="2"/>
       <c r="F791" s="2"/>
-    </row>
-    <row r="792" spans="1:6">
+      <c r="G791" s="4"/>
+    </row>
+    <row r="792" spans="1:7">
       <c r="B792" s="2"/>
       <c r="D792" s="2"/>
       <c r="F792" s="2"/>
-    </row>
-    <row r="793" spans="1:6">
+      <c r="G792" s="4"/>
+    </row>
+    <row r="793" spans="1:7">
       <c r="B793" s="2"/>
       <c r="D793" s="2"/>
       <c r="F793" s="2"/>
-    </row>
-    <row r="794" spans="1:6">
+      <c r="G793" s="4"/>
+    </row>
+    <row r="794" spans="1:7">
       <c r="B794" s="2"/>
       <c r="D794" s="2"/>
       <c r="F794" s="2"/>
-    </row>
-    <row r="795" spans="1:6">
+      <c r="G794" s="4"/>
+    </row>
+    <row r="795" spans="1:7">
       <c r="B795" s="2"/>
       <c r="D795" s="2"/>
       <c r="F795" s="2"/>
-    </row>
-    <row r="796" spans="1:6">
+      <c r="G795" s="4"/>
+    </row>
+    <row r="796" spans="1:7">
       <c r="B796" s="2"/>
       <c r="D796" s="2"/>
       <c r="F796" s="2"/>
-    </row>
-    <row r="797" spans="1:6">
+      <c r="G796" s="4"/>
+    </row>
+    <row r="797" spans="1:7">
       <c r="B797" s="2"/>
       <c r="D797" s="2"/>
       <c r="F797" s="2"/>
-    </row>
-    <row r="798" spans="1:6">
+      <c r="G797" s="4"/>
+    </row>
+    <row r="798" spans="1:7">
       <c r="B798" s="2"/>
       <c r="D798" s="2"/>
       <c r="F798" s="2"/>
-    </row>
-    <row r="799" spans="1:6">
+      <c r="G798" s="4"/>
+    </row>
+    <row r="799" spans="1:7">
       <c r="B799" s="2"/>
       <c r="D799" s="2"/>
       <c r="F799" s="2"/>
-    </row>
-    <row r="800" spans="1:6">
+      <c r="G799" s="4"/>
+    </row>
+    <row r="800" spans="1:7">
       <c r="B800" s="2"/>
       <c r="D800" s="2"/>
       <c r="F800" s="2"/>
-    </row>
-    <row r="801" spans="1:6">
+      <c r="G800" s="4"/>
+    </row>
+    <row r="801" spans="1:7">
       <c r="B801" s="2"/>
       <c r="D801" s="2"/>
       <c r="F801" s="2"/>
-    </row>
-    <row r="802" spans="1:6">
+      <c r="G801" s="4"/>
+    </row>
+    <row r="802" spans="1:7">
       <c r="B802" s="2"/>
       <c r="D802" s="2"/>
       <c r="F802" s="2"/>
-    </row>
-    <row r="803" spans="1:6">
+      <c r="G802" s="4"/>
+    </row>
+    <row r="803" spans="1:7">
       <c r="B803" s="2"/>
       <c r="D803" s="2"/>
       <c r="F803" s="2"/>
-    </row>
-    <row r="804" spans="1:6">
+      <c r="G803" s="4"/>
+    </row>
+    <row r="804" spans="1:7">
       <c r="B804" s="2"/>
       <c r="D804" s="2"/>
       <c r="F804" s="2"/>
-    </row>
-    <row r="805" spans="1:6">
+      <c r="G804" s="4"/>
+    </row>
+    <row r="805" spans="1:7">
       <c r="B805" s="2"/>
       <c r="D805" s="2"/>
       <c r="F805" s="2"/>
-    </row>
-    <row r="806" spans="1:6">
+      <c r="G805" s="4"/>
+    </row>
+    <row r="806" spans="1:7">
       <c r="B806" s="2"/>
       <c r="D806" s="2"/>
       <c r="F806" s="2"/>
-    </row>
-    <row r="807" spans="1:6">
+      <c r="G806" s="4"/>
+    </row>
+    <row r="807" spans="1:7">
       <c r="B807" s="2"/>
       <c r="D807" s="2"/>
       <c r="F807" s="2"/>
-    </row>
-    <row r="808" spans="1:6">
+      <c r="G807" s="4"/>
+    </row>
+    <row r="808" spans="1:7">
       <c r="B808" s="2"/>
       <c r="D808" s="2"/>
       <c r="F808" s="2"/>
-    </row>
-    <row r="809" spans="1:6">
+      <c r="G808" s="4"/>
+    </row>
+    <row r="809" spans="1:7">
       <c r="B809" s="2"/>
       <c r="D809" s="2"/>
       <c r="F809" s="2"/>
-    </row>
-    <row r="810" spans="1:6">
+      <c r="G809" s="4"/>
+    </row>
+    <row r="810" spans="1:7">
       <c r="B810" s="2"/>
       <c r="D810" s="2"/>
       <c r="F810" s="2"/>
-    </row>
-    <row r="811" spans="1:6">
+      <c r="G810" s="4"/>
+    </row>
+    <row r="811" spans="1:7">
       <c r="B811" s="2"/>
       <c r="D811" s="2"/>
       <c r="F811" s="2"/>
-    </row>
-    <row r="812" spans="1:6">
+      <c r="G811" s="4"/>
+    </row>
+    <row r="812" spans="1:7">
       <c r="B812" s="2"/>
       <c r="D812" s="2"/>
       <c r="F812" s="2"/>
-    </row>
-    <row r="813" spans="1:6">
+      <c r="G812" s="4"/>
+    </row>
+    <row r="813" spans="1:7">
       <c r="B813" s="2"/>
       <c r="D813" s="2"/>
       <c r="F813" s="2"/>
-    </row>
-    <row r="814" spans="1:6">
+      <c r="G813" s="4"/>
+    </row>
+    <row r="814" spans="1:7">
       <c r="B814" s="2"/>
       <c r="D814" s="2"/>
       <c r="F814" s="2"/>
-    </row>
-    <row r="815" spans="1:6">
+      <c r="G814" s="4"/>
+    </row>
+    <row r="815" spans="1:7">
       <c r="B815" s="2"/>
       <c r="D815" s="2"/>
       <c r="F815" s="2"/>
-    </row>
-    <row r="816" spans="1:6">
+      <c r="G815" s="4"/>
+    </row>
+    <row r="816" spans="1:7">
       <c r="B816" s="2"/>
       <c r="D816" s="2"/>
       <c r="F816" s="2"/>
-    </row>
-    <row r="817" spans="1:6">
+      <c r="G816" s="4"/>
+    </row>
+    <row r="817" spans="1:7">
       <c r="B817" s="2"/>
       <c r="D817" s="2"/>
       <c r="F817" s="2"/>
-    </row>
-    <row r="818" spans="1:6">
+      <c r="G817" s="4"/>
+    </row>
+    <row r="818" spans="1:7">
       <c r="B818" s="2"/>
       <c r="D818" s="2"/>
       <c r="F818" s="2"/>
-    </row>
-    <row r="819" spans="1:6">
+      <c r="G818" s="4"/>
+    </row>
+    <row r="819" spans="1:7">
       <c r="B819" s="2"/>
       <c r="D819" s="2"/>
       <c r="F819" s="2"/>
-    </row>
-    <row r="820" spans="1:6">
+      <c r="G819" s="4"/>
+    </row>
+    <row r="820" spans="1:7">
       <c r="B820" s="2"/>
       <c r="D820" s="2"/>
       <c r="F820" s="2"/>
-    </row>
-    <row r="821" spans="1:6">
+      <c r="G820" s="4"/>
+    </row>
+    <row r="821" spans="1:7">
       <c r="B821" s="2"/>
       <c r="D821" s="2"/>
       <c r="F821" s="2"/>
-    </row>
-    <row r="822" spans="1:6">
+      <c r="G821" s="4"/>
+    </row>
+    <row r="822" spans="1:7">
       <c r="B822" s="2"/>
       <c r="D822" s="2"/>
       <c r="F822" s="2"/>
-    </row>
-    <row r="823" spans="1:6">
+      <c r="G822" s="4"/>
+    </row>
+    <row r="823" spans="1:7">
       <c r="B823" s="2"/>
       <c r="D823" s="2"/>
       <c r="F823" s="2"/>
-    </row>
-    <row r="824" spans="1:6">
+      <c r="G823" s="4"/>
+    </row>
+    <row r="824" spans="1:7">
       <c r="B824" s="2"/>
       <c r="D824" s="2"/>
       <c r="F824" s="2"/>
-    </row>
-    <row r="825" spans="1:6">
+      <c r="G824" s="4"/>
+    </row>
+    <row r="825" spans="1:7">
       <c r="B825" s="2"/>
       <c r="D825" s="2"/>
       <c r="F825" s="2"/>
-    </row>
-    <row r="826" spans="1:6">
+      <c r="G825" s="4"/>
+    </row>
+    <row r="826" spans="1:7">
       <c r="B826" s="2"/>
       <c r="D826" s="2"/>
       <c r="F826" s="2"/>
-    </row>
-    <row r="827" spans="1:6">
+      <c r="G826" s="4"/>
+    </row>
+    <row r="827" spans="1:7">
       <c r="B827" s="2"/>
       <c r="D827" s="2"/>
       <c r="F827" s="2"/>
-    </row>
-    <row r="828" spans="1:6">
+      <c r="G827" s="4"/>
+    </row>
+    <row r="828" spans="1:7">
       <c r="B828" s="2"/>
       <c r="D828" s="2"/>
       <c r="F828" s="2"/>
-    </row>
-    <row r="829" spans="1:6">
+      <c r="G828" s="4"/>
+    </row>
+    <row r="829" spans="1:7">
       <c r="B829" s="2"/>
       <c r="D829" s="2"/>
       <c r="F829" s="2"/>
-    </row>
-    <row r="830" spans="1:6">
+      <c r="G829" s="4"/>
+    </row>
+    <row r="830" spans="1:7">
       <c r="B830" s="2"/>
       <c r="D830" s="2"/>
       <c r="F830" s="2"/>
-    </row>
-    <row r="831" spans="1:6">
+      <c r="G830" s="4"/>
+    </row>
+    <row r="831" spans="1:7">
       <c r="B831" s="2"/>
       <c r="D831" s="2"/>
       <c r="F831" s="2"/>
-    </row>
-    <row r="832" spans="1:6">
+      <c r="G831" s="4"/>
+    </row>
+    <row r="832" spans="1:7">
       <c r="B832" s="2"/>
       <c r="D832" s="2"/>
       <c r="F832" s="2"/>
-    </row>
-    <row r="833" spans="1:6">
+      <c r="G832" s="4"/>
+    </row>
+    <row r="833" spans="1:7">
       <c r="B833" s="2"/>
       <c r="D833" s="2"/>
       <c r="F833" s="2"/>
-    </row>
-    <row r="834" spans="1:6">
+      <c r="G833" s="4"/>
+    </row>
+    <row r="834" spans="1:7">
       <c r="B834" s="2"/>
       <c r="D834" s="2"/>
       <c r="F834" s="2"/>
-    </row>
-    <row r="835" spans="1:6">
+      <c r="G834" s="4"/>
+    </row>
+    <row r="835" spans="1:7">
       <c r="B835" s="2"/>
       <c r="D835" s="2"/>
       <c r="F835" s="2"/>
-    </row>
-    <row r="836" spans="1:6">
+      <c r="G835" s="4"/>
+    </row>
+    <row r="836" spans="1:7">
       <c r="B836" s="2"/>
       <c r="D836" s="2"/>
       <c r="F836" s="2"/>
-    </row>
-    <row r="837" spans="1:6">
+      <c r="G836" s="4"/>
+    </row>
+    <row r="837" spans="1:7">
       <c r="B837" s="2"/>
       <c r="D837" s="2"/>
       <c r="F837" s="2"/>
-    </row>
-    <row r="838" spans="1:6">
+      <c r="G837" s="4"/>
+    </row>
+    <row r="838" spans="1:7">
       <c r="B838" s="2"/>
       <c r="D838" s="2"/>
       <c r="F838" s="2"/>
-    </row>
-    <row r="839" spans="1:6">
+      <c r="G838" s="4"/>
+    </row>
+    <row r="839" spans="1:7">
       <c r="B839" s="2"/>
       <c r="D839" s="2"/>
       <c r="F839" s="2"/>
-    </row>
-    <row r="840" spans="1:6">
+      <c r="G839" s="4"/>
+    </row>
+    <row r="840" spans="1:7">
       <c r="B840" s="2"/>
       <c r="D840" s="2"/>
       <c r="F840" s="2"/>
-    </row>
-    <row r="841" spans="1:6">
+      <c r="G840" s="4"/>
+    </row>
+    <row r="841" spans="1:7">
       <c r="B841" s="2"/>
       <c r="D841" s="2"/>
       <c r="F841" s="2"/>
-    </row>
-    <row r="842" spans="1:6">
+      <c r="G841" s="4"/>
+    </row>
+    <row r="842" spans="1:7">
       <c r="B842" s="2"/>
       <c r="D842" s="2"/>
       <c r="F842" s="2"/>
-    </row>
-    <row r="843" spans="1:6">
+      <c r="G842" s="4"/>
+    </row>
+    <row r="843" spans="1:7">
       <c r="B843" s="2"/>
       <c r="D843" s="2"/>
       <c r="F843" s="2"/>
-    </row>
-    <row r="844" spans="1:6">
+      <c r="G843" s="4"/>
+    </row>
+    <row r="844" spans="1:7">
       <c r="B844" s="2"/>
       <c r="D844" s="2"/>
       <c r="F844" s="2"/>
-    </row>
-    <row r="845" spans="1:6">
+      <c r="G844" s="4"/>
+    </row>
+    <row r="845" spans="1:7">
       <c r="B845" s="2"/>
       <c r="D845" s="2"/>
       <c r="F845" s="2"/>
-    </row>
-    <row r="846" spans="1:6">
+      <c r="G845" s="4"/>
+    </row>
+    <row r="846" spans="1:7">
       <c r="B846" s="2"/>
       <c r="D846" s="2"/>
       <c r="F846" s="2"/>
-    </row>
-    <row r="847" spans="1:6">
+      <c r="G846" s="4"/>
+    </row>
+    <row r="847" spans="1:7">
       <c r="B847" s="2"/>
       <c r="D847" s="2"/>
       <c r="F847" s="2"/>
-    </row>
-    <row r="848" spans="1:6">
+      <c r="G847" s="4"/>
+    </row>
+    <row r="848" spans="1:7">
       <c r="B848" s="2"/>
       <c r="D848" s="2"/>
       <c r="F848" s="2"/>
-    </row>
-    <row r="849" spans="1:6">
+      <c r="G848" s="4"/>
+    </row>
+    <row r="849" spans="1:7">
       <c r="B849" s="2"/>
       <c r="D849" s="2"/>
       <c r="F849" s="2"/>
-    </row>
-    <row r="850" spans="1:6">
+      <c r="G849" s="4"/>
+    </row>
+    <row r="850" spans="1:7">
       <c r="B850" s="2"/>
       <c r="D850" s="2"/>
       <c r="F850" s="2"/>
-    </row>
-    <row r="851" spans="1:6">
+      <c r="G850" s="4"/>
+    </row>
+    <row r="851" spans="1:7">
       <c r="B851" s="2"/>
       <c r="D851" s="2"/>
       <c r="F851" s="2"/>
-    </row>
-    <row r="852" spans="1:6">
+      <c r="G851" s="4"/>
+    </row>
+    <row r="852" spans="1:7">
       <c r="B852" s="2"/>
       <c r="D852" s="2"/>
       <c r="F852" s="2"/>
-    </row>
-    <row r="853" spans="1:6">
+      <c r="G852" s="4"/>
+    </row>
+    <row r="853" spans="1:7">
       <c r="B853" s="2"/>
       <c r="D853" s="2"/>
       <c r="F853" s="2"/>
-    </row>
-    <row r="854" spans="1:6">
+      <c r="G853" s="4"/>
+    </row>
+    <row r="854" spans="1:7">
       <c r="B854" s="2"/>
       <c r="D854" s="2"/>
       <c r="F854" s="2"/>
-    </row>
-    <row r="855" spans="1:6">
+      <c r="G854" s="4"/>
+    </row>
+    <row r="855" spans="1:7">
       <c r="B855" s="2"/>
       <c r="D855" s="2"/>
       <c r="F855" s="2"/>
-    </row>
-    <row r="856" spans="1:6">
+      <c r="G855" s="4"/>
+    </row>
+    <row r="856" spans="1:7">
       <c r="B856" s="2"/>
       <c r="D856" s="2"/>
       <c r="F856" s="2"/>
-    </row>
-    <row r="857" spans="1:6">
+      <c r="G856" s="4"/>
+    </row>
+    <row r="857" spans="1:7">
       <c r="B857" s="2"/>
       <c r="D857" s="2"/>
       <c r="F857" s="2"/>
-    </row>
-    <row r="858" spans="1:6">
+      <c r="G857" s="4"/>
+    </row>
+    <row r="858" spans="1:7">
       <c r="B858" s="2"/>
       <c r="D858" s="2"/>
       <c r="F858" s="2"/>
-    </row>
-    <row r="859" spans="1:6">
+      <c r="G858" s="4"/>
+    </row>
+    <row r="859" spans="1:7">
       <c r="B859" s="2"/>
       <c r="D859" s="2"/>
       <c r="F859" s="2"/>
-    </row>
-    <row r="860" spans="1:6">
+      <c r="G859" s="4"/>
+    </row>
+    <row r="860" spans="1:7">
       <c r="B860" s="2"/>
       <c r="D860" s="2"/>
       <c r="F860" s="2"/>
-    </row>
-    <row r="861" spans="1:6">
+      <c r="G860" s="4"/>
+    </row>
+    <row r="861" spans="1:7">
       <c r="B861" s="2"/>
       <c r="D861" s="2"/>
       <c r="F861" s="2"/>
-    </row>
-    <row r="862" spans="1:6">
+      <c r="G861" s="4"/>
+    </row>
+    <row r="862" spans="1:7">
       <c r="B862" s="2"/>
       <c r="D862" s="2"/>
       <c r="F862" s="2"/>
-    </row>
-    <row r="863" spans="1:6">
+      <c r="G862" s="4"/>
+    </row>
+    <row r="863" spans="1:7">
       <c r="B863" s="2"/>
       <c r="D863" s="2"/>
       <c r="F863" s="2"/>
-    </row>
-    <row r="864" spans="1:6">
+      <c r="G863" s="4"/>
+    </row>
+    <row r="864" spans="1:7">
       <c r="B864" s="2"/>
       <c r="D864" s="2"/>
       <c r="F864" s="2"/>
-    </row>
-    <row r="865" spans="1:6">
+      <c r="G864" s="4"/>
+    </row>
+    <row r="865" spans="1:7">
       <c r="B865" s="2"/>
       <c r="D865" s="2"/>
       <c r="F865" s="2"/>
-    </row>
-    <row r="866" spans="1:6">
+      <c r="G865" s="4"/>
+    </row>
+    <row r="866" spans="1:7">
       <c r="B866" s="2"/>
       <c r="D866" s="2"/>
       <c r="F866" s="2"/>
-    </row>
-    <row r="867" spans="1:6">
+      <c r="G866" s="4"/>
+    </row>
+    <row r="867" spans="1:7">
       <c r="B867" s="2"/>
       <c r="D867" s="2"/>
       <c r="F867" s="2"/>
-    </row>
-    <row r="868" spans="1:6">
+      <c r="G867" s="4"/>
+    </row>
+    <row r="868" spans="1:7">
       <c r="B868" s="2"/>
       <c r="D868" s="2"/>
       <c r="F868" s="2"/>
-    </row>
-    <row r="869" spans="1:6">
+      <c r="G868" s="4"/>
+    </row>
+    <row r="869" spans="1:7">
       <c r="B869" s="2"/>
       <c r="D869" s="2"/>
       <c r="F869" s="2"/>
-    </row>
-    <row r="870" spans="1:6">
+      <c r="G869" s="4"/>
+    </row>
+    <row r="870" spans="1:7">
       <c r="B870" s="2"/>
       <c r="D870" s="2"/>
       <c r="F870" s="2"/>
-    </row>
-    <row r="871" spans="1:6">
+      <c r="G870" s="4"/>
+    </row>
+    <row r="871" spans="1:7">
       <c r="B871" s="2"/>
       <c r="D871" s="2"/>
       <c r="F871" s="2"/>
-    </row>
-    <row r="872" spans="1:6">
+      <c r="G871" s="4"/>
+    </row>
+    <row r="872" spans="1:7">
       <c r="B872" s="2"/>
       <c r="D872" s="2"/>
       <c r="F872" s="2"/>
-    </row>
-    <row r="873" spans="1:6">
+      <c r="G872" s="4"/>
+    </row>
+    <row r="873" spans="1:7">
       <c r="B873" s="2"/>
       <c r="D873" s="2"/>
       <c r="F873" s="2"/>
-    </row>
-    <row r="874" spans="1:6">
+      <c r="G873" s="4"/>
+    </row>
+    <row r="874" spans="1:7">
       <c r="B874" s="2"/>
       <c r="D874" s="2"/>
       <c r="F874" s="2"/>
-    </row>
-    <row r="875" spans="1:6">
+      <c r="G874" s="4"/>
+    </row>
+    <row r="875" spans="1:7">
       <c r="B875" s="2"/>
       <c r="D875" s="2"/>
       <c r="F875" s="2"/>
-    </row>
-    <row r="876" spans="1:6">
+      <c r="G875" s="4"/>
+    </row>
+    <row r="876" spans="1:7">
       <c r="B876" s="2"/>
       <c r="D876" s="2"/>
       <c r="F876" s="2"/>
-    </row>
-    <row r="877" spans="1:6">
+      <c r="G876" s="4"/>
+    </row>
+    <row r="877" spans="1:7">
       <c r="B877" s="2"/>
       <c r="D877" s="2"/>
       <c r="F877" s="2"/>
-    </row>
-    <row r="878" spans="1:6">
+      <c r="G877" s="4"/>
+    </row>
+    <row r="878" spans="1:7">
       <c r="B878" s="2"/>
       <c r="D878" s="2"/>
       <c r="F878" s="2"/>
-    </row>
-    <row r="879" spans="1:6">
+      <c r="G878" s="4"/>
+    </row>
+    <row r="879" spans="1:7">
       <c r="B879" s="2"/>
       <c r="D879" s="2"/>
       <c r="F879" s="2"/>
-    </row>
-    <row r="880" spans="1:6">
+      <c r="G879" s="4"/>
+    </row>
+    <row r="880" spans="1:7">
       <c r="B880" s="2"/>
       <c r="D880" s="2"/>
       <c r="F880" s="2"/>
-    </row>
-    <row r="881" spans="1:6">
+      <c r="G880" s="4"/>
+    </row>
+    <row r="881" spans="1:7">
       <c r="B881" s="2"/>
       <c r="D881" s="2"/>
       <c r="F881" s="2"/>
-    </row>
-    <row r="882" spans="1:6">
+      <c r="G881" s="4"/>
+    </row>
+    <row r="882" spans="1:7">
       <c r="B882" s="2"/>
       <c r="D882" s="2"/>
       <c r="F882" s="2"/>
-    </row>
-    <row r="883" spans="1:6">
+      <c r="G882" s="4"/>
+    </row>
+    <row r="883" spans="1:7">
       <c r="B883" s="2"/>
       <c r="D883" s="2"/>
       <c r="F883" s="2"/>
-    </row>
-    <row r="884" spans="1:6">
+      <c r="G883" s="4"/>
+    </row>
+    <row r="884" spans="1:7">
       <c r="B884" s="2"/>
       <c r="D884" s="2"/>
       <c r="F884" s="2"/>
-    </row>
-    <row r="885" spans="1:6">
+      <c r="G884" s="4"/>
+    </row>
+    <row r="885" spans="1:7">
       <c r="B885" s="2"/>
       <c r="D885" s="2"/>
       <c r="F885" s="2"/>
-    </row>
-    <row r="886" spans="1:6">
+      <c r="G885" s="4"/>
+    </row>
+    <row r="886" spans="1:7">
       <c r="B886" s="2"/>
       <c r="D886" s="2"/>
       <c r="F886" s="2"/>
-    </row>
-    <row r="887" spans="1:6">
+      <c r="G886" s="4"/>
+    </row>
+    <row r="887" spans="1:7">
       <c r="B887" s="2"/>
       <c r="D887" s="2"/>
       <c r="F887" s="2"/>
-    </row>
-    <row r="888" spans="1:6">
+      <c r="G887" s="4"/>
+    </row>
+    <row r="888" spans="1:7">
       <c r="B888" s="2"/>
       <c r="D888" s="2"/>
       <c r="F888" s="2"/>
-    </row>
-    <row r="889" spans="1:6">
+      <c r="G888" s="4"/>
+    </row>
+    <row r="889" spans="1:7">
       <c r="B889" s="2"/>
       <c r="D889" s="2"/>
       <c r="F889" s="2"/>
-    </row>
-    <row r="890" spans="1:6">
+      <c r="G889" s="4"/>
+    </row>
+    <row r="890" spans="1:7">
       <c r="B890" s="2"/>
       <c r="D890" s="2"/>
       <c r="F890" s="2"/>
-    </row>
-    <row r="891" spans="1:6">
+      <c r="G890" s="4"/>
+    </row>
+    <row r="891" spans="1:7">
       <c r="B891" s="2"/>
       <c r="D891" s="2"/>
       <c r="F891" s="2"/>
-    </row>
-    <row r="892" spans="1:6">
+      <c r="G891" s="4"/>
+    </row>
+    <row r="892" spans="1:7">
       <c r="B892" s="2"/>
       <c r="D892" s="2"/>
       <c r="F892" s="2"/>
-    </row>
-    <row r="893" spans="1:6">
+      <c r="G892" s="4"/>
+    </row>
+    <row r="893" spans="1:7">
       <c r="B893" s="2"/>
       <c r="D893" s="2"/>
       <c r="F893" s="2"/>
-    </row>
-    <row r="894" spans="1:6">
+      <c r="G893" s="4"/>
+    </row>
+    <row r="894" spans="1:7">
       <c r="B894" s="2"/>
       <c r="D894" s="2"/>
       <c r="F894" s="2"/>
-    </row>
-    <row r="895" spans="1:6">
+      <c r="G894" s="4"/>
+    </row>
+    <row r="895" spans="1:7">
       <c r="B895" s="2"/>
       <c r="D895" s="2"/>
       <c r="F895" s="2"/>
-    </row>
-    <row r="896" spans="1:6">
+      <c r="G895" s="4"/>
+    </row>
+    <row r="896" spans="1:7">
       <c r="B896" s="2"/>
       <c r="D896" s="2"/>
       <c r="F896" s="2"/>
-    </row>
-    <row r="897" spans="1:6">
+      <c r="G896" s="4"/>
+    </row>
+    <row r="897" spans="1:7">
       <c r="B897" s="2"/>
       <c r="D897" s="2"/>
       <c r="F897" s="2"/>
-    </row>
-    <row r="898" spans="1:6">
+      <c r="G897" s="4"/>
+    </row>
+    <row r="898" spans="1:7">
       <c r="B898" s="2"/>
       <c r="D898" s="2"/>
       <c r="F898" s="2"/>
-    </row>
-    <row r="899" spans="1:6">
+      <c r="G898" s="4"/>
+    </row>
+    <row r="899" spans="1:7">
       <c r="B899" s="2"/>
       <c r="D899" s="2"/>
       <c r="F899" s="2"/>
-    </row>
-    <row r="900" spans="1:6">
+      <c r="G899" s="4"/>
+    </row>
+    <row r="900" spans="1:7">
       <c r="B900" s="2"/>
       <c r="D900" s="2"/>
       <c r="F900" s="2"/>
-    </row>
-    <row r="901" spans="1:6">
+      <c r="G900" s="4"/>
+    </row>
+    <row r="901" spans="1:7">
       <c r="B901" s="2"/>
       <c r="D901" s="2"/>
       <c r="F901" s="2"/>
-    </row>
-    <row r="902" spans="1:6">
+      <c r="G901" s="4"/>
+    </row>
+    <row r="902" spans="1:7">
       <c r="B902" s="2"/>
       <c r="D902" s="2"/>
       <c r="F902" s="2"/>
-    </row>
-    <row r="903" spans="1:6">
+      <c r="G902" s="4"/>
+    </row>
+    <row r="903" spans="1:7">
       <c r="B903" s="2"/>
       <c r="D903" s="2"/>
       <c r="F903" s="2"/>
-    </row>
-    <row r="904" spans="1:6">
+      <c r="G903" s="4"/>
+    </row>
+    <row r="904" spans="1:7">
       <c r="B904" s="2"/>
       <c r="D904" s="2"/>
       <c r="F904" s="2"/>
-    </row>
-    <row r="905" spans="1:6">
+      <c r="G904" s="4"/>
+    </row>
+    <row r="905" spans="1:7">
       <c r="B905" s="2"/>
       <c r="D905" s="2"/>
       <c r="F905" s="2"/>
-    </row>
-    <row r="906" spans="1:6">
+      <c r="G905" s="4"/>
+    </row>
+    <row r="906" spans="1:7">
       <c r="B906" s="2"/>
       <c r="D906" s="2"/>
       <c r="F906" s="2"/>
-    </row>
-    <row r="907" spans="1:6">
+      <c r="G906" s="4"/>
+    </row>
+    <row r="907" spans="1:7">
       <c r="B907" s="2"/>
       <c r="D907" s="2"/>
       <c r="F907" s="2"/>
-    </row>
-    <row r="908" spans="1:6">
+      <c r="G907" s="4"/>
+    </row>
+    <row r="908" spans="1:7">
       <c r="B908" s="2"/>
       <c r="D908" s="2"/>
       <c r="F908" s="2"/>
-    </row>
-    <row r="909" spans="1:6">
+      <c r="G908" s="4"/>
+    </row>
+    <row r="909" spans="1:7">
       <c r="B909" s="2"/>
       <c r="D909" s="2"/>
       <c r="F909" s="2"/>
-    </row>
-    <row r="910" spans="1:6">
+      <c r="G909" s="4"/>
+    </row>
+    <row r="910" spans="1:7">
       <c r="B910" s="2"/>
       <c r="D910" s="2"/>
       <c r="F910" s="2"/>
-    </row>
-    <row r="911" spans="1:6">
+      <c r="G910" s="4"/>
+    </row>
+    <row r="911" spans="1:7">
       <c r="B911" s="2"/>
       <c r="D911" s="2"/>
       <c r="F911" s="2"/>
-    </row>
-    <row r="912" spans="1:6">
+      <c r="G911" s="4"/>
+    </row>
+    <row r="912" spans="1:7">
       <c r="B912" s="2"/>
       <c r="D912" s="2"/>
       <c r="F912" s="2"/>
-    </row>
-    <row r="913" spans="1:6">
+      <c r="G912" s="4"/>
+    </row>
+    <row r="913" spans="1:7">
       <c r="B913" s="2"/>
       <c r="D913" s="2"/>
       <c r="F913" s="2"/>
-    </row>
-    <row r="914" spans="1:6">
+      <c r="G913" s="4"/>
+    </row>
+    <row r="914" spans="1:7">
       <c r="B914" s="2"/>
       <c r="D914" s="2"/>
       <c r="F914" s="2"/>
-    </row>
-    <row r="915" spans="1:6">
+      <c r="G914" s="4"/>
+    </row>
+    <row r="915" spans="1:7">
       <c r="B915" s="2"/>
       <c r="D915" s="2"/>
       <c r="F915" s="2"/>
-    </row>
-    <row r="916" spans="1:6">
+      <c r="G915" s="4"/>
+    </row>
+    <row r="916" spans="1:7">
       <c r="B916" s="2"/>
       <c r="D916" s="2"/>
       <c r="F916" s="2"/>
-    </row>
-    <row r="917" spans="1:6">
+      <c r="G916" s="4"/>
+    </row>
+    <row r="917" spans="1:7">
       <c r="B917" s="2"/>
       <c r="D917" s="2"/>
       <c r="F917" s="2"/>
-    </row>
-    <row r="918" spans="1:6">
+      <c r="G917" s="4"/>
+    </row>
+    <row r="918" spans="1:7">
       <c r="B918" s="2"/>
       <c r="D918" s="2"/>
       <c r="F918" s="2"/>
-    </row>
-    <row r="919" spans="1:6">
+      <c r="G918" s="4"/>
+    </row>
+    <row r="919" spans="1:7">
       <c r="B919" s="2"/>
       <c r="D919" s="2"/>
       <c r="F919" s="2"/>
-    </row>
-    <row r="920" spans="1:6">
+      <c r="G919" s="4"/>
+    </row>
+    <row r="920" spans="1:7">
       <c r="B920" s="2"/>
       <c r="D920" s="2"/>
       <c r="F920" s="2"/>
-    </row>
-    <row r="921" spans="1:6">
+      <c r="G920" s="4"/>
+    </row>
+    <row r="921" spans="1:7">
       <c r="B921" s="2"/>
       <c r="D921" s="2"/>
       <c r="F921" s="2"/>
-    </row>
-    <row r="922" spans="1:6">
+      <c r="G921" s="4"/>
+    </row>
+    <row r="922" spans="1:7">
       <c r="B922" s="2"/>
       <c r="D922" s="2"/>
       <c r="F922" s="2"/>
-    </row>
-    <row r="923" spans="1:6">
+      <c r="G922" s="4"/>
+    </row>
+    <row r="923" spans="1:7">
       <c r="B923" s="2"/>
       <c r="D923" s="2"/>
       <c r="F923" s="2"/>
-    </row>
-    <row r="924" spans="1:6">
+      <c r="G923" s="4"/>
+    </row>
+    <row r="924" spans="1:7">
       <c r="B924" s="2"/>
       <c r="D924" s="2"/>
       <c r="F924" s="2"/>
-    </row>
-    <row r="925" spans="1:6">
+      <c r="G924" s="4"/>
+    </row>
+    <row r="925" spans="1:7">
       <c r="B925" s="2"/>
       <c r="D925" s="2"/>
       <c r="F925" s="2"/>
-    </row>
-    <row r="926" spans="1:6">
+      <c r="G925" s="4"/>
+    </row>
+    <row r="926" spans="1:7">
       <c r="B926" s="2"/>
       <c r="D926" s="2"/>
       <c r="F926" s="2"/>
-    </row>
-    <row r="927" spans="1:6">
+      <c r="G926" s="4"/>
+    </row>
+    <row r="927" spans="1:7">
       <c r="B927" s="2"/>
       <c r="D927" s="2"/>
       <c r="F927" s="2"/>
-    </row>
-    <row r="928" spans="1:6">
+      <c r="G927" s="4"/>
+    </row>
+    <row r="928" spans="1:7">
       <c r="B928" s="2"/>
       <c r="D928" s="2"/>
       <c r="F928" s="2"/>
-    </row>
-    <row r="929" spans="1:6">
+      <c r="G928" s="4"/>
+    </row>
+    <row r="929" spans="1:7">
       <c r="B929" s="2"/>
       <c r="D929" s="2"/>
       <c r="F929" s="2"/>
-    </row>
-    <row r="930" spans="1:6">
+      <c r="G929" s="4"/>
+    </row>
+    <row r="930" spans="1:7">
       <c r="B930" s="2"/>
       <c r="D930" s="2"/>
       <c r="F930" s="2"/>
-    </row>
-    <row r="931" spans="1:6">
+      <c r="G930" s="4"/>
+    </row>
+    <row r="931" spans="1:7">
       <c r="B931" s="2"/>
       <c r="D931" s="2"/>
       <c r="F931" s="2"/>
-    </row>
-    <row r="932" spans="1:6">
+      <c r="G931" s="4"/>
+    </row>
+    <row r="932" spans="1:7">
       <c r="B932" s="2"/>
       <c r="D932" s="2"/>
       <c r="F932" s="2"/>
-    </row>
-    <row r="933" spans="1:6">
+      <c r="G932" s="4"/>
+    </row>
+    <row r="933" spans="1:7">
       <c r="B933" s="2"/>
       <c r="D933" s="2"/>
       <c r="F933" s="2"/>
-    </row>
-    <row r="934" spans="1:6">
+      <c r="G933" s="4"/>
+    </row>
+    <row r="934" spans="1:7">
       <c r="B934" s="2"/>
       <c r="D934" s="2"/>
       <c r="F934" s="2"/>
-    </row>
-    <row r="935" spans="1:6">
+      <c r="G934" s="4"/>
+    </row>
+    <row r="935" spans="1:7">
       <c r="B935" s="2"/>
       <c r="D935" s="2"/>
       <c r="F935" s="2"/>
-    </row>
-    <row r="936" spans="1:6">
+      <c r="G935" s="4"/>
+    </row>
+    <row r="936" spans="1:7">
       <c r="B936" s="2"/>
       <c r="D936" s="2"/>
       <c r="F936" s="2"/>
-    </row>
-    <row r="937" spans="1:6">
+      <c r="G936" s="4"/>
+    </row>
+    <row r="937" spans="1:7">
       <c r="B937" s="2"/>
       <c r="D937" s="2"/>
       <c r="F937" s="2"/>
-    </row>
-    <row r="938" spans="1:6">
+      <c r="G937" s="4"/>
+    </row>
+    <row r="938" spans="1:7">
       <c r="B938" s="2"/>
       <c r="D938" s="2"/>
       <c r="F938" s="2"/>
-    </row>
-    <row r="939" spans="1:6">
+      <c r="G938" s="4"/>
+    </row>
+    <row r="939" spans="1:7">
       <c r="B939" s="2"/>
       <c r="D939" s="2"/>
       <c r="F939" s="2"/>
-    </row>
-    <row r="940" spans="1:6">
+      <c r="G939" s="4"/>
+    </row>
+    <row r="940" spans="1:7">
       <c r="B940" s="2"/>
       <c r="D940" s="2"/>
       <c r="F940" s="2"/>
-    </row>
-    <row r="941" spans="1:6">
+      <c r="G940" s="4"/>
+    </row>
+    <row r="941" spans="1:7">
       <c r="B941" s="2"/>
       <c r="D941" s="2"/>
       <c r="F941" s="2"/>
-    </row>
-    <row r="942" spans="1:6">
+      <c r="G941" s="4"/>
+    </row>
+    <row r="942" spans="1:7">
       <c r="B942" s="2"/>
       <c r="D942" s="2"/>
       <c r="F942" s="2"/>
-    </row>
-    <row r="943" spans="1:6">
+      <c r="G942" s="4"/>
+    </row>
+    <row r="943" spans="1:7">
       <c r="B943" s="2"/>
       <c r="D943" s="2"/>
       <c r="F943" s="2"/>
-    </row>
-    <row r="944" spans="1:6">
+      <c r="G943" s="4"/>
+    </row>
+    <row r="944" spans="1:7">
       <c r="B944" s="2"/>
       <c r="D944" s="2"/>
       <c r="F944" s="2"/>
-    </row>
-    <row r="945" spans="1:6">
+      <c r="G944" s="4"/>
+    </row>
+    <row r="945" spans="1:7">
       <c r="B945" s="2"/>
       <c r="D945" s="2"/>
       <c r="F945" s="2"/>
-    </row>
-    <row r="946" spans="1:6">
+      <c r="G945" s="4"/>
+    </row>
+    <row r="946" spans="1:7">
       <c r="B946" s="2"/>
       <c r="D946" s="2"/>
       <c r="F946" s="2"/>
-    </row>
-    <row r="947" spans="1:6">
+      <c r="G946" s="4"/>
+    </row>
+    <row r="947" spans="1:7">
       <c r="B947" s="2"/>
       <c r="D947" s="2"/>
       <c r="F947" s="2"/>
-    </row>
-    <row r="948" spans="1:6">
+      <c r="G947" s="4"/>
+    </row>
+    <row r="948" spans="1:7">
       <c r="B948" s="2"/>
       <c r="D948" s="2"/>
       <c r="F948" s="2"/>
-    </row>
-    <row r="949" spans="1:6">
+      <c r="G948" s="4"/>
+    </row>
+    <row r="949" spans="1:7">
       <c r="B949" s="2"/>
       <c r="D949" s="2"/>
       <c r="F949" s="2"/>
-    </row>
-    <row r="950" spans="1:6">
+      <c r="G949" s="4"/>
+    </row>
+    <row r="950" spans="1:7">
       <c r="B950" s="2"/>
       <c r="D950" s="2"/>
       <c r="F950" s="2"/>
-    </row>
-    <row r="951" spans="1:6">
+      <c r="G950" s="4"/>
+    </row>
+    <row r="951" spans="1:7">
       <c r="B951" s="2"/>
       <c r="D951" s="2"/>
       <c r="F951" s="2"/>
-    </row>
-    <row r="952" spans="1:6">
+      <c r="G951" s="4"/>
+    </row>
+    <row r="952" spans="1:7">
       <c r="B952" s="2"/>
       <c r="D952" s="2"/>
       <c r="F952" s="2"/>
-    </row>
-    <row r="953" spans="1:6">
+      <c r="G952" s="4"/>
+    </row>
+    <row r="953" spans="1:7">
       <c r="B953" s="2"/>
       <c r="D953" s="2"/>
       <c r="F953" s="2"/>
-    </row>
-    <row r="954" spans="1:6">
+      <c r="G953" s="4"/>
+    </row>
+    <row r="954" spans="1:7">
       <c r="B954" s="2"/>
       <c r="D954" s="2"/>
       <c r="F954" s="2"/>
-    </row>
-    <row r="955" spans="1:6">
+      <c r="G954" s="4"/>
+    </row>
+    <row r="955" spans="1:7">
       <c r="B955" s="2"/>
       <c r="D955" s="2"/>
       <c r="F955" s="2"/>
-    </row>
-    <row r="956" spans="1:6">
+      <c r="G955" s="4"/>
+    </row>
+    <row r="956" spans="1:7">
       <c r="B956" s="2"/>
       <c r="D956" s="2"/>
       <c r="F956" s="2"/>
-    </row>
-    <row r="957" spans="1:6">
+      <c r="G956" s="4"/>
+    </row>
+    <row r="957" spans="1:7">
       <c r="B957" s="2"/>
       <c r="D957" s="2"/>
       <c r="F957" s="2"/>
-    </row>
-    <row r="958" spans="1:6">
+      <c r="G957" s="4"/>
+    </row>
+    <row r="958" spans="1:7">
       <c r="B958" s="2"/>
       <c r="D958" s="2"/>
       <c r="F958" s="2"/>
-    </row>
-    <row r="959" spans="1:6">
+      <c r="G958" s="4"/>
+    </row>
+    <row r="959" spans="1:7">
       <c r="B959" s="2"/>
       <c r="D959" s="2"/>
       <c r="F959" s="2"/>
-    </row>
-    <row r="960" spans="1:6">
+      <c r="G959" s="4"/>
+    </row>
+    <row r="960" spans="1:7">
       <c r="B960" s="2"/>
       <c r="D960" s="2"/>
       <c r="F960" s="2"/>
-    </row>
-    <row r="961" spans="1:6">
+      <c r="G960" s="4"/>
+    </row>
+    <row r="961" spans="1:7">
       <c r="B961" s="2"/>
       <c r="D961" s="2"/>
       <c r="F961" s="2"/>
-    </row>
-    <row r="962" spans="1:6">
+      <c r="G961" s="4"/>
+    </row>
+    <row r="962" spans="1:7">
       <c r="B962" s="2"/>
       <c r="D962" s="2"/>
       <c r="F962" s="2"/>
-    </row>
-    <row r="963" spans="1:6">
+      <c r="G962" s="4"/>
+    </row>
+    <row r="963" spans="1:7">
       <c r="B963" s="2"/>
       <c r="D963" s="2"/>
       <c r="F963" s="2"/>
-    </row>
-    <row r="964" spans="1:6">
+      <c r="G963" s="4"/>
+    </row>
+    <row r="964" spans="1:7">
       <c r="B964" s="2"/>
       <c r="D964" s="2"/>
       <c r="F964" s="2"/>
-    </row>
-    <row r="965" spans="1:6">
+      <c r="G964" s="4"/>
+    </row>
+    <row r="965" spans="1:7">
       <c r="B965" s="2"/>
       <c r="D965" s="2"/>
       <c r="F965" s="2"/>
-    </row>
-    <row r="966" spans="1:6">
+      <c r="G965" s="4"/>
+    </row>
+    <row r="966" spans="1:7">
       <c r="B966" s="2"/>
       <c r="D966" s="2"/>
       <c r="F966" s="2"/>
-    </row>
-    <row r="967" spans="1:6">
+      <c r="G966" s="4"/>
+    </row>
+    <row r="967" spans="1:7">
       <c r="B967" s="2"/>
       <c r="D967" s="2"/>
       <c r="F967" s="2"/>
-    </row>
-    <row r="968" spans="1:6">
+      <c r="G967" s="4"/>
+    </row>
+    <row r="968" spans="1:7">
       <c r="B968" s="2"/>
       <c r="D968" s="2"/>
       <c r="F968" s="2"/>
-    </row>
-    <row r="969" spans="1:6">
+      <c r="G968" s="4"/>
+    </row>
+    <row r="969" spans="1:7">
       <c r="B969" s="2"/>
       <c r="D969" s="2"/>
       <c r="F969" s="2"/>
-    </row>
-    <row r="970" spans="1:6">
+      <c r="G969" s="4"/>
+    </row>
+    <row r="970" spans="1:7">
       <c r="B970" s="2"/>
       <c r="D970" s="2"/>
       <c r="F970" s="2"/>
-    </row>
-    <row r="971" spans="1:6">
+      <c r="G970" s="4"/>
+    </row>
+    <row r="971" spans="1:7">
       <c r="B971" s="2"/>
       <c r="D971" s="2"/>
       <c r="F971" s="2"/>
-    </row>
-    <row r="972" spans="1:6">
+      <c r="G971" s="4"/>
+    </row>
+    <row r="972" spans="1:7">
       <c r="B972" s="2"/>
       <c r="D972" s="2"/>
       <c r="F972" s="2"/>
-    </row>
-    <row r="973" spans="1:6">
+      <c r="G972" s="4"/>
+    </row>
+    <row r="973" spans="1:7">
       <c r="B973" s="2"/>
       <c r="D973" s="2"/>
       <c r="F973" s="2"/>
-    </row>
-    <row r="974" spans="1:6">
+      <c r="G973" s="4"/>
+    </row>
+    <row r="974" spans="1:7">
       <c r="B974" s="2"/>
       <c r="D974" s="2"/>
       <c r="F974" s="2"/>
-    </row>
-    <row r="975" spans="1:6">
+      <c r="G974" s="4"/>
+    </row>
+    <row r="975" spans="1:7">
       <c r="B975" s="2"/>
       <c r="D975" s="2"/>
       <c r="F975" s="2"/>
-    </row>
-    <row r="976" spans="1:6">
+      <c r="G975" s="4"/>
+    </row>
+    <row r="976" spans="1:7">
       <c r="B976" s="2"/>
       <c r="D976" s="2"/>
       <c r="F976" s="2"/>
-    </row>
-    <row r="977" spans="1:6">
+      <c r="G976" s="4"/>
+    </row>
+    <row r="977" spans="1:7">
       <c r="B977" s="2"/>
       <c r="D977" s="2"/>
       <c r="F977" s="2"/>
-    </row>
-    <row r="978" spans="1:6">
+      <c r="G977" s="4"/>
+    </row>
+    <row r="978" spans="1:7">
       <c r="B978" s="2"/>
       <c r="D978" s="2"/>
       <c r="F978" s="2"/>
-    </row>
-    <row r="979" spans="1:6">
+      <c r="G978" s="4"/>
+    </row>
+    <row r="979" spans="1:7">
       <c r="B979" s="2"/>
       <c r="D979" s="2"/>
       <c r="F979" s="2"/>
-    </row>
-    <row r="980" spans="1:6">
+      <c r="G979" s="4"/>
+    </row>
+    <row r="980" spans="1:7">
       <c r="B980" s="2"/>
       <c r="D980" s="2"/>
       <c r="F980" s="2"/>
-    </row>
-    <row r="981" spans="1:6">
+      <c r="G980" s="4"/>
+    </row>
+    <row r="981" spans="1:7">
       <c r="B981" s="2"/>
       <c r="D981" s="2"/>
       <c r="F981" s="2"/>
-    </row>
-    <row r="982" spans="1:6">
+      <c r="G981" s="4"/>
+    </row>
+    <row r="982" spans="1:7">
       <c r="B982" s="2"/>
       <c r="D982" s="2"/>
       <c r="F982" s="2"/>
-    </row>
-    <row r="983" spans="1:6">
+      <c r="G982" s="4"/>
+    </row>
+    <row r="983" spans="1:7">
       <c r="B983" s="2"/>
       <c r="D983" s="2"/>
       <c r="F983" s="2"/>
-    </row>
-    <row r="984" spans="1:6">
+      <c r="G983" s="4"/>
+    </row>
+    <row r="984" spans="1:7">
       <c r="B984" s="2"/>
       <c r="D984" s="2"/>
       <c r="F984" s="2"/>
-    </row>
-    <row r="985" spans="1:6">
+      <c r="G984" s="4"/>
+    </row>
+    <row r="985" spans="1:7">
       <c r="B985" s="2"/>
       <c r="D985" s="2"/>
       <c r="F985" s="2"/>
-    </row>
-    <row r="986" spans="1:6">
+      <c r="G985" s="4"/>
+    </row>
+    <row r="986" spans="1:7">
       <c r="B986" s="2"/>
       <c r="D986" s="2"/>
       <c r="F986" s="2"/>
-    </row>
-    <row r="987" spans="1:6">
+      <c r="G986" s="4"/>
+    </row>
+    <row r="987" spans="1:7">
       <c r="B987" s="2"/>
       <c r="D987" s="2"/>
       <c r="F987" s="2"/>
-    </row>
-    <row r="988" spans="1:6">
+      <c r="G987" s="4"/>
+    </row>
+    <row r="988" spans="1:7">
       <c r="B988" s="2"/>
       <c r="D988" s="2"/>
       <c r="F988" s="2"/>
-    </row>
-    <row r="989" spans="1:6">
+      <c r="G988" s="4"/>
+    </row>
+    <row r="989" spans="1:7">
       <c r="B989" s="2"/>
       <c r="D989" s="2"/>
       <c r="F989" s="2"/>
-    </row>
-    <row r="990" spans="1:6">
+      <c r="G989" s="4"/>
+    </row>
+    <row r="990" spans="1:7">
       <c r="B990" s="2"/>
       <c r="D990" s="2"/>
       <c r="F990" s="2"/>
-    </row>
-    <row r="991" spans="1:6">
+      <c r="G990" s="4"/>
+    </row>
+    <row r="991" spans="1:7">
       <c r="B991" s="2"/>
       <c r="D991" s="2"/>
       <c r="F991" s="2"/>
-    </row>
-    <row r="992" spans="1:6">
+      <c r="G991" s="4"/>
+    </row>
+    <row r="992" spans="1:7">
       <c r="B992" s="2"/>
       <c r="D992" s="2"/>
       <c r="F992" s="2"/>
-    </row>
-    <row r="993" spans="1:6">
+      <c r="G992" s="4"/>
+    </row>
+    <row r="993" spans="1:7">
       <c r="B993" s="2"/>
       <c r="D993" s="2"/>
       <c r="F993" s="2"/>
-    </row>
-    <row r="994" spans="1:6">
+      <c r="G993" s="4"/>
+    </row>
+    <row r="994" spans="1:7">
       <c r="B994" s="2"/>
       <c r="D994" s="2"/>
       <c r="F994" s="2"/>
-    </row>
-    <row r="995" spans="1:6">
+      <c r="G994" s="4"/>
+    </row>
+    <row r="995" spans="1:7">
       <c r="B995" s="2"/>
       <c r="D995" s="2"/>
       <c r="F995" s="2"/>
-    </row>
-    <row r="996" spans="1:6">
+      <c r="G995" s="4"/>
+    </row>
+    <row r="996" spans="1:7">
       <c r="B996" s="2"/>
       <c r="D996" s="2"/>
       <c r="F996" s="2"/>
-    </row>
-    <row r="997" spans="1:6">
+      <c r="G996" s="4"/>
+    </row>
+    <row r="997" spans="1:7">
       <c r="B997" s="2"/>
       <c r="D997" s="2"/>
       <c r="F997" s="2"/>
-    </row>
-    <row r="998" spans="1:6">
+      <c r="G997" s="4"/>
+    </row>
+    <row r="998" spans="1:7">
       <c r="B998" s="2"/>
       <c r="D998" s="2"/>
       <c r="F998" s="2"/>
-    </row>
-    <row r="999" spans="1:6">
+      <c r="G998" s="4"/>
+    </row>
+    <row r="999" spans="1:7">
       <c r="B999" s="2"/>
       <c r="D999" s="2"/>
       <c r="F999" s="2"/>
-    </row>
-    <row r="1000" spans="1:6">
+      <c r="G999" s="4"/>
+    </row>
+    <row r="1000" spans="1:7">
       <c r="B1000" s="2"/>
       <c r="D1000" s="2"/>
       <c r="F1000" s="2"/>
+      <c r="G1000" s="4"/>
     </row>
   </sheetData>
   <dataValidations count="2">
